--- a/Data/Output/ContactosReporte.xlsx
+++ b/Data/Output/ContactosReporte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\OneDrive\Documents\UiPath\UiPath_RPA_Adriana_Carrillo\Data\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E4475F-32B7-4E59-8B0E-7EAA63CA425A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFB04E6-7199-4E84-897B-71AC86321359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1817" yWindow="1817" windowWidth="16457" windowHeight="8966" xr2:uid="{723EF56F-89BA-4F5A-8EA8-F9BDFCB60ACD}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{723EF56F-89BA-4F5A-8EA8-F9BDFCB60ACD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="388">
   <si>
     <t>Número Telefónico</t>
   </si>
@@ -39,1051 +39,1156 @@
     <t>Localidad</t>
   </si>
   <si>
-    <t>TUMBACO</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>SAN ANTONIO DE PICHINCHA</t>
-  </si>
-  <si>
-    <t>ROCAFUERTE (ESMERALDAS)</t>
-  </si>
-  <si>
-    <t>QUITO</t>
-  </si>
-  <si>
-    <t>BAQUERO CARRILLO JOSE ARTURO PATRICIO</t>
-  </si>
-  <si>
-    <t>COTOPAXI N8 73 Y ESMERALDAS COTOPAXI N8</t>
-  </si>
-  <si>
-    <t>BAQUERO CARRILLO MYRIAM GLADYS</t>
-  </si>
-  <si>
-    <t>BOSSANO IGNACIO 732 Y AVENIDA 6 DE DICIEMBRE EDIFICIO BOSSANO PISO 6 DEPARTAMENTO 603 EDF-BOSSANO-PISO-6-DEPT-603 BOSSANO IGNACIO</t>
-  </si>
-  <si>
-    <t>BARAJA CARRILLO GUILLERMO ANTONIO</t>
-  </si>
-  <si>
-    <t>CALLE S33A 2D Y RAFAEL GARCIA LOTE 2D LAS CUADRAS FUNDEPORTE LOTE-2D-LAS CUADRAS-FUNDEPORTE</t>
-  </si>
-  <si>
-    <t>SARANGO CARRILLO DARWIN LEONIDAS</t>
-  </si>
-  <si>
-    <t>CALLE S34S OE12- 1228 Y CALLE OE12A CALLE S34S OE</t>
-  </si>
-  <si>
-    <t>POMASQUI</t>
-  </si>
-  <si>
-    <t>SARANGO CARRILLO BERTHA GENARA</t>
-  </si>
-  <si>
-    <t>MARCELINA NOLIVOS OE1- 69 Y PASAJE NUEVO HORIZONTTE CONDOMINIO NUEVO HORIZONTE CASA A1 CND-NUEVO HORIZONTE-CASA-A1 MARCELINA NOLIVOS</t>
-  </si>
-  <si>
-    <t>BARRAGAN CARRILLO SANDRA PATRICIA</t>
-  </si>
-  <si>
-    <t>AVENIDA INTEROCEANICA KILOMETRO 0L VIA PIFO BARRIO SAN FRANCISCO VIA PIFO BRR- SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>PIFO</t>
-  </si>
-  <si>
     <t>Número Reservado</t>
   </si>
   <si>
-    <t>MIRAVALLE</t>
-  </si>
-  <si>
-    <t>LA VICTORIA COTOPAXI</t>
-  </si>
-  <si>
-    <t>CUMBAYA</t>
-  </si>
-  <si>
-    <t>CONOCOTO</t>
-  </si>
-  <si>
-    <t>CALDERON</t>
-  </si>
-  <si>
-    <t>AMAGUANA</t>
-  </si>
-  <si>
     <t>:: DATOS TELEFONICOS ::</t>
   </si>
   <si>
-    <t>CARMEN IPATIA PARRA CARRILLO</t>
-  </si>
-  <si>
-    <t>ZAMBIZA 0 N Y BABAHOYO ZAMBIZA 0 Y BABAHOYO</t>
-  </si>
-  <si>
-    <t>ZAMBIZA</t>
-  </si>
-  <si>
-    <t>TERAN CARRILLO OLGA BEATRIZ</t>
-  </si>
-  <si>
-    <t>LOS ARUPOS 0 CALLE MANUELA LEON Y PASAJE TERAN CASA E6-107 COLOR BEIGE CON TERRACOTA TERRACOTA</t>
-  </si>
-  <si>
-    <t>VILLAVICENCIO CARRILLO SEGUNDO ROBERTO</t>
-  </si>
-  <si>
-    <t>AV FRANCISCO DE ORELLANA 0 Y PASAJE GUILLERMO MARTINEZ BARRIO VILLA VEGA BARRIO VILLA VEGA</t>
-  </si>
-  <si>
-    <t>BARRERA CARRILLO CARMELA SUSANA</t>
-  </si>
-  <si>
-    <t>BOYACA 27 Y SAN MARTIN BARRIO SAN BLAS BARRIO SAN-BLAS BOYACA</t>
-  </si>
-  <si>
-    <t>BOYACA 27 Y LATACUNGA</t>
-  </si>
-  <si>
-    <t>BARRERA CARRILLO ELSA JEANNETT</t>
-  </si>
-  <si>
-    <t>NORBERTO SALAZAR 0 Y LA UNION CONJUNTO CASA QUINTA II DEPARTAMENTO 20 NORBERTO SALAZAR casa con cerramiento ladrillo puerta gra CONJUNTO CASA QUINTA II DEPARTAMENTO 20 NORBERTO SALAZAR casa con cerramiento ladrillo puerta gran LA UNION</t>
-  </si>
-  <si>
-    <t>CARANQUI CARRILLO EDUARDO</t>
-  </si>
-  <si>
-    <t>FDC CN TUMBACO RUMIHUAICO SAN JOSE DE RUMIHUAICO LOTE 44</t>
-  </si>
-  <si>
-    <t>CADENA CARRILLO GALO FERNANDO</t>
-  </si>
-  <si>
-    <t>DE LOS NARDOS 134 Y DE LOS MADRO�OS SCT CLUB LOS CHILLOS Y DE LOS-MADRO�OS SCT</t>
-  </si>
-  <si>
-    <t>SANGOLQUI</t>
-  </si>
-  <si>
-    <t>VERDEZOTO CARRILLO MARCO PATRICIO</t>
-  </si>
-  <si>
-    <t>SAN JUAN DE DIOS 0 Y PASAJE JOSE CALDERON CJTO ALICANTE CASA 62</t>
-  </si>
-  <si>
-    <t>ALVARO PATRICIO CARRILLO PUNINA</t>
-  </si>
-  <si>
-    <t>LOS PINGUINOS 0 Y Y DE LOS CISNES CJTO SAHARA</t>
-  </si>
-  <si>
-    <t>AMALIA CARRILLO BASANTES</t>
-  </si>
-  <si>
-    <t>PASAJE PEDERNALES N 2 Y AVE SUA</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL URBANIZACION PLAYA CHICA 2 LOTE H 2</t>
-  </si>
-  <si>
-    <t>ASTRI ANTONIA CARRILLO SANTAMARIA</t>
-  </si>
-  <si>
-    <t>CHILLO JIJON 0 Y SAN PEDRO DE TABOADA CJTO CAVALIER CASA 1 BL HELECHOS CJTO CAVALIER-CASA 1-BL-HELECHOS</t>
-  </si>
-  <si>
-    <t>AZUCENA MARIBEL MAYA CARRILLO</t>
-  </si>
-  <si>
-    <t>RIO ZAMORA 0 Y ACCESO 5 conjunto jardines de san luis etapa1 casa 44 conjunto jardines de san luis etapa1 casa 44 ACCESO 5</t>
-  </si>
-  <si>
-    <t>BYRON SANTIAGO CARRILLO MURILLO</t>
-  </si>
-  <si>
-    <t>CENEPA S4 315 Y RIO ZAMORA RIO ZAMORA</t>
-  </si>
-  <si>
-    <t>TOBAR CARRILLO CARMEN RENE</t>
-  </si>
-  <si>
-    <t>CALLE SE�OR DEL ARBOL 0 N131 8 DE SEPTIEMBRE N131 8 DE-SEPTIEMBRE PARQUE PRINCIPAL</t>
-  </si>
-  <si>
-    <t>TOBAR CARRILLO MERCEDES</t>
-  </si>
-  <si>
-    <t>CALLE SE�OR DEL ARBOL 118 Y QUIJUAR CALLE SE�OR DEL ARBOL</t>
-  </si>
-  <si>
-    <t>ANA LUCIA ENRIQUEZ CARRILLO</t>
-  </si>
-  <si>
-    <t>PIO XII 38 Y MIGUEL MEDINA SECT BELLAVISTA</t>
-  </si>
-  <si>
-    <t>ARTEAGA CARRILLO SANDRA ELISABETH</t>
-  </si>
-  <si>
-    <t>MARIANA DE JESUS 387</t>
-  </si>
-  <si>
-    <t>AYALA CARRILLO JHONNY FERNANDO</t>
-  </si>
-  <si>
-    <t>SENDEROS DEL QUINDE 0 Y ZABALA URBANIZACION SENDERO DEL QUINDE CASA B-04 SECTOR ZABALA - CALDERON URB-SENDERO DEL QUINDE-CASA-B-04 SENDEROS DEL QUINDE</t>
-  </si>
-  <si>
-    <t>ROCIO DEL CARMEN CARRILLO MORA</t>
-  </si>
-  <si>
-    <t>INQ RUMIPAMBA OE2/31 Y ATAHUALPA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ CARRILLO CYNTHIA PAOLA</t>
-  </si>
-  <si>
-    <t>JOSE BARBA 15127L Y SOLANO</t>
-  </si>
-  <si>
-    <t>TERAN CARRILLO JORGE</t>
-  </si>
-  <si>
-    <t>J PAREDES 94</t>
-  </si>
-  <si>
-    <t>IGNACIO CARRASCO N45- 84 Y AV JOSE PAREDES</t>
-  </si>
-  <si>
-    <t>TIERRA CARRILLO LUZ MARIA</t>
-  </si>
-  <si>
-    <t>CALLE D 0 Y Y PASAJE CH SANTO TOMAS</t>
-  </si>
-  <si>
-    <t>TOCTAQUIZA CARRILLO ANGELICA MARIA</t>
-  </si>
-  <si>
-    <t>JOSE FERNADEZ 0 Y ANTONIO FLORES JIJON</t>
-  </si>
-  <si>
-    <t>TOMAS GABRIEL OJEDA CARRILLO</t>
-  </si>
-  <si>
-    <t>JOSE GONZALEZ OE15 104 Y BRACAMONTE BRACAMONTE</t>
-  </si>
-  <si>
-    <t>TORRES CARRILLO ANITA IVUKNOSHE</t>
-  </si>
-  <si>
-    <t>ANTONIO DE ULLOA N34- 225 Y ABELARDO MONCAYO</t>
-  </si>
-  <si>
-    <t>VALLEJO CARRILLO NELSON VICENTE</t>
-  </si>
-  <si>
-    <t>AVENIDA GONZALEZ SUAREZ 730 EDIFICIO VISTA AL VALLE 6P DTO 604</t>
-  </si>
-  <si>
-    <t>AVENIDA GONZALES SUAREZ N31 10 Y CONNESSIAT EDIFICIO VISTA AL VALLE PISO 6 DEPARTAMENTO 603 EDF-VISTA AL VALLE-PISO-6-DEPT-603 AVENIDA GONZALEZ SUAREZ N31</t>
-  </si>
-  <si>
-    <t>VASQUEZ CARRILLO NATALIA PAULINA</t>
-  </si>
-  <si>
-    <t>LOPE ORTIZ DE AGUILERA S15 282 Y DIEGO MEJIA LA INTERNACIONAL</t>
-  </si>
-  <si>
-    <t>VEGA CARRILLO JUAN PATRICIO BERNARDO</t>
-  </si>
-  <si>
-    <t>RIO PERIPA N71 0 Y Y RIO BIGAL RIO PERIPA N71 208 Y JUAN PROCEL CONJUNTO JARDINES DEL CONDADO 1 CASA A 6</t>
-  </si>
-  <si>
-    <t>VERGARA CARRILLO CARLOS JACINTO</t>
-  </si>
-  <si>
-    <t>URBANIZACION RUMINIAHUI MANZANA 45 C 24</t>
-  </si>
-  <si>
-    <t>VERGARA CARRILLO CARLOS ULPIANO</t>
-  </si>
-  <si>
-    <t>CIUDADELA RUMINIAHUI MANZANA 19 C 10</t>
-  </si>
-  <si>
-    <t>VERONICA ALEXANDRA PATI�O CARRILLO</t>
-  </si>
-  <si>
-    <t>CALLE 16 1Y Y PROFETA JEREMIAS</t>
-  </si>
-  <si>
-    <t>VIZCAINO CARRILLO MARIA FANNY</t>
-  </si>
-  <si>
-    <t>IGNACIO DE SAN MARIA E330 NUNEZ DE VELA BENEKLCAZAR EDIFICIO METROPOLI OFICINA 601 6TOPS JUNTO A MI JUGUETERIA EL CCI EDF METROPOLI OFC 601 6TOPS JTO A MI JUGUETERIA EL CCI BENEKLCAZAR</t>
-  </si>
-  <si>
-    <t>VIZCAINO CARRILLO MARTHA ALICIA</t>
-  </si>
-  <si>
-    <t>CAPITAN RAMON BORJA SN 5370 FILCARAVAJAL CasaPUERTA VERDE Piso 2 CASA-PUERTA VERDE-PISO-2-- LA UNICA CASA AL FINAL DE LAS CANCHAS</t>
-  </si>
-  <si>
-    <t>VICTOR MARTILLO 0 Y Y DE LOS CHOLANES EDIF ALEJANDRA 1 ER PISO APTO 8</t>
-  </si>
-  <si>
-    <t>WASHINGTON CRISTOBAL CARRILLO GALLARDO</t>
-  </si>
-  <si>
-    <t>URBANIZACION EL BOSQUE II ETAPA AVENIDA EL PARQUE 6TA TRANSVERSAL 167</t>
-  </si>
-  <si>
-    <t>SANTA PRISCA ENRIQUE RITTER 8VA TRANSVERSAL 332 Y LA GA SANTA PRISCA ENRIQUE RITTER 8VA TRANSVERSAL</t>
-  </si>
-  <si>
-    <t>ANTONIO DE ULLOA 0 Y Y ACU�A</t>
-  </si>
-  <si>
-    <t>WASHINGTON EDUARDO LOPEZ CARRILLO</t>
-  </si>
-  <si>
-    <t>CALLE V 926 Y CALLE A</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO ANGELICA LUCILA</t>
-  </si>
-  <si>
-    <t>NECOCHEA 768 Y MILLER NECOCHEA</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO BETHZABE HIPATIA</t>
-  </si>
-  <si>
-    <t>QUININDE S7- 170 GUAYLLABAMBA Casa1 PLANTA CasaCOLOR NARANJA CLARO OR NARANJA CLARO</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO JORGE EFRAIN</t>
-  </si>
-  <si>
-    <t>CALLE E 0 Y JUAN DE SELIS DEPARTAMENTO 4-A EDIFICIO EL CARDENAL PONCIAN DPT 4-A EDIF EL-CARDENAL PONCIAN CALLE E</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>JUAN DE SELIS 3032 Y PASAJE 33 EDIFICIO EL CARDENAL DEPARTAMENTO 4B EDIF.-EL CARDENAL-DEPT-4B JUAN DE SELIS</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>CUBIJIES 0 OE4-318 Y APUELA OE4-318 Y-APUELA CUBIJIES 0</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO MARIA IGNACIA SUSANA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO CLAVER SPMZ 3 BLOQUE 5 DEPARTAMENTO 1 A PB</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>GONZALO NORIEGA N39 55 Y PORTETE</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO NELLY ELENA ISABEL</t>
-  </si>
-  <si>
-    <t>NACIONES UNIDAS EDIFICIO TORRES DE INIAQUITO 13AVO P DEPARTAMENTO</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO RITA DEL ROCIO</t>
-  </si>
-  <si>
-    <t>SECTOR LA ISLA MANZANA 4 CASA 29 PASAJE G</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO RONALD RUPERTO</t>
-  </si>
-  <si>
-    <t>LUIS DRESSEL OE2 120 EMILIO MULIENDOR CLEMENTE BALLEN</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO SEGUNDO</t>
-  </si>
-  <si>
-    <t>CALLE 2A 150L Y AVENIDA JAIME ROLDOS AGUILERA URBANIZACION MASTODONTES A 200 METROS DEL COLEGIO AMERICANO CARCEL URB MASTODONTES-A 200 METROS-DEL COLEGIO-AMERICANO CARCEL CALLE 2A</t>
-  </si>
-  <si>
-    <t>RUTH ELIZABETH CARRILLO VILLEGAS</t>
-  </si>
-  <si>
-    <t>DE LAS ANONAS E14- 72Y Y CARL NIELSEN SECTOR EL INCA SECTOR EL INCA</t>
-  </si>
-  <si>
-    <t>RUTH MARIELA CARRILLO AGUILAR</t>
-  </si>
-  <si>
-    <t>BARTOLOME DE LA ROSA 3780N Y PEDRO VELASCO E2</t>
-  </si>
-  <si>
-    <t>VILLACIS CARRILLO JEANNETT LUCILA</t>
-  </si>
-  <si>
-    <t>CONJUNTO FARSALIA CASA 74 AVENIDA ELOY ALFARO Y RAMON BORJA</t>
-  </si>
-  <si>
-    <t>VILLACIS CARRILLO PIEDAD ILEANA</t>
-  </si>
-  <si>
-    <t>CARRION 355 Y LEONIDAS PLAZA EDIFICIO CARRION PLAZA PISO CUATRO DEPARTAMENTO 403 EDF-CARRION PLAZA-PISO-CUATRO-DEPT-403 CARRION</t>
-  </si>
-  <si>
-    <t>VILLACRECES CARRILLO CLARA LIGIA</t>
-  </si>
-  <si>
-    <t>CHAMBO S7 308 Y SANGAY CDLA. MEXICO CDLA.-MEXICO</t>
-  </si>
-  <si>
-    <t>VILLACRES CARRILLO JOSE AMABLE</t>
-  </si>
-  <si>
-    <t>TABIAZO 18 Y FRANCISCO BOLA�OS CONJUNTO RIVERA 2 CASA 18 CJTO RIVERA-2-CASA-18 TABIAZO</t>
-  </si>
-  <si>
-    <t>VILLACRES CARRILLO MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>VICENTE ANDA AGUIRRE OE5 188 MACHALA CASA DURAZNO 2PISOS CASA-DURAZNO 2PISOS---- BARRIO SAN PEDRO CLAVER A 1-2 HACIA ESTE DE LA PISCINA DE SAN CARLOS</t>
-  </si>
-  <si>
-    <t>VILLAGOMEZ CARRILLO ALICIA CARLOTA</t>
-  </si>
-  <si>
-    <t>URBANIZACION COCHAPAMBA DERECHA FRANCISCO MONTALVO CALLEJON B SN</t>
-  </si>
-  <si>
-    <t>VILLAGOMEZ CARRILLO GONZALO MESIAS</t>
-  </si>
-  <si>
-    <t>FRANCISCO MONTALVO 11118 Y LA ROMERIA CASA-OE11-118---- FRANCISCO MONTALVO OE11-118 Y LA ROMERIA</t>
-  </si>
-  <si>
-    <t>FRANCISCO MONTALVO 118 LA ROMERIA CASA----- SECTOR COCHAPAMBA NORTE PORTON NEGRO FRENTE A UNA CASAO AZUL DE DOS PISOS</t>
-  </si>
-  <si>
-    <t>VILLAGOMEZ CARRILLO MARIA FLORA</t>
-  </si>
-  <si>
-    <t>AVENIDA 10 DE AGOSTO N20 98 Y JORGE WASHINGTON EDIFICIO CLUB CASA GRANDE PISO 1 MEZANINE LOCAL 23 EDF CLUB-CASA GRANDE-PISO 1 MEZANINE-LOCAL 23 AVENIDA 10 DE AGOSTO N20</t>
-  </si>
-  <si>
-    <t>DIEGO VACA DE LA VEGA N70 311 RIO PERIPA CASA-2 PISOS COLOR BLANCO---- SECTOR QUITO SUR EN LA CASA QUEDA UNA TIENDA LLAMADA MICRO ALEX</t>
-  </si>
-  <si>
-    <t>VILLEGAS CARRILLO DOILE ALFREDO</t>
-  </si>
-  <si>
-    <t>OBISPO DIAZ DE LA MADRID OE8 186 Y LIZARASU</t>
-  </si>
-  <si>
-    <t>VILLEGAS CARRILLO ENMELY HUMBERTO</t>
-  </si>
-  <si>
-    <t>MULTF VILLA FLORA BL A DEPARTAMENTO 2</t>
-  </si>
-  <si>
-    <t>ALINA VALERIA VALLADARES CARRILLO</t>
-  </si>
-  <si>
-    <t>CALLE 4 8L Y CALLE B EUCALIPTOS EUCALIPTOS</t>
-  </si>
-  <si>
-    <t>ALLAUCA CARRILLO ROSA MELCHORA</t>
-  </si>
-  <si>
-    <t>CALLE 7 1Y Y CALLE D</t>
-  </si>
-  <si>
-    <t>ALULEMA CARRILLO LAUTARO EDUARDO</t>
-  </si>
-  <si>
-    <t>LA GASCA 7MA TRANSVERSAL LOTE 1</t>
-  </si>
-  <si>
-    <t>ALVARADO CARRILLO FAUSTO GIOVANI</t>
-  </si>
-  <si>
-    <t>MARIANO PAREDES OE2-133 MARIANO PONCE SUBIDA AL LA FAB SUIZA SUBIDA AL LA FAB . SUIZA</t>
-  </si>
-  <si>
-    <t>CRLN URBANIZACION CONTRALORIA CALLE N75A Y MARIANO POZO OE2/133 LOTE 104</t>
-  </si>
-  <si>
-    <t>ALVAREZ CARRILLO ELVIA BEATRIZ</t>
-  </si>
-  <si>
-    <t>ANDRES PAREDES 1 Y Y N52D</t>
-  </si>
-  <si>
-    <t>ALVAREZ CARRILLO SOLVEIZ SANTOS</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO ENDARA S24- 51 Y AVENIDA SOLANDA CASA S13114-PASAJE 4 JOSE ANTONIO ENDARA</t>
-  </si>
-  <si>
-    <t>ANA ANGELA AUQUILLAS CARRILLO</t>
-  </si>
-  <si>
-    <t>PASAJE 1 93L Y CALLE B BALCONES FERROVIARIA</t>
-  </si>
-  <si>
-    <t>ANA MARIA CARRILLO</t>
-  </si>
-  <si>
-    <t>PASAJE 8 S21- 2 MZ3 CONJUNTO VENCEDORES DE PICHINCHA</t>
-  </si>
-  <si>
-    <t>ANDAGOYA CARRILLO KEVIN ISMAEL</t>
-  </si>
-  <si>
-    <t>AV MARISCAL SUCRE N53- 129 Y JORGE PIEDRA EDF TORRE PEDREGAL PISO 10 DEPT 1001 TORRE 2 EDF-TORRE PEDREGAL-PISO-10-DEPT-1001 TORRE 2</t>
-  </si>
-  <si>
-    <t>ANDRADE CARRILLO AMPARITO DEL PILAR</t>
-  </si>
-  <si>
-    <t>JUAN BAUTISTA URBANIZACION UNION NACIONAL 67</t>
-  </si>
-  <si>
-    <t>ANDRADE CARRILLO VICTOR OSWALDO</t>
-  </si>
-  <si>
-    <t>ISLA MARCHENA 4128 Y AVENIDA DE LOS GRANADOS EDIFICIO SANTA BARBARA PISO 4 DEPARTAMENTO 409 EDF-SANTA BARBARA-PISO-4-DEPT-409 ISLA MARCHENA</t>
-  </si>
-  <si>
-    <t>ANDRADE CARRILLO VICTOR RAMIRO</t>
-  </si>
-  <si>
-    <t>SAN ISIDRO DEL INCA DE LAS FUCCIAS 689 P3 Y LAS TORONJAS SAN ISIDRO DEL INCA DE LAS FUCCIAS 689</t>
-  </si>
-  <si>
-    <t>DE LAS FUCCIAS 689 Y DE LOS GUABOS DE LAS FUCCIAS</t>
-  </si>
-  <si>
-    <t>ANDRADE CARRILLO XIMENA DE LOURDES</t>
-  </si>
-  <si>
-    <t>AVIGIRAS 1A Y DE LOS GUAYACANES EDIF SETAI 25 CALLE A 1 PISO 3 DEPART. 3 URB.JARDINES DE AMAGASI</t>
-  </si>
-  <si>
-    <t>ANGEL ROBERTO CARRILLO ESCALERAS</t>
-  </si>
-  <si>
-    <t>CARAPUNGO MANZANA A7 CASA 13</t>
-  </si>
-  <si>
-    <t>ANGELICA ALEXANDRA CARRILLO MAYANQUER</t>
-  </si>
-  <si>
-    <t>AV RIO COCA 0 DE LAS HIEDRAS CONDOMINIOS DEL INCA BLOQUE 27 DEP 5A DE LAS HIEDRAS CONDOMINIOS DEL INCA BLOQUE 27 DEP 5A</t>
-  </si>
-  <si>
-    <t>ARAUJO CARRILLO DIEGO RAMIRO</t>
-  </si>
-  <si>
-    <t>AV RIO COCA 0Y Y AV 6 DE DICIEMBRE</t>
-  </si>
-  <si>
-    <t>ARAUJO CARRILLO ANGEL RAFAEL</t>
-  </si>
-  <si>
-    <t>CRLN CONJUNTO ALEGRIA URABA CALLE 3 CASA 14 Y CALLE A</t>
-  </si>
-  <si>
-    <t>ARAUJO CARRILLO ANTONIA MARIA</t>
-  </si>
-  <si>
-    <t>CONDOMINIOS SAN SEBASTIAN DEL NORTE BLOQUE 33 DEPARTAMENTO 4B 4TO PISO</t>
-  </si>
-  <si>
-    <t>ARAUJO CARRILLO DOLORES MERCEDES</t>
-  </si>
-  <si>
-    <t>MANIOSCA 102 Y VERACRUZ MULTF BL D DTO 102 MANIOSCA</t>
-  </si>
-  <si>
-    <t>ARCOS CARRILLO IPATIA MARISOL</t>
-  </si>
-  <si>
-    <t>CALLE OE3K- 0 Y DE LOS CIRUELOS CONT. VALERIA PISO 1 DEPAT. 2 URB LOS ROSALES SECTOR PONCEANO BAJO SECTOR PONCEANO BAJO</t>
-  </si>
-  <si>
-    <t>ARIAS CARRILLO EDIE ROBERTO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ ALCIDES OE2- 20 Y CHASQUI URBANIZACION SANTA ANA PISO 1 DEPARTAMENTO 3 URB-SANTA ANA-PISO-1-DEPT-3 ENRIQUEZ ALCIDES</t>
-  </si>
-  <si>
-    <t>ARTEAGA CARRILLO NORMA MARGARITA</t>
-  </si>
-  <si>
-    <t>MULTF SAN JUAN BL CAYAPAS 5TO P DEPARTAMENTO 502</t>
-  </si>
-  <si>
-    <t>AUQUILLA CARRILLO JOSE RODRIGO</t>
-  </si>
-  <si>
-    <t>CALLE 6 16 Y CALLE K SECTOR ORQUIDEAS DEL SUR CALLE 6</t>
-  </si>
-  <si>
-    <t>AVENIDA PANAMERICANA NORTE 0 TULIPANES Y LAU RELES URBANIZACION CAMINO DE LOS EUCALIPTO S CASA 1138D TULIPANES Y LAU-RELES URB.CAMINO-DE LOS EUCALIPTO-S CASA 1138D</t>
-  </si>
-  <si>
-    <t>BANSHUY CARRILLO FERNANDO</t>
-  </si>
-  <si>
-    <t>CARAPUNGO SECTOR LAS ACACIAS CALLE 2 CASA 10 Y CALLE 1 LE 1</t>
-  </si>
-  <si>
-    <t>BAQUERO CARRILLO AIDA VICTORIA</t>
-  </si>
-  <si>
-    <t>COTOPAXI 377</t>
-  </si>
-  <si>
-    <t>BAQUERO CARRILLO EDISON GONZALO</t>
-  </si>
-  <si>
-    <t>COTOPAXI 377 Y ESMERALDAS</t>
-  </si>
-  <si>
-    <t>BASANTES CARRILLO JAIME RODRIGO</t>
-  </si>
-  <si>
-    <t>0 Y ----- MARISCAL SUCRE CJTO CHILLOGALLO BQ 28 DPT 1C Y DIEGO CESPEDES</t>
-  </si>
-  <si>
-    <t>BASANTEZ CARRILLO JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>ALONSO GOMEZ OE9 189 Y AVENIDA LOS LIBERTADORES COOPERATIVA JOSEFINA ENRIQUEZ SECTOR LA MAGDALENA COOPERATIVA-JOSEFINA-ENRIQUEZ SCT.-LA MAGDALENA ALONSO GOMEZ OE9</t>
-  </si>
-  <si>
-    <t>BATRIZ PATRICIA ALLAUCA CARRILLO</t>
-  </si>
-  <si>
-    <t>CALLE 7 610 Y TERCERA TRANSVERSAL SECT CUTUGLAGUA SECT-CUTUGLAGUA</t>
-  </si>
-  <si>
-    <t>BERNAL CARRILLO IVAN MARCELO</t>
-  </si>
-  <si>
-    <t>NICOLAS URQUIOLA E6 138 Y CORNELIO PEDRO BRRO BONANZA NICOLAS URQUIOLA E6</t>
-  </si>
-  <si>
-    <t>BETANCOURT CARRILLO CARMELA ELENA</t>
-  </si>
-  <si>
-    <t>CIUDADELA TARQUI EX MENA 2 DIEGO MORENO 148 MANZANA B Y A DE CARRANZA</t>
-  </si>
-  <si>
-    <t>BLANCA AMERICA CARRILLO POZO</t>
-  </si>
-  <si>
-    <t>PRIETO 0 Y S23A CASA DE 3 PISOS AZUL POR UNA CANCHA CASA DE 3 PISOS AZUL POR UNA CANCHA S23A</t>
-  </si>
-  <si>
-    <t>BLANCA ESPERANZA CARRILLO SANCHEZ</t>
-  </si>
-  <si>
-    <t>17 DE SEPTIEMBRE 0 Y SIMON BOLIVAR LA PRADERA LLANO CHICO S3-49</t>
-  </si>
-  <si>
-    <t>BOLA�OS CARRILLO NIRIA ANTONIETA</t>
-  </si>
-  <si>
-    <t>PASAJE S9 387 Y DORADO JUAN ----- BARRIO JESUS DEL GRAN PODER</t>
-  </si>
-  <si>
-    <t>BRAVO CARRILLO MARCO ENRIQUE</t>
-  </si>
-  <si>
-    <t>CALLE Q 673 Y CALLE B CALLE Q</t>
-  </si>
-  <si>
-    <t>BRAZALES CARRILLO JEFFERSON RICARDO</t>
-  </si>
-  <si>
-    <t>ECHANIQUE MAURICIO OE10 53 Y JOAQUIN CALDERON SECTOR SAN VICICENTE DE LA FLORIDA SECTOR-SAN VICICENTE-DE LA-FLORIDA ECHANIQUE MAURICIO OE10</t>
-  </si>
-  <si>
-    <t>MACHALA N51 116Y Y LA FLORIDA</t>
-  </si>
-  <si>
-    <t>BUITRON CARRILLO PATRICIA DEL ROCIO</t>
-  </si>
-  <si>
-    <t>BUSTAMANTE EMILIO 130 Y FIGUEROA JUAN BUSTAMANTE EMILIO</t>
-  </si>
-  <si>
-    <t>BUITRON CARRILLO SILVIA GERMANIA</t>
-  </si>
-  <si>
-    <t>EMILIO BUSTAMANTE 130 Y JUAN FIGUEROA EMILIO BUSTAMANTE</t>
-  </si>
-  <si>
-    <t>BUITRON CARRILLO SONIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>EMILIO BUSTAMANTE N64- N64- 28 JUAN FIGUEROA CASA-2 PISOS-PISO-2-- SECTOR COTOCOLLAO, COLOR BLANCO, A LADO DE SASTRERIA</t>
-  </si>
-  <si>
-    <t>BU�AY CARRILLO SEGUNDO PABLO</t>
-  </si>
-  <si>
-    <t>CALLE 22 0 Y Y CALLE G CALLE 22 N57 22 Y CALLE G BARRIO ATUCUCHO</t>
-  </si>
-  <si>
-    <t>BUSTILLOS CARRILLO MARIA HERMINIA GLADYS</t>
-  </si>
-  <si>
-    <t>CIUDADELA SANTA ANITA 2 MANZANA 8 CASA 4</t>
-  </si>
-  <si>
-    <t>CABEZAS CARRILLO NANCY CECILIA</t>
-  </si>
-  <si>
-    <t>CALLE I 0 CASA 24 MANZANA 48 49 CASA 24-MZ 48 49 SECTOR ELOY ALFARO EN LA LOMA DE PUENGASI MONJAS</t>
-  </si>
-  <si>
-    <t>CACERES CARRILLO LUIS RICARDO</t>
-  </si>
-  <si>
-    <t>SOLANDA SECTOR 2 SPMZ 3 MANZANA W PRIMA CASA 5 PASAJE 14</t>
-  </si>
-  <si>
-    <t>CACOANGO CARRILLO MELCHOR</t>
-  </si>
-  <si>
-    <t>CNDO ROLDOS PORVENIR MANZANA 46 CALLE D/7 LOTE 01</t>
-  </si>
-  <si>
-    <t>CADENA CARRILLO LID MARIA</t>
-  </si>
-  <si>
-    <t>FRANCISCO JIMENEZ 182</t>
-  </si>
-  <si>
-    <t>CAHUE�AS CARRILLO LUCIA</t>
-  </si>
-  <si>
-    <t>JULIO ARELLANO E 5176 Y DE LOS LIRIOS</t>
-  </si>
-  <si>
-    <t>CAICEDO CARRILLO CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>BALLESTEROS Y JIPIJAPA</t>
-  </si>
-  <si>
-    <t>CAICEDO CARRILLO PATRIA AMADA</t>
-  </si>
-  <si>
-    <t>INIAQUITO LA FLORIDA FRAY AGUSTIN LEON 114 Y AMALIA EGUIGUREN INIAQUITO LA FLORIDA FRAY AGUSTIN LEON</t>
-  </si>
-  <si>
-    <t>CAIZALUISA CARRILLO TRANCITO ALICIA</t>
-  </si>
-  <si>
-    <t>CALLE K 70 Y CALLE D CALLE K</t>
-  </si>
-  <si>
-    <t>CALLE E6 74 -65 ANTONIO BASANTES -65 ANTONIO-BASANTES</t>
-  </si>
-  <si>
-    <t>CALDERON CARRILLO CARMEN CELIA</t>
-  </si>
-  <si>
-    <t>CARCELEN SMZC MZ23 C8</t>
-  </si>
-  <si>
-    <t>CALVOPI�A CARRILLO SUSANA ESTELA</t>
-  </si>
-  <si>
-    <t>LULUNCOTO BAJO DR C SANCHEZ 108 Y F LOPEZ LULUNCOTO BAJO DR C SANCHEZ</t>
-  </si>
-  <si>
-    <t>CAMACHO CARRILLO ANGEL ELICIO</t>
-  </si>
-  <si>
-    <t>CALLE D 0 L Y CALLE B CALLE D 10L Y CALLE B PUEBLO UNIDO</t>
-  </si>
-  <si>
-    <t>CAMPA�A CARRILLO ADRIANA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>JUAN MOLINEROS 0 Y DE LO GUAYACANES REF. CASA ESQ. SECT COMITE DEL PUEBLO</t>
-  </si>
-  <si>
-    <t>CARANQUI CARRILLO DOLORES ALVINA</t>
-  </si>
-  <si>
-    <t>CALLE 12 990 Y CALLE A CUTUGLAGUA//CASA DE UN PISO COLOR CELESTE CUTUGLAGUA//CASA DE UN PISO COLOR CELESTE</t>
-  </si>
-  <si>
-    <t>CARLA CAROLINA CARRILLO GORTAIRE</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL CARRION 0 Y AV. MARISCAL SUCRE JOSE MIGUEL CARRION 0Y Y AV MARISCAL SUCRE TORRES DEL CONDADO 4 PISO DEP 401</t>
-  </si>
-  <si>
-    <t>CARLOS VINICIO CARRILLOGALLEGOS</t>
-  </si>
-  <si>
-    <t>GONZALO PEREZ BUSTAMANTE 155 S Y AURELIO GUERRERO maldonado y simon bolivar casa 155// SOLO LINEA maldonado y simon bolivar casa 155// SOLO LINEA AURELIO GUERRERO</t>
-  </si>
-  <si>
-    <t>CARMEN ALICIA BUSTILLOS CARRILLO</t>
-  </si>
-  <si>
-    <t>CIUDADELA GATAZO CALLE MULALILLO LOTE 10 Y CHUMUNDE</t>
-  </si>
-  <si>
-    <t>CARMEN LUCIA CARRILLO</t>
-  </si>
-  <si>
-    <t>QC AVENIDA GRAN COLOMBIA 220 P3 OFICINA 301</t>
-  </si>
-  <si>
-    <t>CAROLINA YOFIRE CARRILLO CASTA�EDA</t>
-  </si>
-  <si>
-    <t>DE LOS JAZMINES N57 78 Y FRAY LEONARDO MURIALDO SCTR CALIFORNIA ALTA CTR CALIFORNIA ALTA</t>
-  </si>
-  <si>
-    <t>CARRANZA CARRILLO JUAN</t>
-  </si>
-  <si>
-    <t>MIGUEL DE LA ROSA OE2 0Y Y FRANCISCO SANCHES</t>
-  </si>
-  <si>
-    <t>ANCHAPAXI CARRILLO EDWIN PATRICIO</t>
-  </si>
-  <si>
-    <t>BRR CHAUPI MOLINO CLL. QUITO 2 PASAJE BALDEON EGAS PLAN DE VIVIENDA CASA 2 SECT PIFO</t>
-  </si>
-  <si>
-    <t>PUEMBO</t>
-  </si>
-  <si>
-    <t>RUIZ CARRILLO GUILLERMO VIRGILIO</t>
-  </si>
-  <si>
-    <t>AVENIDA CORDOVA GALARZA 0 CONJUNTO DOS HEMISFERIOS MANZANA 4 CASA 13 CONJUNTO-DOS HEMISFERIOS-MZ-4-CASA-13</t>
-  </si>
-  <si>
-    <t>ANCHAPAXI CARRILLO GLORIA ESPERANZA</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL DELGADO 0Y Y GONZALO PIZARRO S1-48 // A LADO DE SUPERMERCADO VIRGEN DEL QUINCHE</t>
-  </si>
-  <si>
-    <t>ANCHAPAXI CARRILLO OLGA MARINA</t>
-  </si>
-  <si>
-    <t>CENTRAL PIFO CALLE IGNACIO J MERA SN Y TULIO GARZON</t>
-  </si>
-  <si>
-    <t>LA CONDAMINE 91L Y PIFO URB WILSON CERCA DEL BRR ANDRANGO URB WILSON CERCA DEL BRR ANDRANGO</t>
-  </si>
-  <si>
-    <t>RUBEN DARIO CARRILLO SALAS</t>
-  </si>
-  <si>
-    <t>URB ALTOS DEL VALLE 0 Y Y AV. INTEROCEANICA AV. INTEROCEANICA</t>
-  </si>
-  <si>
-    <t>ALVAREZ CARRILLO HECTOR OSWALDO</t>
-  </si>
-  <si>
-    <t>CALLE A 2L Y AVENIDA FERNANDEZ SALVADOR ENTRADA A PINLLO CRUZ CASA AMARILLA 2PISOS ENTRADA A PINLLO-CRUZ-CASA AMARILLA-2PISOS PINLLOCRUZ</t>
-  </si>
-  <si>
-    <t>MACHACHI</t>
-  </si>
-  <si>
-    <t>ANGELA CRISTINA TENEMASA CARRILLO</t>
-  </si>
-  <si>
-    <t>CALLE P 0 Y CALLE SIN NOMBRE CASA 06-74 CUTUGLAGUA CASA 06-74-CUTUGLAGUA</t>
-  </si>
-  <si>
-    <t>CADENA CARRILLO MARCELO EDUARDO</t>
-  </si>
-  <si>
-    <t>CRISTOBAL COLON 2 Y PRINCESA TOA</t>
-  </si>
-  <si>
-    <t>CARLOS RENE PEREZ CARRILLO</t>
-  </si>
-  <si>
-    <t>LA TAMPA 0Y Y LOS JADES DIAGIONAL A LA FABRICA DE TE PUERTAS NEGRAS DIAGIONAL A LA FABRICA DE TE PUERTAS NEGRAS</t>
-  </si>
-  <si>
-    <t>LAS GOLONDRINAS</t>
-  </si>
-  <si>
-    <t>BASANTES CARRILLO FLOR ELIZABETH</t>
-  </si>
-  <si>
-    <t>LOS PINOS 0 Y Y AVENIDA CORONEL EDMUNDO ANDRADE - - AVENIDA CORONEL EDMUNDO ANDRADE</t>
-  </si>
-  <si>
-    <t>CADENA CARRILLO JOSE JUAN</t>
-  </si>
-  <si>
-    <t>CATACOCHA 21 Y BIBLIAN BARRIO UNIFICADOS BARRIO-UNIFICADOS CATACOCHA</t>
-  </si>
-  <si>
-    <t>CADENA CARRILLO ROSA ELENA</t>
-  </si>
-  <si>
-    <t>CALLE 1 0 Y Y AVENIDA DEL COOPERATIVISMO - - AVENIDA DEL COOPERATIVISMO</t>
-  </si>
-  <si>
-    <t>ANCHAPAXI CARRILLO ROSARIO DEL PILAR</t>
-  </si>
-  <si>
-    <t>MANABI 97 Y INTEROCEANICA</t>
-  </si>
-  <si>
-    <t>EL QUINCHE</t>
-  </si>
-  <si>
-    <t>URUPAMBA 10L COOPERATIVA HUERTOS FAM ILIARES 23 DE ENERO EL QUINCHE COOP HUERTOS FAM-ILIARES 23 DE-ENERO EL-QUINCHE CASA CON CERRAMIENTO DE BLOQUE PORTON VERDE</t>
-  </si>
-  <si>
-    <t>ANA MAGDALENA JARA CARRILLO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL 0L Y LEONARDO DA VINCI TORRE B 003B</t>
-  </si>
-  <si>
-    <t>ANDRADE CARRILLO LUCIA ESPERANZA</t>
-  </si>
-  <si>
-    <t>CUMBAYA VIA INTEROCEANICA KILOMETRO 10 1/2 CASA S/N</t>
-  </si>
-  <si>
-    <t>PRIMAVERA 2 CALLE 6 NR 269 Y CALLE 7 PRIMAVERA 2 CALLE 6 NR</t>
-  </si>
-  <si>
-    <t>BERNAL CARRILLO JOSE RODOLFO</t>
-  </si>
-  <si>
-    <t>SAGITARIO 14 Y CUARTA TRANSVERSAL MANZANA F TERRANOVA MZ F-TERRANOVA SAGITARIO</t>
-  </si>
-  <si>
-    <t>CALLE E 89L Y CALLE U MIGUEL DE SANTIA GO N10-807 Y B MIGUEL DE SANTIA-GO N10-807 Y B SECOTR PUENTE 4</t>
-  </si>
-  <si>
-    <t>VIZCARRA CARRILLO MARCIA FANNY</t>
-  </si>
-  <si>
-    <t>AVENIDA JAIME ROLDOS AGUILERA N4 67 LUIS CORDERO CASA TOMATE CERRAMIENTO DE CEM CASA-TOMATE CERRAMIENTO DE CEM---- ENTRADA A LA CIUDAD DEL NI�O FRENTE A CANCHAS</t>
-  </si>
-  <si>
-    <t>VILLAFUERTE CARRILLO BRYAN PATRICIO</t>
-  </si>
-  <si>
-    <t>ERNESTO VACA 0 CALLE L5 URB JARDIN DE CO NOCOTO . CALLE L5-URB JARDIN DE CO-NOCOTO-.</t>
-  </si>
-  <si>
-    <t>ANA GABRIELA SANTAMARIA CARRILLO</t>
-  </si>
-  <si>
-    <t>AV. LOLA QUINTANA N9- 13 CND ROSVAL LOTE 16 CND-ROSVAL LOTE 16</t>
-  </si>
-  <si>
-    <t>ARIAS CARRILLO ROBERTO LEOPOLDO</t>
-  </si>
-  <si>
-    <t>CONOCOTO BARRIO NUEVO HORIZONTE AVENIDA LOLA QUINTANA 1855</t>
-  </si>
-  <si>
-    <t>AYALA CARRILLO EDUARDO VINICIO</t>
-  </si>
-  <si>
-    <t>ALBERTO ACOSTA SOBERON 0Y Y ALFONSO PEREZ PALLARES URB CAMPANI 2 CASA 19 URB-CAMPANI 2-CASA-19</t>
-  </si>
-  <si>
-    <t>BLANCA NANCY CARRILLO ORTIZ</t>
-  </si>
-  <si>
-    <t>BENALCAZAR 0 Y RICARDO DESCALZI CND VILLA LINDA CASA 4 LA ARMENIA 2 CND-VILLA LINDA-CASA-4 LA ARMENIA 2</t>
-  </si>
-  <si>
-    <t>BORJA CARRILLO LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>PONCE ENRIQUEZ 3340 Y PASAJE PAQUILLA URBANIZACION LA LUZ CAMILO PONCE ENRIQUEZ 3340 URB-LA LUZ PONCE ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CADENA CARRILLO JENNY PATRICIA</t>
-  </si>
-  <si>
-    <t>SEBASTIAN DE BENALCAZAR 0 CONOCOTO LA ARMENIA SECTOR CORNEJO BAJO FRENTE AL POLICI MEDIO AMBIENTE CONOCOTO LA-ARMENIA-SECTOR CORNEJO-BAJO-FRENTE AL POLICI-MEDIO AMBIENTE LA ARMENIA VIA GUANGOPOLO</t>
-  </si>
-  <si>
-    <t>CA�IZARES CARRILLO MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>AVENIDA SAN PEDRO TOBOADA 43 CJUNTO ZENDRA CASA N� 2 SECTOR CONOCOTO CJUNTO ZENDRA-CASA N� 2</t>
-  </si>
-  <si>
-    <t>WAGNER ALEJANDRO AZACATA CARRILLO</t>
-  </si>
-  <si>
-    <t>ARENAL 0 CONDOMINIO CASALES BUENAVENTURA 2DA ETAPA CASA 168 CND CASALES-BUENAVENTURA-2DA ETAPA-CASA 168</t>
-  </si>
-  <si>
-    <t>VILLARREAL CARRILLO GRINKA ELENA</t>
-  </si>
-  <si>
-    <t>23 DE ABRIL 0 Y 25 DE NOVIEMBRE CTO LLANO DORADO CASA 18 CTO LLANO DORADO-CASA 18 23 DE ABRIL</t>
-  </si>
-  <si>
-    <t>ALOBUELA CARRILLO LIZ ALEJANDRA</t>
-  </si>
-  <si>
-    <t>PACHA 0 LUISA GOMEZ CASA DE 2 PISOS FRENTE A CANCHAS URB CASA TUYA AS URB CASA TUYA</t>
-  </si>
-  <si>
-    <t>CARAN 0 Y 9 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>CALDERON CALLE CARAN S/N Y 9 DE AGOSTO CALDERON CALLE CARAN</t>
-  </si>
-  <si>
-    <t>AZACATA CARRILLO LILIANA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CALDERON BARRIO CHUROLOMA VIA MARIANAS CASA 26 Y CARA</t>
-  </si>
-  <si>
-    <t>ANASI CARRILLO JOSE LUIS</t>
-  </si>
-  <si>
-    <t>III TRANSVERSAL 0 L Y ISIDRO AYORA AMAGUA�A AMAGUA�A ISIDRO AYORA</t>
+    <t>ARMANDO ERNESTO DAVILA VERA</t>
+  </si>
+  <si>
+    <t>VIA A PAMPLONA 0Y Y BARRIO CENTRAL CASA DE MADERA UN PISO CASA DE MADERA UN PISO</t>
+  </si>
+  <si>
+    <t>SELVA ALEGRE IMBABURA</t>
+  </si>
+  <si>
+    <t>FAUSTO GERMAN HINOJOSA DAVILA</t>
+  </si>
+  <si>
+    <t>CHIRIBOGA 0 Y CALDERON CHIRIBOGA</t>
+  </si>
+  <si>
+    <t>SAN PABLO</t>
+  </si>
+  <si>
+    <t>MARIO GUILLERMO DAVILA BAQUERIZO</t>
+  </si>
+  <si>
+    <t>PRINCESA CORY 0 Y PRINCESA PACCHA</t>
+  </si>
+  <si>
+    <t>SAN LUIS DE CARANQUI</t>
+  </si>
+  <si>
+    <t>HERRERA DAVILA GERMAN ATAHUALPA</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL SANSHIPANDA 0 Y VIA SAN VICENTE ----- CALLE PRINCIPAL SANSHIPANDA</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DE SIGSIPAMBA</t>
+  </si>
+  <si>
+    <t>ALMEIDA DAVILA LUIS RAUL</t>
+  </si>
+  <si>
+    <t>HERMANOS MIDEROS 0 Y SIMON BOLIVAR SECT SAN ANTONIO DE IBARRA.</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO DE IBARRA</t>
+  </si>
+  <si>
+    <t>ARAUJO DAVILA CLEMENCIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>POMPILLO MIDEROS 200 Y VENEZUELA CERRAMIENTO DE LADRILLO CIUDADELA GUSTAVO PAREJA DRILLO CIUDADELA GUSTAVO PAREJA</t>
+  </si>
+  <si>
+    <t>DAVILA RIVADENEIRA PATRICIA SILVANA</t>
+  </si>
+  <si>
+    <t>27 DE NOVIEMBRE 187 0 Y PANAMERICANA SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>DAVILA TENA CARLOS HUMBERTO ARMANDO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE CEVALLOS SN 562 CASA2 PISOS BEIGE CASA-2 PISOS BEIGE---- SECTOR SAN ANTONIO DE IBARRA FRENTE AL PARQUE FRANCISCO CALD</t>
+  </si>
+  <si>
+    <t>CARVALLO DAVILA PATRICIA YASMIN</t>
+  </si>
+  <si>
+    <t>MARCO NICOLALDE 0 Y JORGE SUBIA</t>
+  </si>
+  <si>
+    <t>PUGACHO</t>
+  </si>
+  <si>
+    <t>ORQUERA DAVILA MARIA LEONOR</t>
+  </si>
+  <si>
+    <t>MANUELITA SAENZ 0 Y LOS GALEANOS CASA 1P BLANCA FRENTE TIENDA CASA 1P BLANCA-FRENTE TIENDA</t>
+  </si>
+  <si>
+    <t>CORTEZ DAVILA JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>MONTUFAR 0 Y SUCRE TRAS LOS BA�OS MUNICIPALES FRENTE AL MOTOR DE CNT MONTUFAR</t>
+  </si>
+  <si>
+    <t>PIMAMPIRO</t>
+  </si>
+  <si>
+    <t>CORTEZ DAVILA RODRIGO FILIMON</t>
+  </si>
+  <si>
+    <t>ESPEJO 3100 Y PAQUISHA BARRIIO SAN VICENTE BARRIIO-SAN VICENTE ESPEJO</t>
+  </si>
+  <si>
+    <t>DARWIN RAFAEL NAVAS DAVILA</t>
+  </si>
+  <si>
+    <t>SECTOR SAGALAPAMBA 0 Y CALLE SIN MOMBRE FRENTE AL PARQUE</t>
+  </si>
+  <si>
+    <t>PE�AHERRERA</t>
+  </si>
+  <si>
+    <t>DAVILA PIEDRA CARLA ABIGAIL</t>
+  </si>
+  <si>
+    <t>PE�AHERRERA CALLE PRINCIPAL 0 Y PLAZA PRINCIPAL PLAZA 24 DE MAYO</t>
+  </si>
+  <si>
+    <t>CALLE 0 Y CALLE SIN MOMBRE CASA 1 PISO CELESTE PLAZA 24 DE MAYO CASA-1 PISO CELESTE PLAZA 24 DE MAYO</t>
+  </si>
+  <si>
+    <t>EDISSON PATRICIO DAVILA SUAREZ</t>
+  </si>
+  <si>
+    <t>ZONA INTAG PE�AHERRERA 0 SCT. LA PLAZA FTE A LA IGLESIA VILLA PLOMO C/ CAFE</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA DIANA RAQUEL</t>
+  </si>
+  <si>
+    <t>MARIA ANGELICA HIDROVO 151 Y LUIS ENRIQUE CISNEROS MARIA ANGELICA HIDROVO</t>
+  </si>
+  <si>
+    <t>OTAVALO</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA SIXTO TARQUINO</t>
+  </si>
+  <si>
+    <t>OTAVALO IMBAYA LUIS ARCE 131</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA XIMENA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>VICTOR GARCES 0 Y CALLE "G"</t>
+  </si>
+  <si>
+    <t>ANGULO DAVILA NATALIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>CORAZAS 0Y Y PEDRO HERNANDEZ DE LA REINA</t>
+  </si>
+  <si>
+    <t>BURBANO DAVILA PATRICIO AUGUST</t>
+  </si>
+  <si>
+    <t>AV LOS SARANCES 507 Y YAMOR CERRAMIENTO BLANCO CASA 3 PISOS</t>
+  </si>
+  <si>
+    <t>DAVILA ALVEAR MARCIA IRENE</t>
+  </si>
+  <si>
+    <t>BARRIO SAN JUAN SN</t>
+  </si>
+  <si>
+    <t>DAVILA CISNEROS MYRIAN SUSANA</t>
+  </si>
+  <si>
+    <t>CALLE A 49 Y SEBASTIAN MANRIQUE CASA-580 ESQUINA CALLE A</t>
+  </si>
+  <si>
+    <t>DAVILA ENDARA GLORIA MARIA</t>
+  </si>
+  <si>
+    <t>OTAVALO SUCRE 917</t>
+  </si>
+  <si>
+    <t>DAVILA FANNY FANNY ETELVINA</t>
+  </si>
+  <si>
+    <t>OTAVALO GARCIA MORENO 608</t>
+  </si>
+  <si>
+    <t>DAVILA MALDONADO JOSE IVAN</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO DE LA TORRE 0 Y Y CALLE BARR MOSERRAT</t>
+  </si>
+  <si>
+    <t>DAVILA ORBE CESAR HERNAN</t>
+  </si>
+  <si>
+    <t>SUCRE 1005 Y ABDON CALDERON BARRIO SAN LUIS BARRIO-SAN LUIS SUCRE</t>
+  </si>
+  <si>
+    <t>DAVILA ORTIZ YOLANDA ROCIO</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL S/N 68 Y VIA A LA CIUDADELA IMBAYA URBANIZACION MARIA JOSE URBANIZACION-MARIA JOSE CALLE PRINCIPAL S/N</t>
+  </si>
+  <si>
+    <t>DAVILA POSSO DORA LIBERTAD</t>
+  </si>
+  <si>
+    <t>CIUDADELA IMBAYA MANZANA N CASA 13</t>
+  </si>
+  <si>
+    <t>DAVILA ROSERO OLIVER RICARDO</t>
+  </si>
+  <si>
+    <t>AV QUITO 15 Y JACINTO COLLAHUASO URB PRADOS DE PASTAVI HACIENDO DEL AVION JUNTO A LA HACIENDA PASTAVI PASTAVI</t>
+  </si>
+  <si>
+    <t>DAVILA SILVA CARLOS STALIN</t>
+  </si>
+  <si>
+    <t>SUCRE 784 Y MIGUEL EGAS SUCRE</t>
+  </si>
+  <si>
+    <t>DAVILA SILVA MARCO ALFONSO</t>
+  </si>
+  <si>
+    <t>SUCRE 314N Y OLMEDO CASA 1P BLOQUE TRAS CEMENTER CASA-1P BLOQUE TRAS CEMENTER</t>
+  </si>
+  <si>
+    <t>DAVILA TENA FLOR MARIA</t>
+  </si>
+  <si>
+    <t>ESTUARDO JARAMILLO 0 Y VICTOR GARCIA GARCES</t>
+  </si>
+  <si>
+    <t>DAVILA TENA LILIANA TERESA</t>
+  </si>
+  <si>
+    <t>CESAR DAVILA GUERRA 0 Y ALBERTO SUAREZ DAVILA CDLA RUMI�AHUI/MIGRACION A GPON/ COSTO DE INSTALACION CDLA RUMI�AHUI/MIGRACION A GPON/ COSTO DE INSTALACION ALBERTO SUAREZ DAVILA</t>
+  </si>
+  <si>
+    <t>DINA EULALIA DAVILA ALVEAR</t>
+  </si>
+  <si>
+    <t>SINCHICO ANTONIO 334 Y ESTEBAN PERALTA UNA CUADRA ANTES DEL ESTADIO UNA CUADRA ANTES DEL ESTADIO</t>
+  </si>
+  <si>
+    <t>FLOR MARIA DAVILA TENA</t>
+  </si>
+  <si>
+    <t>LUIS GARZON PRADO 0 Y ESTUARDO JARAMILLO PEREZ casa verde de un piso casa verde de un piso ESTUARDO JARAMILLO PEREZ</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER ZEA DAVILA</t>
+  </si>
+  <si>
+    <t>BOLIVAR 1114 Y -- SALINAS</t>
+  </si>
+  <si>
+    <t>GALARZA DAVILA JOAQUIN ANIBAL</t>
+  </si>
+  <si>
+    <t>MORALES 505 Y SUCRE MORALES</t>
+  </si>
+  <si>
+    <t>GALARZA DAVILA LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>OTAVALO AVENIDA LOS CORAZAS 125</t>
+  </si>
+  <si>
+    <t>GALO ALEJANDRO PLAZAS DAVILA</t>
+  </si>
+  <si>
+    <t>VALLE DEL TAMBO 0 Y PANAMERICANA CONJUNTO SAN FRANCISCO /MIGRACION LINEA + INTERNET CONJUNTO SAN FRANCISCO /MIGRACION LINEA + INTERNET PANAMERICANA</t>
+  </si>
+  <si>
+    <t>HERMAN ALFREDO DAVILA PINTO</t>
+  </si>
+  <si>
+    <t>JUAN AGUILAR 0 Y LUIS CHAVEZ GUERRERO FRENTE IGLESIA SAN VICENTE FRENTE IGLESIA SAN VICENTE LUIS CHAVEZ GUERRERO</t>
+  </si>
+  <si>
+    <t>HILDA ELOIZA PAREDES DAVILA</t>
+  </si>
+  <si>
+    <t>OTAVALO BOLIVAR 708 Y J MONTALVO OTAVALO BOLIVAR</t>
+  </si>
+  <si>
+    <t>MARIA ELENA PUENTE DAVILA</t>
+  </si>
+  <si>
+    <t>ATAHUALPA 0Y Y COLLAHUAZO JUNTO EMPRESA ELECTRICA</t>
+  </si>
+  <si>
+    <t>ALEXANDRA MARCELA DAVILA CIFUENTES</t>
+  </si>
+  <si>
+    <t>LOS GALEANOS 0 Y LAS GARDENIAS CONJUNTO NUEVA ESPERANZA CASA H1 CONJUNTO NUEVA ESPERANZA CASA H1 LAS GARDENIAS</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>ALODIA MARGOTH ARAUJO DAVILA</t>
+  </si>
+  <si>
+    <t>AV EL RETORNO 0 Y QUILAGO QUILAGO</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL DAVILA HERRERA</t>
+  </si>
+  <si>
+    <t>VIA AL ESTADIO 0 Y --- ESTADIO OLIMPICO VIA AL ESTADIO</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA OSWART JAVIER</t>
+  </si>
+  <si>
+    <t>JUAN DE LA ROCA 0 Y AVENIDA RICARDO SANCHEZ CASA 4 ATRAS DEL 911 CASA 4 ATRAS DEL 911 AVENIDA RICARDO SANCHEZ</t>
+  </si>
+  <si>
+    <t>IMBABURA PARROQ CUELLAJE CERCA PARQUE</t>
+  </si>
+  <si>
+    <t>BARAHONA DAVILA NELLY PATRICIA</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA LA VICTORIA MARCO TULIO NIETO SN</t>
+  </si>
+  <si>
+    <t>CADENA DAVILA FABRICIO ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAMON ALARCON 0 Y AV. JAIME ROLDOS AGUILERA AV. JAIME ROLDOS AGUILERA</t>
+  </si>
+  <si>
+    <t>CARMELA GORDILLO DAVILA</t>
+  </si>
+  <si>
+    <t>IBARRA ROCAFUERTE 14175</t>
+  </si>
+  <si>
+    <t>CARMEN ARCELIA ARAUJO DAVILA</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO JARAMILLO 0 Y 7 DE AGOSTO SUC IMB/474/ CERRAMIENTO DE MALLA SUC IMB/474/ CERRAMIENTO DE MALLA 7 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>CERON DAVILA JEFERSON ALEXIS</t>
+  </si>
+  <si>
+    <t>PARROQUIA PE�AHERRERA FRENTE AL ESTADIO 0Y Y SAGALAPAMBA SECTOR PE�AHERRERA/BARRIO SAGALAPAMBA/ FRENTE A CABA�ANAS MONSERRAT/CASA DE BLOQUE VISTO P1</t>
+  </si>
+  <si>
+    <t>CHIRIBOGA DAVILA SERGIO BOLIVAR</t>
+  </si>
+  <si>
+    <t>CHILE 275 Y BOLIVIA CASA GRIS CASA-GRIS DEL HOSPITAL DEL SEGURO CUATRO CUADRAS AL SUR, CASA 2 PISOS COLOR GRIS /ROJO</t>
+  </si>
+  <si>
+    <t>DAVILA AGUIRRE MARIA AUGUSTA</t>
+  </si>
+  <si>
+    <t>OBISPO LUIS PEREZ CALDERON 0 Y VICENTE ROCAFUERTE</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE LEONOR MAGDALENA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>IBARRA AVENIDA ELOY ALFARO 103</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE MERCEDES CECILIA DE LOS DOLORES</t>
+  </si>
+  <si>
+    <t>ALFARO ELOY 103 Y RODRIGUEZ CASA 103 CASA-103 ALFARO ELOY</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE NELSON ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN FRANCISCO BONILLA 740 Y AVENIDA ATAHUALPA SECTOR YACUCALLE SECTOR-YACUCALLE JUAN FRANCISCO BONILLA</t>
+  </si>
+  <si>
+    <t>DAVILA BAQUERIZO BYRON LEONARDO</t>
+  </si>
+  <si>
+    <t>MALDONADO 0 502 BOSURCO 502-BOSURCO 3RE PISO SECTOR SAN MARTIN</t>
+  </si>
+  <si>
+    <t>DAVILA BELTRAN LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>IBARRA OVIEDO 933 Y SANCHEZ Y CIFUENTES IBARRA OVIEDO</t>
+  </si>
+  <si>
+    <t>DAVILA BENAVIDES BLANCA LUCIA</t>
+  </si>
+  <si>
+    <t>PEDRO V MALDONADO 627</t>
+  </si>
+  <si>
+    <t>DAVILA BENAVIDES ROMMEL RICARDO</t>
+  </si>
+  <si>
+    <t>MALDONADO 627 Y GRIJALVA CASA 1P BALNCO Y CAFE CASA-1P BALNCO Y CAFE</t>
+  </si>
+  <si>
+    <t>DAVILA CARRERA LUIS ANIBAL</t>
+  </si>
+  <si>
+    <t>MEJIA 341 Y ROCAFUERTE</t>
+  </si>
+  <si>
+    <t>DAVILA DAVILA JUDITH MAGDALENA</t>
+  </si>
+  <si>
+    <t>JACINTO EGAS 481 Y CARLOS EMILIO GRIJALVA</t>
+  </si>
+  <si>
+    <t>DAVILA ESPINOSA RELICARIO DE ROMA</t>
+  </si>
+  <si>
+    <t>IBARRA OLMEDO 221 Y R TROYA IBARRA OLMEDO</t>
+  </si>
+  <si>
+    <t>DAVILA FLORES MILTON HONORATO</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA LA VICTORIA MZNA 19 CASA 19</t>
+  </si>
+  <si>
+    <t>DAVILA GONZALEZ NALDA MARISOL</t>
+  </si>
+  <si>
+    <t>AVENIDA PEREZ GUERRERO 650 Y BOLIVAR AVENIDA PEREZ GUERRERO</t>
+  </si>
+  <si>
+    <t>DAVILA GUZMAN EDWIN RODRIGO</t>
+  </si>
+  <si>
+    <t>BOLIVAR 887 Y VELASCO BOLIVAR</t>
+  </si>
+  <si>
+    <t>DAVILA HERRERA LUIS HERIBERTO VIDALIN</t>
+  </si>
+  <si>
+    <t>PE�AHERRERA 0 Y PARQUE CENTRAL CASA 1 PISO CELESTE A MEDIA CUADR DEL PARQUE CASA-1 PISO CELESTE A MEDIA CUADR DEL PARQUE</t>
+  </si>
+  <si>
+    <t>DAVILA HOLGUIN CARLOS AMADOR</t>
+  </si>
+  <si>
+    <t>BOLIVAR 679 Y OVIEDO EDIFICIO RUEDA 3ER PISO OFICIANA 109 EDIFICIO RUEDA-3ER PISO-OFICIANA-109</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA JARDIN ELIAS ALMEIDA 992 Y JUAN G JARAMILLO JARAMILLO</t>
+  </si>
+  <si>
+    <t>CARLOS ELIAS ALMEIDA 992 Y JUAN G JARAMILLO SECTOR CDLA EL JARDIN</t>
+  </si>
+  <si>
+    <t>DAVILA MALDONADO JORGE RAUL</t>
+  </si>
+  <si>
+    <t>PABLO VELA 518 Y CARLOS VILLACIS URBANIZACION NUEVO HOGAR URBANIZACION-NUEVO HOGAR CASA1PISO BLANCA IBARRA SCT AEROPUERTO DE LA IGLESIA A 100 MTROS</t>
+  </si>
+  <si>
+    <t>AVENIDA CAMILO PONCE ENRIQUE 0 Y CARLOS EMILIO GRIJALVA ESQUINA</t>
+  </si>
+  <si>
+    <t>DAVILA MONGE JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>IBARRA AVENIDA PEREZ GUERRERO 784</t>
+  </si>
+  <si>
+    <t>DAVILA MONTUFAR MARIA LUCRECIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>IBARRA LA VICTORIA SEDA ETP MANZANA 22 CASA 418</t>
+  </si>
+  <si>
+    <t>DAVILA MORENO SILVANA MARIA</t>
+  </si>
+  <si>
+    <t>AVENIDA RICARDO SANCHEZ 825 Y SANCHEZ Y CIFUENTES PISO-3 AVENIDA RICARDO SANCHEZ</t>
+  </si>
+  <si>
+    <t>DAVILA NAVARRETE LUIS DAVID</t>
+  </si>
+  <si>
+    <t>IMBABURA PENAHERRERA PAR PRINCIPAL</t>
+  </si>
+  <si>
+    <t>DAVILA ONA SUSANA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>SUCRE 1860 Y CARLOS EMILIO GRIJALVA TRAS EL ACROPOLIS TRAS EL-ACROPOLIS SUCRE</t>
+  </si>
+  <si>
+    <t>DAVILA OTERO MATILDE NOHEMI</t>
+  </si>
+  <si>
+    <t>PASAJE 5 SN 8 RIO QUILAGO CONJUNTO EL RETORNO MANZANA6B CASAAMARILLO 3 PISO CJTO-EL RETORNO-MZ-6B-CASA-AMARILLO 3 PS SECTOR EL RETORNO 2 CUADRAS ESCUELA TERESA VACQ</t>
+  </si>
+  <si>
+    <t>DAVILA PANTOJA MARIA JOSE</t>
+  </si>
+  <si>
+    <t>GENERAL MIHI 2 Y AV EL RETORNO CASA 2 PISOS COLOR BEIGE Y PLOMO SECTOR LA CANDELARIA CASA-2 PISOS COLOR BEIGE</t>
+  </si>
+  <si>
+    <t>DAVILA PAREDES MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>LUCILA BENALCAZAR 248 Y JOSE MIGUEL LEORO LUCILA BENALCAZAR</t>
+  </si>
+  <si>
+    <t>DAVILA PAREDES SEGUNDO MARCELO</t>
+  </si>
+  <si>
+    <t>DARIO EGAS GRIJALVA 0 Y Y OBISPO PASQUEL MONJE DARIO EGAS 0 Y OBISPO PASQUEL MONJE</t>
+  </si>
+  <si>
+    <t>DAVILA RIVADENEIRA NIDIA MARCELA</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y OVIEDO LOCAL 1 EDIFICIO WAY LOCAL-1 BOLIVAR</t>
+  </si>
+  <si>
+    <t>DAVILA RODAS FAUSTO XAVIER</t>
+  </si>
+  <si>
+    <t>ELEODORO AYALA 1106 Y CRISTOBAL GOMEZ JURADO</t>
+  </si>
+  <si>
+    <t>DAVILA RODAS MARIA ELENA</t>
+  </si>
+  <si>
+    <t>AVENIDA ATAHUALPA 14136 Y JOSE MIGUEL LEORO AVENIDA ATAHUALPA</t>
+  </si>
+  <si>
+    <t>DAVILA ROSALES JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL SANTIAGO DEL REY 0 CASA 1 PISO COLOR BLANCA CASA-1 PISO COLOR BLANCA</t>
+  </si>
+  <si>
+    <t>DAVILA SAA JOSE IGNACIO</t>
+  </si>
+  <si>
+    <t>MIGUEL OVIEDO 933 Y CHICA NARVAEZ MIGUEL OVIEDO</t>
+  </si>
+  <si>
+    <t>OVIEDO 935</t>
+  </si>
+  <si>
+    <t>DAVILA SALAZAR LIVIA ELENA</t>
+  </si>
+  <si>
+    <t>RIO AGUARICO 666 Y RIO CHIMBO CASA 2P AMARILLA CASA-2P AMARILLA FRENTE HUERTO DE LIMONES</t>
+  </si>
+  <si>
+    <t>DAVILA SALAZAR MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>MALDONADO 1741 Y JUAN FRANCISCO BONILLA CASA 3 PISOS COLOR CASA 3 PISOS-COLOR MALDONADO</t>
+  </si>
+  <si>
+    <t>DAVILA TERAN MARIA CASTORINA</t>
+  </si>
+  <si>
+    <t>IBARRA AVENIDA ATAHUALPA 1639</t>
+  </si>
+  <si>
+    <t>DAVILA TORRES RAUL FERNANDO VINICIO</t>
+  </si>
+  <si>
+    <t>AV. ATAHUALPA 21330 Y -</t>
+  </si>
+  <si>
+    <t>DAVILA YEPEZ VERONICA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>BRASIL 0 Y PARAGUAY BRASIL</t>
+  </si>
+  <si>
+    <t>ECHEVERRIA DAVILA KATIA PAULINA</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO GRIJALVA 0 Y Y ELEODORO AYALA Y RICARDO SANCHEZ CONDOMINIO SHALOM II CASA 15</t>
+  </si>
+  <si>
+    <t>FABRICIO ALEXANDER CADENA DAVILA</t>
+  </si>
+  <si>
+    <t>NELSON LOPEZ OBANDO 0 Y MARIANA DE JESUS PAREDES POR EL 2X1</t>
+  </si>
+  <si>
+    <t>FAUSTO MARCELO VILLEGAS DAVILA</t>
+  </si>
+  <si>
+    <t>PROLONGACI�N ROCAFUERTE 0 Y RIO CENEPA</t>
+  </si>
+  <si>
+    <t>FLORES DAVILA HILDA INES</t>
+  </si>
+  <si>
+    <t>EL TEJAR CALLE PRINCIPAL 0 Y NAZACOTA PUENTO EL TEJAR CALLE PRINCIPAL</t>
+  </si>
+  <si>
+    <t>GOMEZ DAVILA ALBERTO OLMEDO</t>
+  </si>
+  <si>
+    <t>TENA 820 Y CALLE TUNHURAGUA</t>
+  </si>
+  <si>
+    <t>GUERRERO DAVILA LUCIA MAGALI</t>
+  </si>
+  <si>
+    <t>IBARRA 513 Y Y MACAS</t>
+  </si>
+  <si>
+    <t>HERRERA DAVILA FELIPE RAFAEL</t>
+  </si>
+  <si>
+    <t>AVENIDA PEREZ GUERRERO 549 Y BOLIVAR AVENIDA PEREZ GUERRERO</t>
+  </si>
+  <si>
+    <t>CIUDADELA JARDIN SN</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA JARDIN JUAN GENARO JARAMILLO 419</t>
+  </si>
+  <si>
+    <t>TOBAR SUBIA 245 Y ELEODORO AYALA TOBAR SUBIA</t>
+  </si>
+  <si>
+    <t>HINOJOSA DAVILA FERNANDA MAGDALENA</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE BORJA 0 Y AV. VICTOR MANUEL GUZMAN INSTALAR 14:00PM// LLAMAR A 0998373130-0987662144-62953606</t>
+  </si>
+  <si>
+    <t>JAIME HUMBERTO FEDERICO DAVILA CARRERA</t>
+  </si>
+  <si>
+    <t>CIUDADELA DEL CHOFER SN Y PADRE ALBERTO HARO</t>
+  </si>
+  <si>
+    <t>LUCIA JACQUELINE DAVILA ALBORNOZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ Y CIFUENTES 0 Y AYACUCHO</t>
+  </si>
+  <si>
+    <t>MARGARITA SUSANA MENESES DAVILA</t>
+  </si>
+  <si>
+    <t>IBARRA LUIS GOMEZ JURADO 339 Y LUIS VARGAS TORRES IBARRA LUIS GOMEZ JURADO</t>
+  </si>
+  <si>
+    <t>MARIA ELENA DAVILA RODAS</t>
+  </si>
+  <si>
+    <t>MIGUEL OVIEDO 739 Y SIMON BOLIVAR EDIFICIO MUTUALISTA IMBABURA EDIFICIO MUTUALISTA IMBABURA SIMON BOLIVAR</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA VALLE DAVILA</t>
+  </si>
+  <si>
+    <t>ANTONIO JOSE DE SUCRE 0 Y TOBIAS MENA tras de la cooperativa bola amarilla tras de la cooperativa bola amarilla TOBIAS MENA</t>
+  </si>
+  <si>
+    <t>MARIA RAQUEL CARVALLO DAVILA</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE BORJA 0 Y VICTOR GOMEZ JURADO CASA 43 CASA-43 LUIS FELIPE BORJA</t>
+  </si>
+  <si>
+    <t>MARIO RAMIRO MENESES DAVILA</t>
+  </si>
+  <si>
+    <t>CALLE QUILAGO 0 CASA 10 - A CASA-10 - A COLINAS DEL RETORNO</t>
+  </si>
+  <si>
+    <t>MARTHA SUSANA DAVILA PAREDES</t>
+  </si>
+  <si>
+    <t>SUCRE 21103 Y TOBIAS MENA SECTOR BOLA AMARILLA</t>
+  </si>
+  <si>
+    <t>MENESES DAVILA HUGO ALFREDO</t>
+  </si>
+  <si>
+    <t>IBARRA FLORES Y SANCHEZ Y CIFUENTES ESQUINA</t>
+  </si>
+  <si>
+    <t>MONTALVO DAVILA PATRICIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>CALLE LOS GALEANOS 0 Y AV MANUELA CA�IZARES SECTOR ELJIDO DE IBARRA CONJUNTO SANTA LUCIA</t>
+  </si>
+  <si>
+    <t>NAVARRO DAVILA JULIO CESAR</t>
+  </si>
+  <si>
+    <t>IBARRA URBANIZACION JOSE M LEORO CALLE 6 164</t>
+  </si>
+  <si>
+    <t>NIETO DAVILA NANCY RUBY</t>
+  </si>
+  <si>
+    <t>CIUDADELA JARDIN CALLE 26 SN</t>
+  </si>
+  <si>
+    <t>NIETO DAVILA WILSON EDMUNDO</t>
+  </si>
+  <si>
+    <t>CARLOS ELIAS ALMEIDA 9104 Y GENARO JARAMILLO CARLOS ELIAS ALMEIDA</t>
+  </si>
+  <si>
+    <t>IBARRA ELIAS ALMEIDA 9104</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA JARDIN ELIAS ALMEIDA 9104</t>
+  </si>
+  <si>
+    <t>OREJUELA DAVILA GUILLERMO JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>IBARRA AVENIDA VICTOR M GUZMAN 332</t>
+  </si>
+  <si>
+    <t>ORQUERA DAVILA LORENA ANA CECILIA</t>
+  </si>
+  <si>
+    <t>ELEODORO AYALA 110 Y JORGE DAVILA MEZA CLINICA IBARRA PISO 3 CONSULTORIOS CLINICA IBARRA-PISO 3 ELEODORO AYALA</t>
+  </si>
+  <si>
+    <t>OSCAR EFREN HERRERA DAVILA</t>
+  </si>
+  <si>
+    <t>RAFAEL TROYA 655 Y AVENIDA CRISTOBAL DETROYA RAFAEL TROYA</t>
+  </si>
+  <si>
+    <t>AVENIDA MARIANO ACOSTA 0 Y CALLE SIN NOMBRE AVENIDA MARIANO ACOSTA</t>
+  </si>
+  <si>
+    <t>DAVILA CEVALLOS SILVIA MARGOTH</t>
+  </si>
+  <si>
+    <t>MAGDALENA BAJO 0 Y CALLE S/N MAS ARRIAB DE TANQUES DE AGUA MAGDALENA BAJO</t>
+  </si>
+  <si>
+    <t>GARCIA MORENO IMBABURA</t>
+  </si>
+  <si>
+    <t>ANGULO DAVILA JAMES OLGUIN</t>
+  </si>
+  <si>
+    <t>VIA EL ROSARIIO 0 Y CALLE SIN NOMBRE VIA EL ROSARIIO</t>
+  </si>
+  <si>
+    <t>CUELLAJE</t>
+  </si>
+  <si>
+    <t>ANGULO DAVILA JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>ELOISA ALVAREZ 0 Y 21 DE NOVIEMBRE ELOISA ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANGULO DAVILA MARSOVIA MARIBEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO AYALA 0 Y VIA SAN JOAQUIN ESQUINA ALEJANDRO AYALA</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA LIBA CARMEN VICTORIA</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL 0 Y CALLE SIN NOMBRE VIA AL CEMENTERIO CUELLAJE ALTO CALLE PRINCIPAL</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA ROSA MERCEDES</t>
+  </si>
+  <si>
+    <t>VIA EL ROSARIIO 0 Y CALLE SIN NOMBRE CASA EN LO ALTO DE LA VIA LOCALIDDA LA MAGDALENA VIA EL ROSARIIO</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA WILMAN GIOVANI</t>
+  </si>
+  <si>
+    <t>VIA PRINCIAL A LA MAGDALENA 0 Y VIA AL ROSARIO CASA DE UN PISO FACHADA DE CERAMICA CASA-DE UN PISO VIA PRINCIAL A LA MAGDALENA</t>
+  </si>
+  <si>
+    <t>DAVILA ANGULO HERMOGENES ALFREDO</t>
+  </si>
+  <si>
+    <t>VIA PRINCIAL A LA MAGDALENA 0 Y VIA AL ROSARIO BARRIO LA MAGDALENA VIA AL ROSARIO VIA PRINCIAL A LA MAGDALENA</t>
+  </si>
+  <si>
+    <t>DAVILA NOGALES HERALDO JUSTINO</t>
+  </si>
+  <si>
+    <t>VIA A LA MAGDALENA 0 Y VIA EL ROSARIIO CASA DE UN PISO DE BLOQUE Y TEJA CASA-DE UN PISO DE BLOQUE VIA A LA MAGDALENA</t>
+  </si>
+  <si>
+    <t>MARCO IVAN AYALA DAVILA</t>
+  </si>
+  <si>
+    <t>VIA EL ROSARIIO 0 Y CALLE SIN NOMBRE CASA 1 PISO DE ETERNIT LOCALIDAD LA MAGDALENA VIA EL ROSARIIO</t>
+  </si>
+  <si>
+    <t>HARO DAVILA PEDRO MIGUEL ERMENEGILDO</t>
+  </si>
+  <si>
+    <t>COTACACHI PARR QUIROGA BARRIO LA VICTORIA VIA DON BOSCO</t>
+  </si>
+  <si>
+    <t>COTACACHI</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA MIGUEL ANGEL BOLIVAR</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI JUAN DE VELASCO 0886</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI</t>
+  </si>
+  <si>
+    <t>ARAUJO DAVILA LUCIA MATILDE</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ SN 0 21 DE NOVIEMBRE CasaAZUL 2PISOS CASA-AZUL 2PISOS---- SEC ANDRADE MARIN BRR CENTRAL 1 CUADRA DEL PARQUE MARIN</t>
+  </si>
+  <si>
+    <t>CADENA DAVILA KAREN DOMINIC</t>
+  </si>
+  <si>
+    <t>GONZALEZ SUAREZ 0 Y BOLIVAR GONZALEZ SUAREZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN PAUL CADENA DAVILA</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y AV. PICHINCHA</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE JAIME PATRICIO</t>
+  </si>
+  <si>
+    <t>CALLE S/N 0 Y B. MIRADOR CALLE S/N CALLE S/N</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE LUIS ROBERTO</t>
+  </si>
+  <si>
+    <t>ABDON CALDERON 944 Y JUNIN ABDON CALDERON</t>
+  </si>
+  <si>
+    <t>DAVILA BELTRAN JOSE LINO</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI PENIAHERRERA SN Y GENERAL ENRIQUEZ ESQUINA</t>
+  </si>
+  <si>
+    <t>DAVILA BRAVO SEGUNDO CARLOS</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI ATAHUALPA S/N Y ROCAFUERTE ATUNTAQUI ATAHUALPA</t>
+  </si>
+  <si>
+    <t>ATAHUALPA 841 Y ROCAFUERTE ATAHUALPA</t>
+  </si>
+  <si>
+    <t>DAVILA CADENA SANDRA LUCIA</t>
+  </si>
+  <si>
+    <t>JUAN MONTALVO 0 Y QUITO JUAN MONTALVO</t>
+  </si>
+  <si>
+    <t>DAVILA CALDERON DANNY PAUL</t>
+  </si>
+  <si>
+    <t>JOSE IGNACIO PE�AHERRERA 0 Y GENERAL ENRIQUEZ CASA 2 PISOS ROSADA EN LA PARTE DE ATRAS DIAGONAL AL PARQUE SECTOR ANDRADE MARIN CASA-2 PISOS ROSADA EN LA JOSE IGNACIO PE�AHERRERA</t>
+  </si>
+  <si>
+    <t>DAVILA CALDERON JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GONZALEZ SAUREZ SN Y PABNMERICANA ATUNTAQUI GONZALEZ SAUREZ SN</t>
+  </si>
+  <si>
+    <t>DAVILA CALUQUI LUIS ARTURO</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 1109 Y ATAHUALPA ANDRADE MARIN</t>
+  </si>
+  <si>
+    <t>DAVILA CEVALLOS FABIOLA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI DALMAO SN Y GENERAL ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>DAVILA ENCALADA EMMA VIOLETA</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI OLMEDO SN Y ESPEJO</t>
+  </si>
+  <si>
+    <t>DAVILA ESPINOSA ANA LUISA</t>
+  </si>
+  <si>
+    <t>GONZALEZ SUAREZ 2109 Y ELOY ALFARO GONZALEZ SUAREZ</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 0 Y BOLIVAR</t>
+  </si>
+  <si>
+    <t>BOLIVAR 1222 Y AMAZONAS BARRIO CENTRAL BOLIVAR</t>
+  </si>
+  <si>
+    <t>DAVILA ESPINOSA RUBI DE SANTA MONICA</t>
+  </si>
+  <si>
+    <t>LUIS OLMEDO JATIVA 0 Y AV LUIS LEORO FRANCO</t>
+  </si>
+  <si>
+    <t>DAVILA GARZON CARLOS RAMIRO</t>
+  </si>
+  <si>
+    <t>BOLIVAR SN 1341 OLMEDO CasaROSADA 2 PISOS CASA-ROSADA 2 PISOS---- BARRIO SANTA ANA JUNTO A AGENCIA DE ANDINATEL</t>
+  </si>
+  <si>
+    <t>DAVILA GARZON ELSA IRALDA</t>
+  </si>
+  <si>
+    <t>JUAN MONTALVO 970 Y GONZALEZ SUAREZ CASA DURAZNO JUAN MONTALVO</t>
+  </si>
+  <si>
+    <t>DAVILA GARZON PACO ANIBAL</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI PLAZA LIBERTAD SN</t>
+  </si>
+  <si>
+    <t>DAVILA GARZON PIEDAD MAGDALENA</t>
+  </si>
+  <si>
+    <t>GONZALEZ SUAREZ 7 Y ALEJANDRO ANDRADE CONDOMINIO PLAZA CENTRO CONDOMINIO-PLAZA CENTRO GONZALEZ SUAREZ</t>
+  </si>
+  <si>
+    <t>DAVILA GUEVARA MARIANITA DE JESUS</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GENERAL ENRIQUEZ 1230 ENTRE SUCRE Y BOLIVAR</t>
+  </si>
+  <si>
+    <t>DAVILA GUEVARA PEDRO JORGE</t>
+  </si>
+  <si>
+    <t>2 DE MARZO 1526 Y ESPEJO 2 DE MARZO</t>
+  </si>
+  <si>
+    <t>DAVILA HINOJOSA GLORIA MARIA</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 5- 1356 Y Y PEREZ MU�OZ ALTOS ALMACEN DCACHE ALTOS ALMACEN DCACHE PEREZ MU�OZ</t>
+  </si>
+  <si>
+    <t>DAVILA LEON MARIA</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GARCIA MORENO SN Y GONZALEZ SUAREZ</t>
+  </si>
+  <si>
+    <t>DAVILA MALITAXI INES GERMANIA</t>
+  </si>
+  <si>
+    <t>21 DE NOVIEMBRE 1027 BARRIO CENTRAL BRR-CENTRAL</t>
+  </si>
+  <si>
+    <t>DAVILA MARINA MARINA LEONOR</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 0Y DALMAU ESQUINA SECTOR ANDRADE MARIN DALMAU-ESQUINA-SECTOR ANDRADE-MARIN</t>
+  </si>
+  <si>
+    <t>DAVILA MARROQUIN SONIA JAQUELINE</t>
+  </si>
+  <si>
+    <t>RIO FRIO 0 Y IMBABURA BARRIO CENTRAL BARRIO-CENTRAL RIO FRIO</t>
+  </si>
+  <si>
+    <t>DAVILA MARTINEZ CIA LTDA</t>
+  </si>
+  <si>
+    <t>AVENIDA JULIO MIGUEL AGUINAGA 1339 Y OLMEDO AVENIDA JULIO MIGUEL AGUINAGA</t>
+  </si>
+  <si>
+    <t>DAVILA MARTINEZ CRISTIAN ANDRES</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 320 Y BOLIVAR VINUEZA</t>
+  </si>
+  <si>
+    <t>DAVILA POSSO CARMEN AMELIA</t>
+  </si>
+  <si>
+    <t>PEREZ MU�OZ 1115 Y GENERAL ENRIQUEZ PEREZ MU�OZ</t>
+  </si>
+  <si>
+    <t>DAVILA POSSO EDWIN MAURICIO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO ANDRADE 1137 Y AVENIDA RIO AMAZONAS Y GENERAL ENRIQUEZ FRENTE A CONFECC MISHEL Y GRAL. ENRIQUEZ-FRENTE A CONFECC-MISHEL-. ALEJANDRO ANDRADE</t>
+  </si>
+  <si>
+    <t>DAVILA POSSO MARIA ANGELICA MATILDE</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 11106</t>
+  </si>
+  <si>
+    <t>DAVILA POZO MARTHA CECILIA</t>
+  </si>
+  <si>
+    <t>AV. JULIO MIGUEL AGUINAGA 318 Y OLMEDO</t>
+  </si>
+  <si>
+    <t>DAVILA PULLAS LORENA MARIVEL</t>
+  </si>
+  <si>
+    <t>LUIS OLMEDO JATIVA 0 Y AV. LUIS LEORO FRANCO</t>
+  </si>
+  <si>
+    <t>DAVILA SEVILLA FANNY GUADALUPE</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GENERAL ALBERTO ENRIQUEZ SN Y ATAHUALPA</t>
+  </si>
+  <si>
+    <t>DAVILA SILVA ESPERANZA DE JESUS</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI RIOFRIO SN Y PARQUE 9 DE OCTUBRE</t>
+  </si>
+  <si>
+    <t>DAVILA TERAN JAIME NEPTALI</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI JUNIN SN Y ABDON CALDERON</t>
+  </si>
+  <si>
+    <t>DAVILA TERAN MANUEL ARTURO</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI JUNIN 641</t>
+  </si>
+  <si>
+    <t>DAVILA TERAN MARIANITA DE JESUS</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI ANDRADE MARIN 21 NOVIEMBRE SN</t>
+  </si>
+  <si>
+    <t>DIEGO FERNANDO DAVILA ARCINIEGA</t>
+  </si>
+  <si>
+    <t>12 DE FEBRERO 0 Y AVENIDA SIMON BOLIVAR CASA DE 2P COLOR CREMA, PORTON NEGRO, FRENTE ESCUELA 2 DE MARZO CASA DE 2P COLOR CREMA, PORTON NEGRO, FRENTE ESCUELA 2 DE MARZO AVENIDA SIMON BOLIVAR</t>
+  </si>
+  <si>
+    <t>JATIVA DAVILA GERMAN ALFREDO</t>
+  </si>
+  <si>
+    <t>ATAHUALPA 832 Y OLMEDO ATAHUALPA</t>
+  </si>
+  <si>
+    <t>JATIVA DAVILA LUISA HERMELINDA</t>
+  </si>
+  <si>
+    <t>ALF BOADA 1030</t>
+  </si>
+  <si>
+    <t>LUIS ARTURO PAEZ DAVILA</t>
+  </si>
+  <si>
+    <t>CALLE 14 0 Y LUIS HIDROVO LUIS HIDROVO</t>
+  </si>
+  <si>
+    <t>MARCIA YOLANDA DE LOURDES DAVILA GARZON</t>
+  </si>
+  <si>
+    <t>GONZALES SUAREZ 0 Y JUAN MONTALVO CASA 3 PISOS AMARILLA ESQUIN CASA-3 PISOS AMARILLA ESQUIN</t>
+  </si>
+  <si>
+    <t>DAVILA CARRILLO GLADYS TERESA</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL 0 Y AMBUQUI A 1 CUADRA DELCONJUNTO PARAISO</t>
+  </si>
+  <si>
+    <t>AMBUQUI</t>
+  </si>
+  <si>
+    <t>CARLOS JACINTO DAVILA DAVILA</t>
+  </si>
+  <si>
+    <t>JOSE PE�AHERRERA 0 Y CRISTOBAL COLON</t>
+  </si>
+  <si>
+    <t>DAVILA ARCINIEGA CARLOS ANDRES</t>
+  </si>
+  <si>
+    <t>RAFAEL SANCHEZ 0 Y JUAN FRANCISCO BONILLA CASA 1 PISO ESQUINERA COLOR NEGRO CASA-1 PISO ESQUINERA COLOR</t>
+  </si>
+  <si>
+    <t>DAVILA MERINO PEDRO RAFAEL</t>
+  </si>
+  <si>
+    <t>LUIS DAVILA PEREZ 0 Y REINALDO CHAVEZ CASA 2 PS COLOR BLANCA CON NEGRO PORTON GRIS CASA 2 PS COLOR-BLANCA CON NEGRO</t>
+  </si>
+  <si>
+    <t>DAVILA MONTUFAR HECTOR HOLGER</t>
+  </si>
+  <si>
+    <t>DR. LUIS DAVILA PEREZ 0 Y REINALDO CHAVEZ YUYUCOCHA CASA DE DOS PISOS</t>
+  </si>
+  <si>
+    <t>DAVILA PASQUEL VANESSA</t>
+  </si>
+  <si>
+    <t>CDLA. ANGEL ESCOBAR 0Y Y CALLE D FRENTE CABA�AS HACIENDA</t>
+  </si>
+  <si>
+    <t>DIAZ DAVILA NORMA ELIZABETH</t>
+  </si>
+  <si>
+    <t>CALLE G 0 Y CALLE D CASA TOMATE CON PORTON BLANCO 1 PISO TERRAZA - CASA TOMATE CON-PORTON BLANCO-1 PISO TERRAZA-- CALLE G</t>
+  </si>
+  <si>
+    <t>MARIANA DE JESUS CABRERA DAVILA</t>
+  </si>
+  <si>
+    <t>QUINTA EL OLIVO 0 BARRIO SANTA MARIANITA</t>
+  </si>
+  <si>
+    <t>NATALY JOHANNA DAVILA FREIRE</t>
+  </si>
+  <si>
+    <t>AUTOPISTA YAHUARCOCHA 0 Y CALLE STA. MARIANITA</t>
   </si>
 </sst>
 </file>
@@ -1454,3082 +1559,3058 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>22886749</v>
+        <v>63051064</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>22376450</v>
+        <v>62918920</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>22376450</v>
+        <v>62652836</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>24503711</v>
+        <v>63017631</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>22376946</v>
+        <v>62932053</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>24524092</v>
+        <v>62550142</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>22370721</v>
+        <v>62932543</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>22373800</v>
+        <v>62932054</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>22873252</v>
+        <v>62631007</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>23519762</v>
+        <v>62630529</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>22851468</v>
+        <v>62937749</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>22863031</v>
+        <v>62937398</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>22864182</v>
+        <v>62569082</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>23516887</v>
+        <v>62569086</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>22090376</v>
+        <v>62569036</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>22861820</v>
+        <v>62569117</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>23432533</v>
+        <v>62528003</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>22398077</v>
+        <v>62923139</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>23432533</v>
+        <v>62525898</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>22398077</v>
+        <v>62520655</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>23468094</v>
+        <v>62520598</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>22035283</v>
+        <v>62903674</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>22063279</v>
+        <v>62923898</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>22273090</v>
+        <v>62928763</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>24523402</v>
+        <v>62920074</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>22432403</v>
+        <v>62927375</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>24525463</v>
+        <v>62927684</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>23006487</v>
+        <v>62930476</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>23184488</v>
+        <v>62920866</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>23151166</v>
+        <v>62668347</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>23316399</v>
+        <v>62668190</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>23818494</v>
+        <v>62520803</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>23818503</v>
+        <v>62520348</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>23020945</v>
+        <v>62521775</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>22494762</v>
+        <v>62520818</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>22475086</v>
+        <v>62927902</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>22531291</v>
+        <v>62922997</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>24530997</v>
+        <v>62921650</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>22432403</v>
+        <v>62922849</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>24525463</v>
+        <v>62521380</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>23006487</v>
+        <v>62523753</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>23184488</v>
+        <v>62921512</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>23151166</v>
+        <v>62920494</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45">
-        <v>23316399</v>
+      <c r="A45" t="s">
+        <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A46">
-        <v>22460581</v>
+      <c r="A46" t="s">
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A47">
-        <v>22407320</v>
+      <c r="A47" t="s">
+        <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A48">
-        <v>22812169</v>
+      <c r="A48" t="s">
+        <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A49">
-        <v>22467250</v>
+      <c r="A49" t="s">
+        <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A50">
-        <v>22560626</v>
+      <c r="A50" t="s">
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A51">
-        <v>22565555</v>
+      <c r="A51" t="s">
+        <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A52">
-        <v>22494167</v>
+      <c r="A52" t="s">
+        <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A53">
-        <v>22284034</v>
+      <c r="A53" t="s">
+        <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A54">
-        <v>22663972</v>
+      <c r="A54" t="s">
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A55">
-        <v>23500313</v>
+      <c r="A55" t="s">
+        <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A56">
-        <v>22808107</v>
+      <c r="A56" t="s">
+        <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A57">
-        <v>22628152</v>
+      <c r="A57" t="s">
+        <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A58">
-        <v>22590226</v>
+      <c r="A58" t="s">
+        <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A59">
-        <v>22920474</v>
+      <c r="A59" t="s">
+        <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A60">
-        <v>22459869</v>
+      <c r="A60" t="s">
+        <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A61">
-        <v>22730755</v>
+      <c r="A61" t="s">
+        <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A62">
-        <v>22615667</v>
+      <c r="A62" t="s">
+        <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>23440352</v>
+        <v>62516222</v>
       </c>
       <c r="B63" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>23285000</v>
+        <v>62539292</v>
       </c>
       <c r="B64" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>22480908</v>
+        <v>62569037</v>
       </c>
       <c r="B65" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>22432403</v>
+        <v>62585846</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>24525463</v>
+        <v>62679043</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>23054361</v>
+        <v>62615580</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>22410881</v>
+        <v>62952013</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>22558276</v>
+        <v>62951868</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="D70" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>22663898</v>
+        <v>62540277</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>23027926</v>
+        <v>62569004</v>
       </c>
       <c r="B72" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="C72" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="D72" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>22294012</v>
+        <v>62956658</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>22433414</v>
+        <v>62600228</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C74" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D74" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>22444975</v>
+        <v>62950109</v>
       </c>
       <c r="B75" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C75" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="D75" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>22268037</v>
+        <v>62641557</v>
       </c>
       <c r="B76" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>22236040</v>
+        <v>62957877</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C77" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="D77" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>22493567</v>
+        <v>62952847</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C78" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>22233643</v>
+        <v>62644586</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="C79" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>22662364</v>
+        <v>62954310</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="C80" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81">
-        <v>24504786</v>
+        <v>62612346</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="C81" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>23008578</v>
+        <v>62958515</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D82" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>22521438</v>
+        <v>62641586</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="C83" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="D83" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>22479297</v>
+        <v>62959723</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C84" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D84" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>22479298</v>
+        <v>62616099</v>
       </c>
       <c r="B85" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="C85" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>22955882</v>
+        <v>62612844</v>
       </c>
       <c r="B86" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C86" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D86" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>22679769</v>
+        <v>62605505</v>
       </c>
       <c r="B87" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C87" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D87" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>23122292</v>
+        <v>63022057</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C88" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="D88" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89">
-        <v>22844184</v>
+        <v>62950099</v>
       </c>
       <c r="B89" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90">
-        <v>22598914</v>
+        <v>62641881</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D90" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91">
-        <v>22436876</v>
+        <v>62954209</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="C91" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>22267210</v>
+        <v>62950031</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>23260828</v>
+        <v>62958641</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="C93" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="D93" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>23262164</v>
+        <v>62950140</v>
       </c>
       <c r="B94" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95">
-        <v>24502173</v>
+        <v>62615800</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C95" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>22427499</v>
+        <v>62601656</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C96" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D96" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>24529050</v>
+        <v>62569041</v>
       </c>
       <c r="B97" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C97" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>22251062</v>
+        <v>62606442</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="C98" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="D98" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>22270019</v>
+        <v>62539261</v>
       </c>
       <c r="B99" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="C99" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D99" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>22802436</v>
+        <v>62505138</v>
       </c>
       <c r="B100" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C100" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="D100" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101">
-        <v>22479001</v>
+        <v>62585254</v>
       </c>
       <c r="B101" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C101" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="D101" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102">
-        <v>22277797</v>
+        <v>62603923</v>
       </c>
       <c r="B102" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C102" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D102" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103">
-        <v>23406564</v>
+        <v>62641627</v>
       </c>
       <c r="B103" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="C103" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="D103" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104">
-        <v>22643709</v>
+        <v>62955989</v>
       </c>
       <c r="B104" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C104" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="D104" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105">
-        <v>22570418</v>
+        <v>62602721</v>
       </c>
       <c r="B105" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C105" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D105" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106">
-        <v>23118921</v>
+        <v>63048245</v>
       </c>
       <c r="B106" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="C106" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="D106" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107">
-        <v>23118922</v>
+        <v>62958522</v>
       </c>
       <c r="B107" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="C107" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108">
-        <v>23807358</v>
+        <v>62950155</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="C108" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="D108" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109">
-        <v>22427667</v>
+        <v>62600450</v>
       </c>
       <c r="B109" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="C109" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D109" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110">
-        <v>22285809</v>
+        <v>62952898</v>
       </c>
       <c r="B110" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="C110" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="D110" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A111">
-        <v>22282106</v>
+        <v>62956805</v>
       </c>
       <c r="B111" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C111" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="D111" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112">
-        <v>22282458</v>
+        <v>62651397</v>
       </c>
       <c r="B112" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="C112" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="D112" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A113">
-        <v>22460577</v>
+        <v>62610693</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="C113" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="D113" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A114">
-        <v>23033506</v>
+        <v>62951218</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="D114" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A115">
-        <v>22848000</v>
+        <v>62652921</v>
       </c>
       <c r="B115" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C115" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D115" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A116">
-        <v>23103654</v>
+        <v>62511184</v>
       </c>
       <c r="B116" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C116" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A117">
-        <v>23009352</v>
+        <v>62604106</v>
       </c>
       <c r="B117" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C117" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D117" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118">
-        <v>23285354</v>
+        <v>62511967</v>
       </c>
       <c r="B118" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C118" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D118" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119">
-        <v>22622751</v>
+        <v>62546138</v>
       </c>
       <c r="B119" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C119" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="D119" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120">
-        <v>22674484</v>
+        <v>62603619</v>
       </c>
       <c r="B120" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C120" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D120" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121">
-        <v>24506142</v>
+        <v>62951027</v>
       </c>
       <c r="B121" t="s">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D121" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A122">
-        <v>22665311</v>
+        <v>62955017</v>
       </c>
       <c r="B122" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D122" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A123">
-        <v>22911802</v>
+        <v>62958048</v>
       </c>
       <c r="B123" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A124">
-        <v>23803107</v>
+        <v>62953606</v>
       </c>
       <c r="B124" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C124" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D124" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A125">
-        <v>23300004</v>
+        <v>62951209</v>
       </c>
       <c r="B125" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C125" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D125" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A126">
-        <v>22293710</v>
+        <v>62505159</v>
       </c>
       <c r="B126" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C126" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D126" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A127">
-        <v>22295269</v>
+        <v>62641357</v>
       </c>
       <c r="B127" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C127" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D127" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A128">
-        <v>22293829</v>
+        <v>62952487</v>
       </c>
       <c r="B128" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C128" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D128" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A129">
-        <v>23412756</v>
+        <v>62512586</v>
       </c>
       <c r="B129" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C129" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D129" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A130">
-        <v>22666972</v>
+        <v>62632125</v>
       </c>
       <c r="B130" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="C130" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="D130" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A131">
-        <v>22604877</v>
+        <v>62539103</v>
       </c>
       <c r="B131" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C131" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D131" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A132">
-        <v>22732060</v>
+        <v>62511872</v>
       </c>
       <c r="B132" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="C132" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D132" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A133">
-        <v>22497525</v>
+        <v>62953213</v>
       </c>
       <c r="B133" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C133" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="D133" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A134">
-        <v>22667226</v>
+        <v>62510003</v>
       </c>
       <c r="B134" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C134" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A135">
-        <v>23340676</v>
+        <v>62957147</v>
       </c>
       <c r="B135" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C135" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D135" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A136">
-        <v>22657739</v>
+        <v>62641007</v>
       </c>
       <c r="B136" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C136" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="D136" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A137">
-        <v>22454822</v>
+        <v>62609729</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C137" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="D137" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A138">
-        <v>22323648</v>
+        <v>62953073</v>
       </c>
       <c r="B138" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D138" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A139">
-        <v>22808294</v>
+        <v>62956932</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C139" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A140">
-        <v>22473053</v>
+        <v>62956753</v>
       </c>
       <c r="B140" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="D140" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A141">
-        <v>23130006</v>
+        <v>62606752</v>
       </c>
       <c r="B141" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A142">
-        <v>23048255</v>
+        <v>62609753</v>
       </c>
       <c r="B142" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C142" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="D142" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A143">
-        <v>23452558</v>
+        <v>62609755</v>
       </c>
       <c r="B143" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="C143" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D143" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A144">
-        <v>23009232</v>
+        <v>62505030</v>
       </c>
       <c r="B144" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C144" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="D144" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A145">
-        <v>22494315</v>
+        <v>63051249</v>
       </c>
       <c r="B145" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C145" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="D145" t="s">
-        <v>8</v>
+        <v>254</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A146">
-        <v>22683472</v>
+        <v>63016179</v>
       </c>
       <c r="B146" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C146" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D146" t="s">
-        <v>8</v>
+        <v>257</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A147">
-        <v>22630957</v>
+        <v>62679181</v>
       </c>
       <c r="B147" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="C147" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="D147" t="s">
-        <v>8</v>
+        <v>257</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A148">
-        <v>22950049</v>
+        <v>63051996</v>
       </c>
       <c r="B148" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="C148" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>8</v>
+        <v>257</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A149">
-        <v>23282780</v>
+        <v>63016125</v>
       </c>
       <c r="B149" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="C149" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="D149" t="s">
-        <v>8</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A150">
-        <v>22475274</v>
+        <v>63016171</v>
       </c>
       <c r="B150" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C150" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>8</v>
+        <v>257</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A151">
-        <v>24508673</v>
+        <v>63016353</v>
       </c>
       <c r="B151" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="C151" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="D151" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A152">
-        <v>22354644</v>
+        <v>63016312</v>
       </c>
       <c r="B152" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="C152" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="D152" t="s">
-        <v>17</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A153">
-        <v>22353027</v>
+        <v>63016355</v>
       </c>
       <c r="B153" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="C153" t="s">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="D153" t="s">
-        <v>17</v>
+        <v>257</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A154">
-        <v>22380507</v>
+        <v>63016163</v>
       </c>
       <c r="B154" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C154" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="D154" t="s">
-        <v>22</v>
+        <v>257</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A155">
-        <v>22380402</v>
+        <v>62537311</v>
       </c>
       <c r="B155" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C155" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="D155" t="s">
-        <v>22</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A156">
-        <v>23895865</v>
+        <v>62907942</v>
       </c>
       <c r="B156" t="s">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="C156" t="s">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="D156" t="s">
-        <v>22</v>
+        <v>279</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A157">
-        <v>22145319</v>
+        <v>62530020</v>
       </c>
       <c r="B157" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C157" t="s">
+        <v>281</v>
+      </c>
+      <c r="D157" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A158">
+        <v>62910178</v>
+      </c>
+      <c r="B158" t="s">
+        <v>282</v>
+      </c>
+      <c r="C158" t="s">
+        <v>283</v>
+      </c>
+      <c r="D158" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A159">
+        <v>62907857</v>
+      </c>
+      <c r="B159" t="s">
+        <v>284</v>
+      </c>
+      <c r="C159" t="s">
+        <v>285</v>
+      </c>
+      <c r="D159" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A160">
+        <v>62909842</v>
+      </c>
+      <c r="B160" t="s">
+        <v>286</v>
+      </c>
+      <c r="C160" t="s">
+        <v>287</v>
+      </c>
+      <c r="D160" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A161">
+        <v>62530136</v>
+      </c>
+      <c r="B161" t="s">
+        <v>288</v>
+      </c>
+      <c r="C161" t="s">
+        <v>289</v>
+      </c>
+      <c r="D161" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A162">
+        <v>62530699</v>
+      </c>
+      <c r="B162" t="s">
+        <v>290</v>
+      </c>
+      <c r="C162" t="s">
+        <v>291</v>
+      </c>
+      <c r="D162" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A163">
+        <v>62907624</v>
+      </c>
+      <c r="B163" t="s">
         <v>292</v>
       </c>
-      <c r="D157" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A158" t="s">
-        <v>23</v>
-      </c>
-      <c r="B158" t="s">
-        <v>23</v>
-      </c>
-      <c r="C158" t="s">
-        <v>23</v>
-      </c>
-      <c r="D158" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
-        <v>23</v>
-      </c>
-      <c r="B159" t="s">
-        <v>23</v>
-      </c>
-      <c r="C159" t="s">
-        <v>23</v>
-      </c>
-      <c r="D159" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
-        <v>23</v>
-      </c>
-      <c r="B160" t="s">
-        <v>23</v>
-      </c>
-      <c r="C160" t="s">
-        <v>23</v>
-      </c>
-      <c r="D160" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A161" t="s">
-        <v>23</v>
-      </c>
-      <c r="B161" t="s">
-        <v>23</v>
-      </c>
-      <c r="C161" t="s">
-        <v>23</v>
-      </c>
-      <c r="D161" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A162" t="s">
-        <v>23</v>
-      </c>
-      <c r="B162" t="s">
-        <v>23</v>
-      </c>
-      <c r="C162" t="s">
-        <v>23</v>
-      </c>
-      <c r="D162" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A163" t="s">
-        <v>23</v>
-      </c>
-      <c r="B163" t="s">
-        <v>23</v>
-      </c>
       <c r="C163" t="s">
-        <v>23</v>
+        <v>293</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A164" t="s">
-        <v>23</v>
+      <c r="A164">
+        <v>62907814</v>
       </c>
       <c r="B164" t="s">
-        <v>23</v>
+        <v>292</v>
       </c>
       <c r="C164" t="s">
-        <v>23</v>
+        <v>294</v>
       </c>
       <c r="D164" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A165" t="s">
-        <v>23</v>
+      <c r="A165">
+        <v>62907946</v>
       </c>
       <c r="B165" t="s">
-        <v>23</v>
+        <v>295</v>
       </c>
       <c r="C165" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="D165" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A166" t="s">
-        <v>23</v>
+      <c r="A166">
+        <v>62530739</v>
       </c>
       <c r="B166" t="s">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="C166" t="s">
-        <v>23</v>
+        <v>298</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A167">
-        <v>22899558</v>
+        <v>62530584</v>
       </c>
       <c r="B167" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C167" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D167" t="s">
-        <v>24</v>
+        <v>279</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A168">
-        <v>23672360</v>
+        <v>62530583</v>
       </c>
       <c r="B168" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C168" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D168" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A169">
-        <v>23030251</v>
+        <v>62530657</v>
       </c>
       <c r="B169" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C169" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D169" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A170">
-        <v>22316285</v>
+        <v>62907179</v>
       </c>
       <c r="B170" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C170" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D170" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A171" t="s">
-        <v>0</v>
+      <c r="A171">
+        <v>62530190</v>
       </c>
       <c r="B171" t="s">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="C171" t="s">
-        <v>2</v>
+        <v>308</v>
       </c>
       <c r="D171" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A172" t="s">
-        <v>0</v>
+      <c r="A172">
+        <v>62530769</v>
       </c>
       <c r="B172" t="s">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="C172" t="s">
-        <v>2</v>
+        <v>309</v>
       </c>
       <c r="D172" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
-        <v>0</v>
+      <c r="A173">
+        <v>62906599</v>
       </c>
       <c r="B173" t="s">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="C173" t="s">
-        <v>2</v>
+        <v>310</v>
       </c>
       <c r="D173" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A174" t="s">
-        <v>0</v>
+      <c r="A174">
+        <v>62908902</v>
       </c>
       <c r="B174" t="s">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="C174" t="s">
-        <v>2</v>
+        <v>312</v>
       </c>
       <c r="D174" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A175" t="s">
-        <v>0</v>
+      <c r="A175">
+        <v>62906523</v>
       </c>
       <c r="B175" t="s">
-        <v>1</v>
+        <v>313</v>
       </c>
       <c r="C175" t="s">
-        <v>2</v>
+        <v>314</v>
       </c>
       <c r="D175" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A176" t="s">
-        <v>0</v>
+      <c r="A176">
+        <v>62906212</v>
       </c>
       <c r="B176" t="s">
-        <v>1</v>
+        <v>315</v>
       </c>
       <c r="C176" t="s">
-        <v>2</v>
+        <v>316</v>
       </c>
       <c r="D176" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A177" t="s">
-        <v>0</v>
+      <c r="A177">
+        <v>62906091</v>
       </c>
       <c r="B177" t="s">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="C177" t="s">
-        <v>2</v>
+        <v>318</v>
       </c>
       <c r="D177" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A178" t="s">
-        <v>0</v>
+      <c r="A178">
+        <v>62910244</v>
       </c>
       <c r="B178" t="s">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="C178" t="s">
-        <v>2</v>
+        <v>320</v>
       </c>
       <c r="D178" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A179" t="s">
-        <v>0</v>
+      <c r="A179">
+        <v>62907739</v>
       </c>
       <c r="B179" t="s">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="C179" t="s">
-        <v>2</v>
+        <v>322</v>
       </c>
       <c r="D179" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A180" t="s">
-        <v>0</v>
+      <c r="A180">
+        <v>62908341</v>
       </c>
       <c r="B180" t="s">
-        <v>1</v>
+        <v>323</v>
       </c>
       <c r="C180" t="s">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="D180" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A181">
-        <v>22386295</v>
+        <v>62617467</v>
       </c>
       <c r="B181" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C181" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="D181" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A182">
-        <v>23740777</v>
+        <v>62906564</v>
       </c>
       <c r="B182" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C182" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="D182" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A183">
-        <v>23758335</v>
+        <v>62530124</v>
       </c>
       <c r="B183" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C183" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="D183" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A184">
-        <v>23784013</v>
+        <v>62530781</v>
       </c>
       <c r="B184" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C184" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="D184" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A185">
-        <v>22120481</v>
+        <v>62530040</v>
       </c>
       <c r="B185" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C185" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="D185" t="s">
-        <v>313</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A186">
-        <v>22388002</v>
+        <v>62906186</v>
       </c>
       <c r="B186" t="s">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="C186" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="D186" t="s">
-        <v>313</v>
+        <v>279</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A187">
-        <v>24525093</v>
+        <v>62909405</v>
       </c>
       <c r="B187" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C187" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="D187" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A188">
-        <v>22891306</v>
+        <v>62906565</v>
       </c>
       <c r="B188" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C188" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="D188" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A189">
-        <v>23551251</v>
+        <v>62908014</v>
       </c>
       <c r="B189" t="s">
-        <v>190</v>
+        <v>341</v>
       </c>
       <c r="C189" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="D189" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A190">
-        <v>23518972</v>
+        <v>62530566</v>
       </c>
       <c r="B190" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C190" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="D190" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A191">
-        <v>22602026</v>
+        <v>62909183</v>
       </c>
       <c r="B191" t="s">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="C191" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="D191" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A192">
-        <v>22602026</v>
+        <v>62910193</v>
       </c>
       <c r="B192" t="s">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="C192" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="D192" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A193">
-        <v>22340626</v>
+        <v>62530593</v>
       </c>
       <c r="B193" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="C193" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="D193" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A194">
-        <v>22051054</v>
+        <v>62530624</v>
       </c>
       <c r="B194" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="C194" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="D194" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A195">
-        <v>22348075</v>
+        <v>62530610</v>
       </c>
       <c r="B195" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="C195" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="D195" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A196">
-        <v>22341912</v>
+        <v>62530629</v>
       </c>
       <c r="B196" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="C196" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="D196" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A197">
-        <v>22798491</v>
+        <v>62530715</v>
       </c>
       <c r="B197" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C197" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="D197" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A198">
-        <v>23810461</v>
+        <v>62617623</v>
       </c>
       <c r="B198" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="C198" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="D198" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A199">
-        <v>22344477</v>
+        <v>62908130</v>
       </c>
       <c r="B199" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="C199" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="D199" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A200">
-        <v>22190537</v>
+        <v>62906044</v>
       </c>
       <c r="B200" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C200" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="D200" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A201">
-        <v>22865218</v>
+        <v>62617977</v>
       </c>
       <c r="B201" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C201" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="D201" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A202">
-        <v>23811691</v>
+        <v>62908186</v>
       </c>
       <c r="B202" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="C202" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="D202" t="s">
-        <v>28</v>
+        <v>279</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A203">
-        <v>22837821</v>
+        <v>62637257</v>
       </c>
       <c r="B203" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C203" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="D203" t="s">
-        <v>28</v>
+        <v>371</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A204">
-        <v>22823957</v>
+      <c r="A204" t="s">
+        <v>5</v>
       </c>
       <c r="B204" t="s">
-        <v>345</v>
+        <v>5</v>
       </c>
       <c r="C204" t="s">
-        <v>346</v>
+        <v>5</v>
       </c>
       <c r="D204" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A205">
-        <v>22821172</v>
+      <c r="A205" t="s">
+        <v>5</v>
       </c>
       <c r="B205" t="s">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="C205" t="s">
-        <v>347</v>
+        <v>5</v>
       </c>
       <c r="D205" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A206">
-        <v>22822571</v>
+      <c r="A206" t="s">
+        <v>5</v>
       </c>
       <c r="B206" t="s">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>348</v>
+        <v>5</v>
       </c>
       <c r="D206" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A207">
-        <v>22826717</v>
+      <c r="A207" t="s">
+        <v>5</v>
       </c>
       <c r="B207" t="s">
-        <v>349</v>
+        <v>5</v>
       </c>
       <c r="C207" t="s">
-        <v>350</v>
+        <v>5</v>
       </c>
       <c r="D207" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A208">
-        <v>22856005</v>
+      <c r="A208" t="s">
+        <v>5</v>
       </c>
       <c r="B208" t="s">
-        <v>351</v>
+        <v>5</v>
       </c>
       <c r="C208" t="s">
-        <v>352</v>
+        <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B209" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C209" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D209" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B210" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C210" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B211" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D211" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B212" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C212" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D212" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B213" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C213" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D213" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A214" t="s">
-        <v>30</v>
+      <c r="A214">
+        <v>62530932</v>
       </c>
       <c r="B214" t="s">
-        <v>30</v>
+        <v>372</v>
       </c>
       <c r="C214" t="s">
-        <v>30</v>
-      </c>
-      <c r="D214" t="s">
-        <v>30</v>
+        <v>373</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A215" t="s">
-        <v>30</v>
+      <c r="A215">
+        <v>62586305</v>
       </c>
       <c r="B215" t="s">
-        <v>30</v>
+        <v>374</v>
       </c>
       <c r="C215" t="s">
-        <v>30</v>
-      </c>
-      <c r="D215" t="s">
-        <v>30</v>
+        <v>375</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A216" t="s">
-        <v>30</v>
+      <c r="A216">
+        <v>62585418</v>
       </c>
       <c r="B216" t="s">
-        <v>30</v>
+        <v>376</v>
       </c>
       <c r="C216" t="s">
-        <v>30</v>
-      </c>
-      <c r="D216" t="s">
-        <v>30</v>
+        <v>377</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A217" t="s">
-        <v>30</v>
+      <c r="A217">
+        <v>62585862</v>
       </c>
       <c r="B217" t="s">
-        <v>30</v>
+        <v>378</v>
       </c>
       <c r="C217" t="s">
-        <v>30</v>
-      </c>
-      <c r="D217" t="s">
-        <v>30</v>
+        <v>379</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A218" t="s">
-        <v>30</v>
+      <c r="A218">
+        <v>62903577</v>
       </c>
       <c r="B218" t="s">
-        <v>30</v>
+        <v>380</v>
       </c>
       <c r="C218" t="s">
-        <v>30</v>
-      </c>
-      <c r="D218" t="s">
-        <v>30</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A219" t="s">
-        <v>30</v>
+      <c r="A219">
+        <v>62904484</v>
       </c>
       <c r="B219" t="s">
-        <v>30</v>
+        <v>382</v>
       </c>
       <c r="C219" t="s">
-        <v>30</v>
-      </c>
-      <c r="D219" t="s">
-        <v>30</v>
+        <v>383</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A220" t="s">
-        <v>30</v>
+      <c r="A220">
+        <v>62580296</v>
       </c>
       <c r="B220" t="s">
-        <v>30</v>
+        <v>384</v>
       </c>
       <c r="C220" t="s">
-        <v>30</v>
-      </c>
-      <c r="D220" t="s">
-        <v>30</v>
+        <v>385</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A221" t="s">
-        <v>30</v>
+      <c r="A221">
+        <v>62581163</v>
       </c>
       <c r="B221" t="s">
-        <v>30</v>
+        <v>386</v>
       </c>
       <c r="C221" t="s">
-        <v>30</v>
-      </c>
-      <c r="D221" t="s">
-        <v>30</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Output/ContactosReporte.xlsx
+++ b/Data/Output/ContactosReporte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\OneDrive\Documents\UiPath\UiPath_RPA_Adriana_Carrillo\Data\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFB04E6-7199-4E84-897B-71AC86321359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660AC96D-6328-45FB-9307-469946BB40E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{723EF56F-89BA-4F5A-8EA8-F9BDFCB60ACD}"/>
+    <workbookView xWindow="1817" yWindow="1817" windowWidth="16457" windowHeight="8966" xr2:uid="{723EF56F-89BA-4F5A-8EA8-F9BDFCB60ACD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="375">
   <si>
     <t>Número Telefónico</t>
   </si>
@@ -45,1150 +45,1111 @@
     <t>:: DATOS TELEFONICOS ::</t>
   </si>
   <si>
-    <t>ARMANDO ERNESTO DAVILA VERA</t>
-  </si>
-  <si>
-    <t>VIA A PAMPLONA 0Y Y BARRIO CENTRAL CASA DE MADERA UN PISO CASA DE MADERA UN PISO</t>
-  </si>
-  <si>
-    <t>SELVA ALEGRE IMBABURA</t>
-  </si>
-  <si>
-    <t>FAUSTO GERMAN HINOJOSA DAVILA</t>
-  </si>
-  <si>
-    <t>CHIRIBOGA 0 Y CALDERON CHIRIBOGA</t>
-  </si>
-  <si>
-    <t>SAN PABLO</t>
-  </si>
-  <si>
-    <t>MARIO GUILLERMO DAVILA BAQUERIZO</t>
-  </si>
-  <si>
-    <t>PRINCESA CORY 0 Y PRINCESA PACCHA</t>
-  </si>
-  <si>
-    <t>SAN LUIS DE CARANQUI</t>
-  </si>
-  <si>
-    <t>HERRERA DAVILA GERMAN ATAHUALPA</t>
-  </si>
-  <si>
-    <t>CALLE PRINCIPAL SANSHIPANDA 0 Y VIA SAN VICENTE ----- CALLE PRINCIPAL SANSHIPANDA</t>
-  </si>
-  <si>
-    <t>SAN FRANCISCO DE SIGSIPAMBA</t>
-  </si>
-  <si>
-    <t>ALMEIDA DAVILA LUIS RAUL</t>
-  </si>
-  <si>
-    <t>HERMANOS MIDEROS 0 Y SIMON BOLIVAR SECT SAN ANTONIO DE IBARRA.</t>
-  </si>
-  <si>
-    <t>SAN ANTONIO DE IBARRA</t>
-  </si>
-  <si>
-    <t>ARAUJO DAVILA CLEMENCIA ELIZABETH</t>
-  </si>
-  <si>
-    <t>POMPILLO MIDEROS 200 Y VENEZUELA CERRAMIENTO DE LADRILLO CIUDADELA GUSTAVO PAREJA DRILLO CIUDADELA GUSTAVO PAREJA</t>
-  </si>
-  <si>
-    <t>DAVILA RIVADENEIRA PATRICIA SILVANA</t>
-  </si>
-  <si>
-    <t>27 DE NOVIEMBRE 187 0 Y PANAMERICANA SAN ANTONIO</t>
-  </si>
-  <si>
-    <t>DAVILA TENA CARLOS HUMBERTO ARMANDO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE CEVALLOS SN 562 CASA2 PISOS BEIGE CASA-2 PISOS BEIGE---- SECTOR SAN ANTONIO DE IBARRA FRENTE AL PARQUE FRANCISCO CALD</t>
-  </si>
-  <si>
-    <t>CARVALLO DAVILA PATRICIA YASMIN</t>
-  </si>
-  <si>
-    <t>MARCO NICOLALDE 0 Y JORGE SUBIA</t>
-  </si>
-  <si>
-    <t>PUGACHO</t>
-  </si>
-  <si>
-    <t>ORQUERA DAVILA MARIA LEONOR</t>
-  </si>
-  <si>
-    <t>MANUELITA SAENZ 0 Y LOS GALEANOS CASA 1P BLANCA FRENTE TIENDA CASA 1P BLANCA-FRENTE TIENDA</t>
-  </si>
-  <si>
-    <t>CORTEZ DAVILA JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>MONTUFAR 0 Y SUCRE TRAS LOS BA�OS MUNICIPALES FRENTE AL MOTOR DE CNT MONTUFAR</t>
-  </si>
-  <si>
-    <t>PIMAMPIRO</t>
-  </si>
-  <si>
-    <t>CORTEZ DAVILA RODRIGO FILIMON</t>
-  </si>
-  <si>
-    <t>ESPEJO 3100 Y PAQUISHA BARRIIO SAN VICENTE BARRIIO-SAN VICENTE ESPEJO</t>
-  </si>
-  <si>
-    <t>DARWIN RAFAEL NAVAS DAVILA</t>
-  </si>
-  <si>
-    <t>SECTOR SAGALAPAMBA 0 Y CALLE SIN MOMBRE FRENTE AL PARQUE</t>
-  </si>
-  <si>
-    <t>PE�AHERRERA</t>
-  </si>
-  <si>
-    <t>DAVILA PIEDRA CARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>PE�AHERRERA CALLE PRINCIPAL 0 Y PLAZA PRINCIPAL PLAZA 24 DE MAYO</t>
-  </si>
-  <si>
-    <t>CALLE 0 Y CALLE SIN MOMBRE CASA 1 PISO CELESTE PLAZA 24 DE MAYO CASA-1 PISO CELESTE PLAZA 24 DE MAYO</t>
-  </si>
-  <si>
-    <t>EDISSON PATRICIO DAVILA SUAREZ</t>
-  </si>
-  <si>
-    <t>ZONA INTAG PE�AHERRERA 0 SCT. LA PLAZA FTE A LA IGLESIA VILLA PLOMO C/ CAFE</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA DIANA RAQUEL</t>
-  </si>
-  <si>
-    <t>MARIA ANGELICA HIDROVO 151 Y LUIS ENRIQUE CISNEROS MARIA ANGELICA HIDROVO</t>
-  </si>
-  <si>
-    <t>OTAVALO</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA SIXTO TARQUINO</t>
-  </si>
-  <si>
-    <t>OTAVALO IMBAYA LUIS ARCE 131</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA XIMENA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>VICTOR GARCES 0 Y CALLE "G"</t>
-  </si>
-  <si>
-    <t>ANGULO DAVILA NATALIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>CORAZAS 0Y Y PEDRO HERNANDEZ DE LA REINA</t>
-  </si>
-  <si>
-    <t>BURBANO DAVILA PATRICIO AUGUST</t>
-  </si>
-  <si>
-    <t>AV LOS SARANCES 507 Y YAMOR CERRAMIENTO BLANCO CASA 3 PISOS</t>
-  </si>
-  <si>
-    <t>DAVILA ALVEAR MARCIA IRENE</t>
-  </si>
-  <si>
-    <t>BARRIO SAN JUAN SN</t>
-  </si>
-  <si>
-    <t>DAVILA CISNEROS MYRIAN SUSANA</t>
-  </si>
-  <si>
-    <t>CALLE A 49 Y SEBASTIAN MANRIQUE CASA-580 ESQUINA CALLE A</t>
-  </si>
-  <si>
-    <t>DAVILA ENDARA GLORIA MARIA</t>
-  </si>
-  <si>
-    <t>OTAVALO SUCRE 917</t>
-  </si>
-  <si>
-    <t>DAVILA FANNY FANNY ETELVINA</t>
-  </si>
-  <si>
-    <t>OTAVALO GARCIA MORENO 608</t>
-  </si>
-  <si>
-    <t>DAVILA MALDONADO JOSE IVAN</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO DE LA TORRE 0 Y Y CALLE BARR MOSERRAT</t>
-  </si>
-  <si>
-    <t>DAVILA ORBE CESAR HERNAN</t>
-  </si>
-  <si>
-    <t>SUCRE 1005 Y ABDON CALDERON BARRIO SAN LUIS BARRIO-SAN LUIS SUCRE</t>
-  </si>
-  <si>
-    <t>DAVILA ORTIZ YOLANDA ROCIO</t>
-  </si>
-  <si>
-    <t>CALLE PRINCIPAL S/N 68 Y VIA A LA CIUDADELA IMBAYA URBANIZACION MARIA JOSE URBANIZACION-MARIA JOSE CALLE PRINCIPAL S/N</t>
-  </si>
-  <si>
-    <t>DAVILA POSSO DORA LIBERTAD</t>
-  </si>
-  <si>
-    <t>CIUDADELA IMBAYA MANZANA N CASA 13</t>
-  </si>
-  <si>
-    <t>DAVILA ROSERO OLIVER RICARDO</t>
-  </si>
-  <si>
-    <t>AV QUITO 15 Y JACINTO COLLAHUASO URB PRADOS DE PASTAVI HACIENDO DEL AVION JUNTO A LA HACIENDA PASTAVI PASTAVI</t>
-  </si>
-  <si>
-    <t>DAVILA SILVA CARLOS STALIN</t>
-  </si>
-  <si>
-    <t>SUCRE 784 Y MIGUEL EGAS SUCRE</t>
-  </si>
-  <si>
-    <t>DAVILA SILVA MARCO ALFONSO</t>
-  </si>
-  <si>
-    <t>SUCRE 314N Y OLMEDO CASA 1P BLOQUE TRAS CEMENTER CASA-1P BLOQUE TRAS CEMENTER</t>
-  </si>
-  <si>
-    <t>DAVILA TENA FLOR MARIA</t>
-  </si>
-  <si>
-    <t>ESTUARDO JARAMILLO 0 Y VICTOR GARCIA GARCES</t>
-  </si>
-  <si>
-    <t>DAVILA TENA LILIANA TERESA</t>
-  </si>
-  <si>
-    <t>CESAR DAVILA GUERRA 0 Y ALBERTO SUAREZ DAVILA CDLA RUMI�AHUI/MIGRACION A GPON/ COSTO DE INSTALACION CDLA RUMI�AHUI/MIGRACION A GPON/ COSTO DE INSTALACION ALBERTO SUAREZ DAVILA</t>
-  </si>
-  <si>
-    <t>DINA EULALIA DAVILA ALVEAR</t>
-  </si>
-  <si>
-    <t>SINCHICO ANTONIO 334 Y ESTEBAN PERALTA UNA CUADRA ANTES DEL ESTADIO UNA CUADRA ANTES DEL ESTADIO</t>
-  </si>
-  <si>
-    <t>FLOR MARIA DAVILA TENA</t>
-  </si>
-  <si>
-    <t>LUIS GARZON PRADO 0 Y ESTUARDO JARAMILLO PEREZ casa verde de un piso casa verde de un piso ESTUARDO JARAMILLO PEREZ</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER ZEA DAVILA</t>
-  </si>
-  <si>
-    <t>BOLIVAR 1114 Y -- SALINAS</t>
-  </si>
-  <si>
-    <t>GALARZA DAVILA JOAQUIN ANIBAL</t>
-  </si>
-  <si>
-    <t>MORALES 505 Y SUCRE MORALES</t>
-  </si>
-  <si>
-    <t>GALARZA DAVILA LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>OTAVALO AVENIDA LOS CORAZAS 125</t>
-  </si>
-  <si>
-    <t>GALO ALEJANDRO PLAZAS DAVILA</t>
-  </si>
-  <si>
-    <t>VALLE DEL TAMBO 0 Y PANAMERICANA CONJUNTO SAN FRANCISCO /MIGRACION LINEA + INTERNET CONJUNTO SAN FRANCISCO /MIGRACION LINEA + INTERNET PANAMERICANA</t>
-  </si>
-  <si>
-    <t>HERMAN ALFREDO DAVILA PINTO</t>
-  </si>
-  <si>
-    <t>JUAN AGUILAR 0 Y LUIS CHAVEZ GUERRERO FRENTE IGLESIA SAN VICENTE FRENTE IGLESIA SAN VICENTE LUIS CHAVEZ GUERRERO</t>
-  </si>
-  <si>
-    <t>HILDA ELOIZA PAREDES DAVILA</t>
-  </si>
-  <si>
-    <t>OTAVALO BOLIVAR 708 Y J MONTALVO OTAVALO BOLIVAR</t>
-  </si>
-  <si>
-    <t>MARIA ELENA PUENTE DAVILA</t>
-  </si>
-  <si>
-    <t>ATAHUALPA 0Y Y COLLAHUAZO JUNTO EMPRESA ELECTRICA</t>
-  </si>
-  <si>
-    <t>ALEXANDRA MARCELA DAVILA CIFUENTES</t>
-  </si>
-  <si>
-    <t>LOS GALEANOS 0 Y LAS GARDENIAS CONJUNTO NUEVA ESPERANZA CASA H1 CONJUNTO NUEVA ESPERANZA CASA H1 LAS GARDENIAS</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>ALODIA MARGOTH ARAUJO DAVILA</t>
-  </si>
-  <si>
-    <t>AV EL RETORNO 0 Y QUILAGO QUILAGO</t>
-  </si>
-  <si>
-    <t>ANGEL ISMAEL DAVILA HERRERA</t>
-  </si>
-  <si>
-    <t>VIA AL ESTADIO 0 Y --- ESTADIO OLIMPICO VIA AL ESTADIO</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA OSWART JAVIER</t>
-  </si>
-  <si>
-    <t>JUAN DE LA ROCA 0 Y AVENIDA RICARDO SANCHEZ CASA 4 ATRAS DEL 911 CASA 4 ATRAS DEL 911 AVENIDA RICARDO SANCHEZ</t>
-  </si>
-  <si>
-    <t>IMBABURA PARROQ CUELLAJE CERCA PARQUE</t>
-  </si>
-  <si>
-    <t>BARAHONA DAVILA NELLY PATRICIA</t>
-  </si>
-  <si>
-    <t>IBARRA CIUDADELA LA VICTORIA MARCO TULIO NIETO SN</t>
-  </si>
-  <si>
-    <t>CADENA DAVILA FABRICIO ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAMON ALARCON 0 Y AV. JAIME ROLDOS AGUILERA AV. JAIME ROLDOS AGUILERA</t>
-  </si>
-  <si>
-    <t>CARMELA GORDILLO DAVILA</t>
-  </si>
-  <si>
-    <t>IBARRA ROCAFUERTE 14175</t>
-  </si>
-  <si>
-    <t>CARMEN ARCELIA ARAUJO DAVILA</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO JARAMILLO 0 Y 7 DE AGOSTO SUC IMB/474/ CERRAMIENTO DE MALLA SUC IMB/474/ CERRAMIENTO DE MALLA 7 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>CERON DAVILA JEFERSON ALEXIS</t>
-  </si>
-  <si>
-    <t>PARROQUIA PE�AHERRERA FRENTE AL ESTADIO 0Y Y SAGALAPAMBA SECTOR PE�AHERRERA/BARRIO SAGALAPAMBA/ FRENTE A CABA�ANAS MONSERRAT/CASA DE BLOQUE VISTO P1</t>
-  </si>
-  <si>
-    <t>CHIRIBOGA DAVILA SERGIO BOLIVAR</t>
-  </si>
-  <si>
-    <t>CHILE 275 Y BOLIVIA CASA GRIS CASA-GRIS DEL HOSPITAL DEL SEGURO CUATRO CUADRAS AL SUR, CASA 2 PISOS COLOR GRIS /ROJO</t>
-  </si>
-  <si>
-    <t>DAVILA AGUIRRE MARIA AUGUSTA</t>
-  </si>
-  <si>
-    <t>OBISPO LUIS PEREZ CALDERON 0 Y VICENTE ROCAFUERTE</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE LEONOR MAGDALENA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>IBARRA AVENIDA ELOY ALFARO 103</t>
-  </si>
-  <si>
     <t>DAVILA ANDRADE MERCEDES CECILIA DE LOS DOLORES</t>
   </si>
   <si>
-    <t>ALFARO ELOY 103 Y RODRIGUEZ CASA 103 CASA-103 ALFARO ELOY</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE NELSON ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN FRANCISCO BONILLA 740 Y AVENIDA ATAHUALPA SECTOR YACUCALLE SECTOR-YACUCALLE JUAN FRANCISCO BONILLA</t>
-  </si>
-  <si>
-    <t>DAVILA BAQUERIZO BYRON LEONARDO</t>
-  </si>
-  <si>
-    <t>MALDONADO 0 502 BOSURCO 502-BOSURCO 3RE PISO SECTOR SAN MARTIN</t>
-  </si>
-  <si>
-    <t>DAVILA BELTRAN LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>IBARRA OVIEDO 933 Y SANCHEZ Y CIFUENTES IBARRA OVIEDO</t>
-  </si>
-  <si>
-    <t>DAVILA BENAVIDES BLANCA LUCIA</t>
-  </si>
-  <si>
-    <t>PEDRO V MALDONADO 627</t>
-  </si>
-  <si>
-    <t>DAVILA BENAVIDES ROMMEL RICARDO</t>
-  </si>
-  <si>
-    <t>MALDONADO 627 Y GRIJALVA CASA 1P BALNCO Y CAFE CASA-1P BALNCO Y CAFE</t>
-  </si>
-  <si>
-    <t>DAVILA CARRERA LUIS ANIBAL</t>
-  </si>
-  <si>
-    <t>MEJIA 341 Y ROCAFUERTE</t>
-  </si>
-  <si>
-    <t>DAVILA DAVILA JUDITH MAGDALENA</t>
-  </si>
-  <si>
-    <t>JACINTO EGAS 481 Y CARLOS EMILIO GRIJALVA</t>
-  </si>
-  <si>
-    <t>DAVILA ESPINOSA RELICARIO DE ROMA</t>
-  </si>
-  <si>
-    <t>IBARRA OLMEDO 221 Y R TROYA IBARRA OLMEDO</t>
-  </si>
-  <si>
-    <t>DAVILA FLORES MILTON HONORATO</t>
-  </si>
-  <si>
-    <t>IBARRA CIUDADELA LA VICTORIA MZNA 19 CASA 19</t>
-  </si>
-  <si>
-    <t>DAVILA GONZALEZ NALDA MARISOL</t>
-  </si>
-  <si>
-    <t>AVENIDA PEREZ GUERRERO 650 Y BOLIVAR AVENIDA PEREZ GUERRERO</t>
-  </si>
-  <si>
-    <t>DAVILA GUZMAN EDWIN RODRIGO</t>
-  </si>
-  <si>
-    <t>BOLIVAR 887 Y VELASCO BOLIVAR</t>
-  </si>
-  <si>
-    <t>DAVILA HERRERA LUIS HERIBERTO VIDALIN</t>
-  </si>
-  <si>
-    <t>PE�AHERRERA 0 Y PARQUE CENTRAL CASA 1 PISO CELESTE A MEDIA CUADR DEL PARQUE CASA-1 PISO CELESTE A MEDIA CUADR DEL PARQUE</t>
-  </si>
-  <si>
-    <t>DAVILA HOLGUIN CARLOS AMADOR</t>
-  </si>
-  <si>
-    <t>BOLIVAR 679 Y OVIEDO EDIFICIO RUEDA 3ER PISO OFICIANA 109 EDIFICIO RUEDA-3ER PISO-OFICIANA-109</t>
-  </si>
-  <si>
-    <t>IBARRA CIUDADELA JARDIN ELIAS ALMEIDA 992 Y JUAN G JARAMILLO JARAMILLO</t>
-  </si>
-  <si>
-    <t>CARLOS ELIAS ALMEIDA 992 Y JUAN G JARAMILLO SECTOR CDLA EL JARDIN</t>
-  </si>
-  <si>
-    <t>DAVILA MALDONADO JORGE RAUL</t>
-  </si>
-  <si>
-    <t>PABLO VELA 518 Y CARLOS VILLACIS URBANIZACION NUEVO HOGAR URBANIZACION-NUEVO HOGAR CASA1PISO BLANCA IBARRA SCT AEROPUERTO DE LA IGLESIA A 100 MTROS</t>
-  </si>
-  <si>
-    <t>AVENIDA CAMILO PONCE ENRIQUE 0 Y CARLOS EMILIO GRIJALVA ESQUINA</t>
-  </si>
-  <si>
-    <t>DAVILA MONGE JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>IBARRA AVENIDA PEREZ GUERRERO 784</t>
-  </si>
-  <si>
-    <t>DAVILA MONTUFAR MARIA LUCRECIA BEATRIZ</t>
-  </si>
-  <si>
-    <t>IBARRA LA VICTORIA SEDA ETP MANZANA 22 CASA 418</t>
-  </si>
-  <si>
-    <t>DAVILA MORENO SILVANA MARIA</t>
-  </si>
-  <si>
-    <t>AVENIDA RICARDO SANCHEZ 825 Y SANCHEZ Y CIFUENTES PISO-3 AVENIDA RICARDO SANCHEZ</t>
-  </si>
-  <si>
-    <t>DAVILA NAVARRETE LUIS DAVID</t>
-  </si>
-  <si>
-    <t>IMBABURA PENAHERRERA PAR PRINCIPAL</t>
-  </si>
-  <si>
-    <t>DAVILA ONA SUSANA DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>SUCRE 1860 Y CARLOS EMILIO GRIJALVA TRAS EL ACROPOLIS TRAS EL-ACROPOLIS SUCRE</t>
-  </si>
-  <si>
-    <t>DAVILA OTERO MATILDE NOHEMI</t>
-  </si>
-  <si>
-    <t>PASAJE 5 SN 8 RIO QUILAGO CONJUNTO EL RETORNO MANZANA6B CASAAMARILLO 3 PISO CJTO-EL RETORNO-MZ-6B-CASA-AMARILLO 3 PS SECTOR EL RETORNO 2 CUADRAS ESCUELA TERESA VACQ</t>
-  </si>
-  <si>
-    <t>DAVILA PANTOJA MARIA JOSE</t>
-  </si>
-  <si>
-    <t>GENERAL MIHI 2 Y AV EL RETORNO CASA 2 PISOS COLOR BEIGE Y PLOMO SECTOR LA CANDELARIA CASA-2 PISOS COLOR BEIGE</t>
-  </si>
-  <si>
-    <t>DAVILA PAREDES MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>LUCILA BENALCAZAR 248 Y JOSE MIGUEL LEORO LUCILA BENALCAZAR</t>
-  </si>
-  <si>
-    <t>DAVILA PAREDES SEGUNDO MARCELO</t>
-  </si>
-  <si>
-    <t>DARIO EGAS GRIJALVA 0 Y Y OBISPO PASQUEL MONJE DARIO EGAS 0 Y OBISPO PASQUEL MONJE</t>
-  </si>
-  <si>
-    <t>DAVILA RIVADENEIRA NIDIA MARCELA</t>
-  </si>
-  <si>
-    <t>BOLIVAR 0 Y OVIEDO LOCAL 1 EDIFICIO WAY LOCAL-1 BOLIVAR</t>
-  </si>
-  <si>
-    <t>DAVILA RODAS FAUSTO XAVIER</t>
-  </si>
-  <si>
-    <t>ELEODORO AYALA 1106 Y CRISTOBAL GOMEZ JURADO</t>
-  </si>
-  <si>
-    <t>DAVILA RODAS MARIA ELENA</t>
-  </si>
-  <si>
-    <t>AVENIDA ATAHUALPA 14136 Y JOSE MIGUEL LEORO AVENIDA ATAHUALPA</t>
-  </si>
-  <si>
-    <t>DAVILA ROSALES JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CALLE PRINCIPAL SANTIAGO DEL REY 0 CASA 1 PISO COLOR BLANCA CASA-1 PISO COLOR BLANCA</t>
-  </si>
-  <si>
-    <t>DAVILA SAA JOSE IGNACIO</t>
-  </si>
-  <si>
-    <t>MIGUEL OVIEDO 933 Y CHICA NARVAEZ MIGUEL OVIEDO</t>
-  </si>
-  <si>
-    <t>OVIEDO 935</t>
-  </si>
-  <si>
-    <t>DAVILA SALAZAR LIVIA ELENA</t>
-  </si>
-  <si>
-    <t>RIO AGUARICO 666 Y RIO CHIMBO CASA 2P AMARILLA CASA-2P AMARILLA FRENTE HUERTO DE LIMONES</t>
-  </si>
-  <si>
-    <t>DAVILA SALAZAR MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>MALDONADO 1741 Y JUAN FRANCISCO BONILLA CASA 3 PISOS COLOR CASA 3 PISOS-COLOR MALDONADO</t>
-  </si>
-  <si>
-    <t>DAVILA TERAN MARIA CASTORINA</t>
-  </si>
-  <si>
-    <t>IBARRA AVENIDA ATAHUALPA 1639</t>
-  </si>
-  <si>
-    <t>DAVILA TORRES RAUL FERNANDO VINICIO</t>
-  </si>
-  <si>
-    <t>AV. ATAHUALPA 21330 Y -</t>
-  </si>
-  <si>
-    <t>DAVILA YEPEZ VERONICA ALEXANDRA</t>
-  </si>
-  <si>
-    <t>BRASIL 0 Y PARAGUAY BRASIL</t>
-  </si>
-  <si>
-    <t>ECHEVERRIA DAVILA KATIA PAULINA</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO GRIJALVA 0 Y Y ELEODORO AYALA Y RICARDO SANCHEZ CONDOMINIO SHALOM II CASA 15</t>
-  </si>
-  <si>
-    <t>FABRICIO ALEXANDER CADENA DAVILA</t>
-  </si>
-  <si>
-    <t>NELSON LOPEZ OBANDO 0 Y MARIANA DE JESUS PAREDES POR EL 2X1</t>
-  </si>
-  <si>
-    <t>FAUSTO MARCELO VILLEGAS DAVILA</t>
-  </si>
-  <si>
-    <t>PROLONGACI�N ROCAFUERTE 0 Y RIO CENEPA</t>
-  </si>
-  <si>
-    <t>FLORES DAVILA HILDA INES</t>
-  </si>
-  <si>
-    <t>EL TEJAR CALLE PRINCIPAL 0 Y NAZACOTA PUENTO EL TEJAR CALLE PRINCIPAL</t>
-  </si>
-  <si>
-    <t>GOMEZ DAVILA ALBERTO OLMEDO</t>
-  </si>
-  <si>
-    <t>TENA 820 Y CALLE TUNHURAGUA</t>
-  </si>
-  <si>
-    <t>GUERRERO DAVILA LUCIA MAGALI</t>
-  </si>
-  <si>
-    <t>IBARRA 513 Y Y MACAS</t>
-  </si>
-  <si>
-    <t>HERRERA DAVILA FELIPE RAFAEL</t>
-  </si>
-  <si>
-    <t>AVENIDA PEREZ GUERRERO 549 Y BOLIVAR AVENIDA PEREZ GUERRERO</t>
-  </si>
-  <si>
-    <t>CIUDADELA JARDIN SN</t>
-  </si>
-  <si>
-    <t>IBARRA CIUDADELA JARDIN JUAN GENARO JARAMILLO 419</t>
-  </si>
-  <si>
-    <t>TOBAR SUBIA 245 Y ELEODORO AYALA TOBAR SUBIA</t>
-  </si>
-  <si>
-    <t>HINOJOSA DAVILA FERNANDA MAGDALENA</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE BORJA 0 Y AV. VICTOR MANUEL GUZMAN INSTALAR 14:00PM// LLAMAR A 0998373130-0987662144-62953606</t>
-  </si>
-  <si>
-    <t>JAIME HUMBERTO FEDERICO DAVILA CARRERA</t>
-  </si>
-  <si>
-    <t>CIUDADELA DEL CHOFER SN Y PADRE ALBERTO HARO</t>
-  </si>
-  <si>
-    <t>LUCIA JACQUELINE DAVILA ALBORNOZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ Y CIFUENTES 0 Y AYACUCHO</t>
-  </si>
-  <si>
-    <t>MARGARITA SUSANA MENESES DAVILA</t>
-  </si>
-  <si>
-    <t>IBARRA LUIS GOMEZ JURADO 339 Y LUIS VARGAS TORRES IBARRA LUIS GOMEZ JURADO</t>
-  </si>
-  <si>
-    <t>MARIA ELENA DAVILA RODAS</t>
-  </si>
-  <si>
-    <t>MIGUEL OVIEDO 739 Y SIMON BOLIVAR EDIFICIO MUTUALISTA IMBABURA EDIFICIO MUTUALISTA IMBABURA SIMON BOLIVAR</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA VALLE DAVILA</t>
-  </si>
-  <si>
-    <t>ANTONIO JOSE DE SUCRE 0 Y TOBIAS MENA tras de la cooperativa bola amarilla tras de la cooperativa bola amarilla TOBIAS MENA</t>
-  </si>
-  <si>
-    <t>MARIA RAQUEL CARVALLO DAVILA</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE BORJA 0 Y VICTOR GOMEZ JURADO CASA 43 CASA-43 LUIS FELIPE BORJA</t>
-  </si>
-  <si>
-    <t>MARIO RAMIRO MENESES DAVILA</t>
-  </si>
-  <si>
-    <t>CALLE QUILAGO 0 CASA 10 - A CASA-10 - A COLINAS DEL RETORNO</t>
-  </si>
-  <si>
-    <t>MARTHA SUSANA DAVILA PAREDES</t>
-  </si>
-  <si>
-    <t>SUCRE 21103 Y TOBIAS MENA SECTOR BOLA AMARILLA</t>
-  </si>
-  <si>
-    <t>MENESES DAVILA HUGO ALFREDO</t>
-  </si>
-  <si>
-    <t>IBARRA FLORES Y SANCHEZ Y CIFUENTES ESQUINA</t>
-  </si>
-  <si>
-    <t>MONTALVO DAVILA PATRICIA ELIZABETH</t>
-  </si>
-  <si>
-    <t>CALLE LOS GALEANOS 0 Y AV MANUELA CA�IZARES SECTOR ELJIDO DE IBARRA CONJUNTO SANTA LUCIA</t>
-  </si>
-  <si>
-    <t>NAVARRO DAVILA JULIO CESAR</t>
-  </si>
-  <si>
-    <t>IBARRA URBANIZACION JOSE M LEORO CALLE 6 164</t>
-  </si>
-  <si>
-    <t>NIETO DAVILA NANCY RUBY</t>
-  </si>
-  <si>
-    <t>CIUDADELA JARDIN CALLE 26 SN</t>
-  </si>
-  <si>
-    <t>NIETO DAVILA WILSON EDMUNDO</t>
-  </si>
-  <si>
-    <t>CARLOS ELIAS ALMEIDA 9104 Y GENARO JARAMILLO CARLOS ELIAS ALMEIDA</t>
-  </si>
-  <si>
-    <t>IBARRA ELIAS ALMEIDA 9104</t>
-  </si>
-  <si>
-    <t>IBARRA CIUDADELA JARDIN ELIAS ALMEIDA 9104</t>
-  </si>
-  <si>
-    <t>OREJUELA DAVILA GUILLERMO JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>IBARRA AVENIDA VICTOR M GUZMAN 332</t>
-  </si>
-  <si>
-    <t>ORQUERA DAVILA LORENA ANA CECILIA</t>
-  </si>
-  <si>
-    <t>ELEODORO AYALA 110 Y JORGE DAVILA MEZA CLINICA IBARRA PISO 3 CONSULTORIOS CLINICA IBARRA-PISO 3 ELEODORO AYALA</t>
-  </si>
-  <si>
-    <t>OSCAR EFREN HERRERA DAVILA</t>
-  </si>
-  <si>
-    <t>RAFAEL TROYA 655 Y AVENIDA CRISTOBAL DETROYA RAFAEL TROYA</t>
-  </si>
-  <si>
-    <t>AVENIDA MARIANO ACOSTA 0 Y CALLE SIN NOMBRE AVENIDA MARIANO ACOSTA</t>
-  </si>
-  <si>
-    <t>DAVILA CEVALLOS SILVIA MARGOTH</t>
-  </si>
-  <si>
-    <t>MAGDALENA BAJO 0 Y CALLE S/N MAS ARRIAB DE TANQUES DE AGUA MAGDALENA BAJO</t>
-  </si>
-  <si>
-    <t>GARCIA MORENO IMBABURA</t>
-  </si>
-  <si>
-    <t>ANGULO DAVILA JAMES OLGUIN</t>
-  </si>
-  <si>
-    <t>VIA EL ROSARIIO 0 Y CALLE SIN NOMBRE VIA EL ROSARIIO</t>
-  </si>
-  <si>
-    <t>CUELLAJE</t>
-  </si>
-  <si>
-    <t>ANGULO DAVILA JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>ELOISA ALVAREZ 0 Y 21 DE NOVIEMBRE ELOISA ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANGULO DAVILA MARSOVIA MARIBEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO AYALA 0 Y VIA SAN JOAQUIN ESQUINA ALEJANDRO AYALA</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA LIBA CARMEN VICTORIA</t>
-  </si>
-  <si>
-    <t>CALLE PRINCIPAL 0 Y CALLE SIN NOMBRE VIA AL CEMENTERIO CUELLAJE ALTO CALLE PRINCIPAL</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA ROSA MERCEDES</t>
-  </si>
-  <si>
-    <t>VIA EL ROSARIIO 0 Y CALLE SIN NOMBRE CASA EN LO ALTO DE LA VIA LOCALIDDA LA MAGDALENA VIA EL ROSARIIO</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA WILMAN GIOVANI</t>
-  </si>
-  <si>
-    <t>VIA PRINCIAL A LA MAGDALENA 0 Y VIA AL ROSARIO CASA DE UN PISO FACHADA DE CERAMICA CASA-DE UN PISO VIA PRINCIAL A LA MAGDALENA</t>
-  </si>
-  <si>
-    <t>DAVILA ANGULO HERMOGENES ALFREDO</t>
-  </si>
-  <si>
-    <t>VIA PRINCIAL A LA MAGDALENA 0 Y VIA AL ROSARIO BARRIO LA MAGDALENA VIA AL ROSARIO VIA PRINCIAL A LA MAGDALENA</t>
-  </si>
-  <si>
-    <t>DAVILA NOGALES HERALDO JUSTINO</t>
-  </si>
-  <si>
-    <t>VIA A LA MAGDALENA 0 Y VIA EL ROSARIIO CASA DE UN PISO DE BLOQUE Y TEJA CASA-DE UN PISO DE BLOQUE VIA A LA MAGDALENA</t>
-  </si>
-  <si>
-    <t>MARCO IVAN AYALA DAVILA</t>
-  </si>
-  <si>
-    <t>VIA EL ROSARIIO 0 Y CALLE SIN NOMBRE CASA 1 PISO DE ETERNIT LOCALIDAD LA MAGDALENA VIA EL ROSARIIO</t>
-  </si>
-  <si>
-    <t>HARO DAVILA PEDRO MIGUEL ERMENEGILDO</t>
-  </si>
-  <si>
-    <t>COTACACHI PARR QUIROGA BARRIO LA VICTORIA VIA DON BOSCO</t>
-  </si>
-  <si>
-    <t>COTACACHI</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA MIGUEL ANGEL BOLIVAR</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI JUAN DE VELASCO 0886</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI</t>
-  </si>
-  <si>
-    <t>ARAUJO DAVILA LUCIA MATILDE</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ SN 0 21 DE NOVIEMBRE CasaAZUL 2PISOS CASA-AZUL 2PISOS---- SEC ANDRADE MARIN BRR CENTRAL 1 CUADRA DEL PARQUE MARIN</t>
-  </si>
-  <si>
-    <t>CADENA DAVILA KAREN DOMINIC</t>
-  </si>
-  <si>
-    <t>GONZALEZ SUAREZ 0 Y BOLIVAR GONZALEZ SUAREZ</t>
-  </si>
-  <si>
-    <t>CRISTIAN PAUL CADENA DAVILA</t>
-  </si>
-  <si>
-    <t>BOLIVAR 0 Y AV. PICHINCHA</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE JAIME PATRICIO</t>
-  </si>
-  <si>
-    <t>CALLE S/N 0 Y B. MIRADOR CALLE S/N CALLE S/N</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE LUIS ROBERTO</t>
-  </si>
-  <si>
-    <t>ABDON CALDERON 944 Y JUNIN ABDON CALDERON</t>
-  </si>
-  <si>
-    <t>DAVILA BELTRAN JOSE LINO</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI PENIAHERRERA SN Y GENERAL ENRIQUEZ ESQUINA</t>
-  </si>
-  <si>
-    <t>DAVILA BRAVO SEGUNDO CARLOS</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI ATAHUALPA S/N Y ROCAFUERTE ATUNTAQUI ATAHUALPA</t>
-  </si>
-  <si>
-    <t>ATAHUALPA 841 Y ROCAFUERTE ATAHUALPA</t>
-  </si>
-  <si>
-    <t>DAVILA CADENA SANDRA LUCIA</t>
-  </si>
-  <si>
-    <t>JUAN MONTALVO 0 Y QUITO JUAN MONTALVO</t>
-  </si>
-  <si>
-    <t>DAVILA CALDERON DANNY PAUL</t>
-  </si>
-  <si>
-    <t>JOSE IGNACIO PE�AHERRERA 0 Y GENERAL ENRIQUEZ CASA 2 PISOS ROSADA EN LA PARTE DE ATRAS DIAGONAL AL PARQUE SECTOR ANDRADE MARIN CASA-2 PISOS ROSADA EN LA JOSE IGNACIO PE�AHERRERA</t>
-  </si>
-  <si>
-    <t>DAVILA CALDERON JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI GONZALEZ SAUREZ SN Y PABNMERICANA ATUNTAQUI GONZALEZ SAUREZ SN</t>
-  </si>
-  <si>
-    <t>DAVILA CALUQUI LUIS ARTURO</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ 1109 Y ATAHUALPA ANDRADE MARIN</t>
-  </si>
-  <si>
-    <t>DAVILA CEVALLOS FABIOLA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI DALMAO SN Y GENERAL ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>DAVILA ENCALADA EMMA VIOLETA</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI OLMEDO SN Y ESPEJO</t>
-  </si>
-  <si>
-    <t>DAVILA ESPINOSA ANA LUISA</t>
-  </si>
-  <si>
-    <t>GONZALEZ SUAREZ 2109 Y ELOY ALFARO GONZALEZ SUAREZ</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ 0 Y BOLIVAR</t>
-  </si>
-  <si>
-    <t>BOLIVAR 1222 Y AMAZONAS BARRIO CENTRAL BOLIVAR</t>
-  </si>
-  <si>
-    <t>DAVILA ESPINOSA RUBI DE SANTA MONICA</t>
-  </si>
-  <si>
-    <t>LUIS OLMEDO JATIVA 0 Y AV LUIS LEORO FRANCO</t>
-  </si>
-  <si>
-    <t>DAVILA GARZON CARLOS RAMIRO</t>
-  </si>
-  <si>
-    <t>BOLIVAR SN 1341 OLMEDO CasaROSADA 2 PISOS CASA-ROSADA 2 PISOS---- BARRIO SANTA ANA JUNTO A AGENCIA DE ANDINATEL</t>
-  </si>
-  <si>
-    <t>DAVILA GARZON ELSA IRALDA</t>
-  </si>
-  <si>
-    <t>JUAN MONTALVO 970 Y GONZALEZ SUAREZ CASA DURAZNO JUAN MONTALVO</t>
-  </si>
-  <si>
-    <t>DAVILA GARZON PACO ANIBAL</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI PLAZA LIBERTAD SN</t>
-  </si>
-  <si>
-    <t>DAVILA GARZON PIEDAD MAGDALENA</t>
-  </si>
-  <si>
-    <t>GONZALEZ SUAREZ 7 Y ALEJANDRO ANDRADE CONDOMINIO PLAZA CENTRO CONDOMINIO-PLAZA CENTRO GONZALEZ SUAREZ</t>
-  </si>
-  <si>
-    <t>DAVILA GUEVARA MARIANITA DE JESUS</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI GENERAL ENRIQUEZ 1230 ENTRE SUCRE Y BOLIVAR</t>
-  </si>
-  <si>
-    <t>DAVILA GUEVARA PEDRO JORGE</t>
-  </si>
-  <si>
-    <t>2 DE MARZO 1526 Y ESPEJO 2 DE MARZO</t>
-  </si>
-  <si>
-    <t>DAVILA HINOJOSA GLORIA MARIA</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ 5- 1356 Y Y PEREZ MU�OZ ALTOS ALMACEN DCACHE ALTOS ALMACEN DCACHE PEREZ MU�OZ</t>
-  </si>
-  <si>
-    <t>DAVILA LEON MARIA</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI GARCIA MORENO SN Y GONZALEZ SUAREZ</t>
-  </si>
-  <si>
-    <t>DAVILA MALITAXI INES GERMANIA</t>
-  </si>
-  <si>
-    <t>21 DE NOVIEMBRE 1027 BARRIO CENTRAL BRR-CENTRAL</t>
-  </si>
-  <si>
-    <t>DAVILA MARINA MARINA LEONOR</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ 0Y DALMAU ESQUINA SECTOR ANDRADE MARIN DALMAU-ESQUINA-SECTOR ANDRADE-MARIN</t>
-  </si>
-  <si>
-    <t>DAVILA MARROQUIN SONIA JAQUELINE</t>
-  </si>
-  <si>
-    <t>RIO FRIO 0 Y IMBABURA BARRIO CENTRAL BARRIO-CENTRAL RIO FRIO</t>
-  </si>
-  <si>
-    <t>DAVILA MARTINEZ CIA LTDA</t>
-  </si>
-  <si>
-    <t>AVENIDA JULIO MIGUEL AGUINAGA 1339 Y OLMEDO AVENIDA JULIO MIGUEL AGUINAGA</t>
-  </si>
-  <si>
-    <t>DAVILA MARTINEZ CRISTIAN ANDRES</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ 320 Y BOLIVAR VINUEZA</t>
-  </si>
-  <si>
-    <t>DAVILA POSSO CARMEN AMELIA</t>
-  </si>
-  <si>
-    <t>PEREZ MU�OZ 1115 Y GENERAL ENRIQUEZ PEREZ MU�OZ</t>
-  </si>
-  <si>
-    <t>DAVILA POSSO EDWIN MAURICIO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO ANDRADE 1137 Y AVENIDA RIO AMAZONAS Y GENERAL ENRIQUEZ FRENTE A CONFECC MISHEL Y GRAL. ENRIQUEZ-FRENTE A CONFECC-MISHEL-. ALEJANDRO ANDRADE</t>
-  </si>
-  <si>
-    <t>DAVILA POSSO MARIA ANGELICA MATILDE</t>
-  </si>
-  <si>
-    <t>GENERAL ENRIQUEZ 11106</t>
-  </si>
-  <si>
-    <t>DAVILA POZO MARTHA CECILIA</t>
-  </si>
-  <si>
-    <t>AV. JULIO MIGUEL AGUINAGA 318 Y OLMEDO</t>
-  </si>
-  <si>
-    <t>DAVILA PULLAS LORENA MARIVEL</t>
-  </si>
-  <si>
-    <t>LUIS OLMEDO JATIVA 0 Y AV. LUIS LEORO FRANCO</t>
-  </si>
-  <si>
-    <t>DAVILA SEVILLA FANNY GUADALUPE</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI GENERAL ALBERTO ENRIQUEZ SN Y ATAHUALPA</t>
-  </si>
-  <si>
-    <t>DAVILA SILVA ESPERANZA DE JESUS</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI RIOFRIO SN Y PARQUE 9 DE OCTUBRE</t>
-  </si>
-  <si>
-    <t>DAVILA TERAN JAIME NEPTALI</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI JUNIN SN Y ABDON CALDERON</t>
-  </si>
-  <si>
-    <t>DAVILA TERAN MANUEL ARTURO</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI JUNIN 641</t>
-  </si>
-  <si>
-    <t>DAVILA TERAN MARIANITA DE JESUS</t>
-  </si>
-  <si>
-    <t>ATUNTAQUI ANDRADE MARIN 21 NOVIEMBRE SN</t>
-  </si>
-  <si>
-    <t>DIEGO FERNANDO DAVILA ARCINIEGA</t>
-  </si>
-  <si>
-    <t>12 DE FEBRERO 0 Y AVENIDA SIMON BOLIVAR CASA DE 2P COLOR CREMA, PORTON NEGRO, FRENTE ESCUELA 2 DE MARZO CASA DE 2P COLOR CREMA, PORTON NEGRO, FRENTE ESCUELA 2 DE MARZO AVENIDA SIMON BOLIVAR</t>
-  </si>
-  <si>
-    <t>JATIVA DAVILA GERMAN ALFREDO</t>
-  </si>
-  <si>
-    <t>ATAHUALPA 832 Y OLMEDO ATAHUALPA</t>
-  </si>
-  <si>
-    <t>JATIVA DAVILA LUISA HERMELINDA</t>
-  </si>
-  <si>
-    <t>ALF BOADA 1030</t>
-  </si>
-  <si>
-    <t>LUIS ARTURO PAEZ DAVILA</t>
-  </si>
-  <si>
-    <t>CALLE 14 0 Y LUIS HIDROVO LUIS HIDROVO</t>
-  </si>
-  <si>
-    <t>MARCIA YOLANDA DE LOURDES DAVILA GARZON</t>
-  </si>
-  <si>
-    <t>GONZALES SUAREZ 0 Y JUAN MONTALVO CASA 3 PISOS AMARILLA ESQUIN CASA-3 PISOS AMARILLA ESQUIN</t>
-  </si>
-  <si>
-    <t>DAVILA CARRILLO GLADYS TERESA</t>
-  </si>
-  <si>
-    <t>CALLE PRINCIPAL 0 Y AMBUQUI A 1 CUADRA DELCONJUNTO PARAISO</t>
-  </si>
-  <si>
-    <t>AMBUQUI</t>
-  </si>
-  <si>
-    <t>CARLOS JACINTO DAVILA DAVILA</t>
-  </si>
-  <si>
-    <t>JOSE PE�AHERRERA 0 Y CRISTOBAL COLON</t>
-  </si>
-  <si>
-    <t>DAVILA ARCINIEGA CARLOS ANDRES</t>
-  </si>
-  <si>
-    <t>RAFAEL SANCHEZ 0 Y JUAN FRANCISCO BONILLA CASA 1 PISO ESQUINERA COLOR NEGRO CASA-1 PISO ESQUINERA COLOR</t>
-  </si>
-  <si>
-    <t>DAVILA MERINO PEDRO RAFAEL</t>
-  </si>
-  <si>
-    <t>LUIS DAVILA PEREZ 0 Y REINALDO CHAVEZ CASA 2 PS COLOR BLANCA CON NEGRO PORTON GRIS CASA 2 PS COLOR-BLANCA CON NEGRO</t>
-  </si>
-  <si>
-    <t>DAVILA MONTUFAR HECTOR HOLGER</t>
-  </si>
-  <si>
-    <t>DR. LUIS DAVILA PEREZ 0 Y REINALDO CHAVEZ YUYUCOCHA CASA DE DOS PISOS</t>
-  </si>
-  <si>
-    <t>DAVILA PASQUEL VANESSA</t>
-  </si>
-  <si>
-    <t>CDLA. ANGEL ESCOBAR 0Y Y CALLE D FRENTE CABA�AS HACIENDA</t>
-  </si>
-  <si>
-    <t>DIAZ DAVILA NORMA ELIZABETH</t>
-  </si>
-  <si>
-    <t>CALLE G 0 Y CALLE D CASA TOMATE CON PORTON BLANCO 1 PISO TERRAZA - CASA TOMATE CON-PORTON BLANCO-1 PISO TERRAZA-- CALLE G</t>
-  </si>
-  <si>
-    <t>MARIANA DE JESUS CABRERA DAVILA</t>
-  </si>
-  <si>
-    <t>QUINTA EL OLIVO 0 BARRIO SANTA MARIANITA</t>
-  </si>
-  <si>
-    <t>NATALY JOHANNA DAVILA FREIRE</t>
-  </si>
-  <si>
-    <t>AUTOPISTA YAHUARCOCHA 0 Y CALLE STA. MARIANITA</t>
+    <t>GALARZA DAVILA JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>NOVENA TRANSVERSAL 30 Y INTERVALLES NOVENA TRANSVERSAL</t>
+  </si>
+  <si>
+    <t>TUMBACO</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA SERGIO FRANCISCO</t>
+  </si>
+  <si>
+    <t>CALLE 1 0L Y CALLE 3 LOS ARUPOS S4-75 RUTA VIVA KM 8 TORRE A SAIN JOSEPH 305A TUMBACO LOS ARUPOS S4-75 RUTA VIVA KM 8 TORRE A SAIN JOSEPH 305A TUMBACO</t>
+  </si>
+  <si>
+    <t>CARLOS GUILLERMO DAVILA ARREGUI</t>
+  </si>
+  <si>
+    <t>ABDON CALDERON 0 L Y GONZALO DE VERA</t>
+  </si>
+  <si>
+    <t>DAVILA AGUILERA LUCRECIA MERCEDES</t>
+  </si>
+  <si>
+    <t>CAMINO DE LA VI�A 0 CONJUNTO ACANTHUS CASA 2 SECTOR LA VI�A TUMBACO JUANTO A CASETA DE LOS GUARDIAS CJT ACANTHUS-CASA 2-SECT LA VI�A-TUMBACO-JUANTO A CASETA-DE LOS GUARDIAS</t>
+  </si>
+  <si>
+    <t>ALBA DEL ROCIO DAVILA BAQUERO</t>
+  </si>
+  <si>
+    <t>ZARUMA 7N Y GENERAL RUMI�AHUI SECTOR EL RANCHO CONJ VICTTORIA CASA B7 SECTOR EL RANCHO CONJ VICTTORIA CASA B7</t>
+  </si>
+  <si>
+    <t>SANGOLQUI</t>
+  </si>
+  <si>
+    <t>ANDREA DAVILA VINTIMILLA</t>
+  </si>
+  <si>
+    <t>12 DE FEBRERO 0L 27 DE FEBRERO CONJUNTO EL CANELO CASA 8 27 DE FEBRERO CONJUNTO EL CANELO CASA 8</t>
+  </si>
+  <si>
+    <t>ARIAS DAVILA IVONNE ALEXANDRA</t>
+  </si>
+  <si>
+    <t>REINALDO FLOR 1L Y ANTONIO TANDAZO</t>
+  </si>
+  <si>
+    <t>AVILA DAVILA CESAR AUGUSTO</t>
+  </si>
+  <si>
+    <t>SELVA ALEGRE JATUMPUNGO AVENIDA ATAHUALPA 1087</t>
+  </si>
+  <si>
+    <t>BLANCA CECILIA DAVILA GUALOTU�A</t>
+  </si>
+  <si>
+    <t>AV JUAN SALINAS 0 Y NICOLAS PE�A BARRIO SELVA ALEGRE FRENTE AL COMPLEJO LA CASCADA</t>
+  </si>
+  <si>
+    <t>SANGOLQUI BARRIO INCHALILLO AUTOPISTA GENERAL RUMINIAHUI LOTE 11 E INES GANGOTENA JIJON</t>
+  </si>
+  <si>
+    <t>DAVILA ALVAREZ ELSA CECILIA</t>
+  </si>
+  <si>
+    <t>PASTAZA S21- 224 MANUEL CORDOVA GALARZA CASA 1 PISO CASA LADRILLO VISTO CASA-1 PISO-CASA-LADRILLO VISTO-- BARRIO SAN FRANCISCO DE CONOCOTO SECTOR EXTREMO SUR OCCIDENTAL A LADO DE CAPILLA</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE CARLOS HUMBERTO</t>
+  </si>
+  <si>
+    <t>CLUB LOS CHILLOS NARDOS LOTE 407</t>
+  </si>
+  <si>
+    <t>ASTUDILLO DAVILA FANNY LETICIA</t>
+  </si>
+  <si>
+    <t>LAS ALONDRAS 0 Y AV ILALO (CONJUNTO VALENCIA PLAZA CASA 22)</t>
+  </si>
+  <si>
+    <t>SAN RAFAEL</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO HARO DAVILA</t>
+  </si>
+  <si>
+    <t>ISLA PUNA 2L Y ISLA RABIDA</t>
+  </si>
+  <si>
+    <t>ALMEIDA DAVILA LUIS ULPIANO</t>
+  </si>
+  <si>
+    <t>SAN JOSE DE MINAS CALLE ANTONIO FLORES SN Y ELOY ALFARO</t>
+  </si>
+  <si>
+    <t>SAN JOSE DE MINAS</t>
+  </si>
+  <si>
+    <t>BURBANO DAVILA MARIA DE LAS MERCEDES FRANCISC</t>
+  </si>
+  <si>
+    <t>ALBERTO FREILE 0L HACIENDA LA VICTORIA HACIENDA- LA VICTORIA</t>
+  </si>
+  <si>
+    <t>CABEZAS DAVILA JOSE ENRIQUE</t>
+  </si>
+  <si>
+    <t>GARCIA MORENO SN 0 HERMANO MIGUEL CASACELESTE 2 PISOS CASA-CELESTE 2PS---- SECTOR 14 DE SEPTIEMBRE FRENTE DE LA ESCUELA CUMANDA</t>
+  </si>
+  <si>
+    <t>DAVILA ALARCON DAYSI JACQUELINE</t>
+  </si>
+  <si>
+    <t>LULUBAMBA 19Y Y ACURIA CND PARIS II CASA 1</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO DE PICHINCHA</t>
+  </si>
+  <si>
+    <t>DAVILA ALBAN JORGE ANTONIO</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO CALLE SN 200 METROS AL SUR DEL COLEGIO V DEL CONSUELO</t>
+  </si>
+  <si>
+    <t>DAVILA ANGELICA ANDRADE DE</t>
+  </si>
+  <si>
+    <t>AV. EQUINOCCIAL 0A Y AV. 13 DE JUNIO</t>
+  </si>
+  <si>
+    <t>CRESPO DAVILA GRACIELA JOHANNE</t>
+  </si>
+  <si>
+    <t>PASAJE E 276 ENTRE PASAJE I Y AVENIDA MARIANA DE JESUS COOPERATIVA JULIO ZABALA ENTRE PASAJE I Y-AV MARIANA DE-JESUS COOP JULIO-ZABALA</t>
+  </si>
+  <si>
+    <t>ROCAFUERTE (ESMERALDAS)</t>
+  </si>
+  <si>
+    <t>ACOSTA DAVILA RAFAEL ENRIQUE MANUEL</t>
+  </si>
+  <si>
+    <t>AVENIDA 10 DE AGOSTO 5019</t>
+  </si>
+  <si>
+    <t>QUITO</t>
+  </si>
+  <si>
+    <t>AGUILAR DAVILA GEORGINA PURIFICACION</t>
+  </si>
+  <si>
+    <t>LIZARDO RUIZ OE4- 747 DIEGO DE TAPIA ----- SECTOR BANCO DEL PICHINCHA BARRIO COTOCOLLAO TIENDA VIVERES EN GENERAL COLOR MOSTAZA 1PISO</t>
+  </si>
+  <si>
+    <t>AGUINAGA DAVILA CARLOS ANIBAL</t>
+  </si>
+  <si>
+    <t>PASAJE 6B-N69- 18 Y FRANCISCO DALMAU EDIFICIO VENTURA PISO 4 DEPARTAMENTO PH2 EDF-VENTURA-PISO-4-DEPT-PH2 SECTOR URB MARISOL</t>
+  </si>
+  <si>
+    <t>AGUINAGA DAVILA CECILIA VIOLETA</t>
+  </si>
+  <si>
+    <t>CTLL CONJUNTO HABT MABEREY CASA 15 AVENIDA DE LA PRENSA ENTRE GUALAQUIZA Y VALVERDE</t>
+  </si>
+  <si>
+    <t>AGUINAGA DAVILA FAUSTO MARINO</t>
+  </si>
+  <si>
+    <t>CALLE N74B E4-67 CERCA DE JOAQUIN MANCHENO Y ELOY ALFARO PANAMERICANA NORTE KILOMETRO 7 1/2 PANAMERICANA NORTE KM 7 1/2</t>
+  </si>
+  <si>
+    <t>AGUINAGA DAVILA JOSE MARIA</t>
+  </si>
+  <si>
+    <t>CARCELEN ALTO CALLE JOAQUIN MANCHENO E/4 65 Y AVENIDA ELOY ALFARO CARCELEN ALTO CALLE JOAQUIN MANCHENO E/4</t>
+  </si>
+  <si>
+    <t>ALBA ELIZABETH DAVILA ANDRADE</t>
+  </si>
+  <si>
+    <t>JOSE ARAGON OE3- 66 Y Y SALVADOR BRAVO solanda solanda SALVADOR BRAVO</t>
+  </si>
+  <si>
+    <t>ALEGRIA DAVILA BELGICA NIEVES ESTHER</t>
+  </si>
+  <si>
+    <t>SECTOR 1 SPMZ 3 MANZANA N CASA 2</t>
+  </si>
+  <si>
+    <t>ALEGRIA DAVILA BLANCA ELICIA</t>
+  </si>
+  <si>
+    <t>SECTOR LA ISLA MANZANA 3 CASA 18 PASAJE F</t>
+  </si>
+  <si>
+    <t>ALEXANDER PATRICIO DAVILA GRANIZO</t>
+  </si>
+  <si>
+    <t>CALLE 8 N67 148 Y FRANCISCO DALMAU URBANIZACION MAR Y SOL EDIFICIO SARA MARIA DEPARTAMENTO 2 URB MAR Y SOL-EDF SARA MARIA-DPTO-2 CALLE 8 N67</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO DAVILA SYLVITA MIREYA</t>
+  </si>
+  <si>
+    <t>MXA CONJUNTO XIMENA DEL ESTE CASA C SABANILLA Y MELCHOR TOAZA</t>
+  </si>
+  <si>
+    <t>ALVARADO DAVILA LUCIA EUGENIA</t>
+  </si>
+  <si>
+    <t>ESTOCOLMO 0 Y AVENIDA RIO AMAZONAS</t>
+  </si>
+  <si>
+    <t>ALVARADO DAVILA OSCAR MAURICIO</t>
+  </si>
+  <si>
+    <t>AVENIDA GASPAR DE VILLAROEL 1100 Y AVENIDA 6 DE DICIEMBRE CONJUNTO PARQUE REAL TORRE NOGAL 1 DEPARTAMENTO 84 AVENIDA GASPAR DE VILLAROEL</t>
+  </si>
+  <si>
+    <t>ALVAREZ DAVILA SILVIA KARINA</t>
+  </si>
+  <si>
+    <t>GUALAQUIZA OE4 88 Y AVENIDA DE LA PRENSA GUALAQUIZA OE4</t>
+  </si>
+  <si>
+    <t>AMORES DAVILA JOSE ARMANDO</t>
+  </si>
+  <si>
+    <t>FDC CN INQ CALLE LA TIERRA 358 Y AVENIDA DE LOS SHYRIS FDC CN INQ CALLE LA TIERRA</t>
+  </si>
+  <si>
+    <t>ANA KARIM ELIZABETH DAVILA CAICEDO</t>
+  </si>
+  <si>
+    <t>ANTONIO GRANDA CENTENO 0 Y ALVAREZ DEL CORRO EDIFICIO MANSION II / DEPARTAMENTO 501A EDIFICIO MANSION II / DEPARTAMENTO 501A ALVAREZ DEL CORRO</t>
+  </si>
+  <si>
+    <t>ANA LUCIA DAVILA PASTOR</t>
+  </si>
+  <si>
+    <t>AVIGIRAS 0Y Y DE LOS GUAYACANES EDIFICIO AMANECER, LOTE 241, PISO 3, DEPARTAMENTO 3 EDIFICIO AMANECER, LOTE 241, PISO 3, DEPARTAMENTO 3</t>
+  </si>
+  <si>
+    <t>ANA MARIA DAVILA LOPEZ</t>
+  </si>
+  <si>
+    <t>AVENIDA DE LA PRENSA 146 Y Y EDMUNDO CARVAJAL PASAJE ERNESTO MU�OZ PASAJE ERNESTO MU�OZ EDMUNDO CARVAJAL</t>
+  </si>
+  <si>
+    <t>A�AZCO DAVILA SARA BEATRIZ</t>
+  </si>
+  <si>
+    <t>INQ URBANIZACION INECEL CALLE A LOTE 15 Y DE LOS MOTILONES</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA CARLOS ARTURO</t>
+  </si>
+  <si>
+    <t>DIOGENES PAREDES PB D13 C1A</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>AVENIDA 9 DE OCTUBRE 729 PB ENTRE RAMIREZ DAVALOS Y VEINTIMILLA</t>
+  </si>
+  <si>
+    <t>ANDRADE DAVILA VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS TAMAYO 0 IGNACIO DE VEINTIMILLA EDIF TIZIANO PISO 7 DPTO 7E IGNACIO DE-VEINTIMILLA-EDIF TIZIANO-PISO 7 DPTO 7E SECT MARISCAL</t>
+  </si>
+  <si>
+    <t>AZCUNAGA 344 Y AVENIDA BRASIL EDIFICIO AQUAZUL PISO CUARTO DEPARTAMENTO 4C EDIFICIO-AQUAZUL-PISO-CUARTO-DEPARTAMENTO-4C AZCUNAGA</t>
+  </si>
+  <si>
+    <t>MARIANO HURTADO 175L Y ANTONIO ROMAN EDIF LA RIOJA-PISO 7-DEPT 7D-SECT MARISCAL-DEPT 7D-SECT MARISCAL MARIANO HURTADO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS TAMAYO 0 IGNACIO DE VEINTIMILLA EDIF TIZIANO PB LOCAL 3 IGNACIO DE-VEINTIMILLA-EDIF TIZIANO PB-LOCAL 3 SECT MARISCAL</t>
+  </si>
+  <si>
+    <t>ANDRADE ELDA DAVILA DE</t>
+  </si>
+  <si>
+    <t>SAN GREGORIO 270</t>
+  </si>
+  <si>
+    <t>ANDREA FERNANDA GRIJALVA DAVILA</t>
+  </si>
+  <si>
+    <t>DE LAS ANONAS 0 Y E12A esquinera en un edificio de 4 pisos esquinera en un edificio de 4 pisos E12A</t>
+  </si>
+  <si>
+    <t>ANDREA SOLEDAD GOMEZ DAVILA</t>
+  </si>
+  <si>
+    <t>SEYMUR SN</t>
+  </si>
+  <si>
+    <t>ANDRES VICENTE PRADO DAVILA</t>
+  </si>
+  <si>
+    <t>GUANGUILTAGUA N39 36 Y TOMAS BERMUR EDIF VISTA REAL PISO 3 DPTO 301 SECT PARQUE METROPOLITANO AL PISO 3 DPTO 301 SECT PARQUE METROPOLITANO</t>
+  </si>
+  <si>
+    <t>ANGELICA CRISTINA DAVILA PORTUGAL</t>
+  </si>
+  <si>
+    <t>JORGE GONZALEZ 0 Y CALLE RODRIGO MURIEL CONJ BRISAS DE CRISTAL BLOQUE C DPTO C23 SECTOR I�AQUITO ALTO FRENTE AL BOSQUE CONJ BRISAS DE CRISTAL BLOQUE C DPTO C23 SECTOR I�AQUITO ALTO FRENTE AL BOSQUE CALLE RODRIGO MURIEL</t>
+  </si>
+  <si>
+    <t>ANGULO DAVILA GLORIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>RAMIREZ DAVALOS E3- 42 Y AVENIDA 9 DE OCTUBRE EDIFICIO CONSULTORIO S MEDICOS ASOCIA PISO 6 CONSULTORIO 23 EDIF CONSULTORIO-S MEDICOS ASOCIA-PISO 6-CONSULTORIO 23 RAMIREZ DAVALOS E3-</t>
+  </si>
+  <si>
+    <t>ANIBAL AURELIANO SILVA DAVILA</t>
+  </si>
+  <si>
+    <t>RAFAEL CALVACHE N 954 Y Y LEONIDAS PUEBLA CJNT VENTURADA 2 PISO 3 CJNT VENTURADA 2 PISO 3 LEONIDAS PUEBLA</t>
+  </si>
+  <si>
+    <t>ARAUJO DAVILA CESAR AUGUSTO</t>
+  </si>
+  <si>
+    <t>EDIFICIO CIUDAD DE QUITO OFICINA 806 P8 AVENIDA NACIONES UNIDAS 193 Y AVENIDA 10 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>FERRUZOLA 0 CASA OE7-31 Y CRNL PINTAG CASA OE7-31 Y-CRNL.PINTAG. CDLA.YAGUACHI</t>
+  </si>
+  <si>
+    <t>ARAUJO DAVILA JOSE MARIA</t>
+  </si>
+  <si>
+    <t>GENERAL FLORES JUAN JOSE 150 Y VICENTE ROCAFUERTE GENERAL FLORES JUAN JOSE</t>
+  </si>
+  <si>
+    <t>ARAUJO DAVILA MARIA LUISA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>MANABI SN 201 MONTUFAR CasaAMARILLA DE 2 PISOS CASA-AMARILLA DE 2 PISOS---- ALMACEN TUNGURAHUA FRENTE AL REGIMIENTO QUITO NUMERO 2</t>
+  </si>
+  <si>
+    <t>QC CALLE MANABI 201 Y MONTUFAR QC CALLE MANABI</t>
+  </si>
+  <si>
+    <t>ARBOLEDA DAVILA JOSE MARCO</t>
+  </si>
+  <si>
+    <t>CALLE SENA E8 44 Y PARIS PB ATRAS PB-ATRAS CALLE SENA E8</t>
+  </si>
+  <si>
+    <t>ARGUELLO DAVILA ESTEBAN ADRIANO</t>
+  </si>
+  <si>
+    <t>DE LOS TULIPANES 155 Y DE LOS ARUPOS CONJUNTO LA MIRAGE CASA 7B CJTO LA MIRAGE-CASA 7B DE LOS TULIPANES</t>
+  </si>
+  <si>
+    <t>ARIZAGA DAVILA LEONCIO ABELARDO</t>
+  </si>
+  <si>
+    <t>URBANIZACION EL CONDADO CALLE B LOTE 13</t>
+  </si>
+  <si>
+    <t>ARMIJOS DAVILA ANGEL GUSTAVO</t>
+  </si>
+  <si>
+    <t>URBANIZACION SANTA CECILIA DE LAS ACACIAS BEETHOVEN D 44</t>
+  </si>
+  <si>
+    <t>ARREGUI DAVILA SILVIA MORAYMA</t>
+  </si>
+  <si>
+    <t>TERESA DE CEPEDA 216 Y IGNACIO SAN MARIA URB-REAL ALTO TERESA DE CEPEDA</t>
+  </si>
+  <si>
+    <t>ARTURO DAVILA GLORIA DE LOURDES</t>
+  </si>
+  <si>
+    <t>VERSALLES 2039 Y BOLIVIA VERSALLES</t>
+  </si>
+  <si>
+    <t>ASTUDILLO DAVILA GLADYS ELENA</t>
+  </si>
+  <si>
+    <t>LUIS CADENA OE8- 173 Y CALLE OE8C -----</t>
+  </si>
+  <si>
+    <t>AULESTIA DAVILA CARLOS GUILLERMO</t>
+  </si>
+  <si>
+    <t>VF CONJUNTO HABT LOS LIBERTADORES DEPARTAMENTO A 6 23 P2 AVENIDA LOS LIBERTADORES Y CARANQUI</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA CLARA TERESA DE JESUS</t>
+  </si>
+  <si>
+    <t>SOLANDA SECTOR 3 SPMZ 1 MANZANA W CASA 12</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA ELENA NANCY ANGELICA</t>
+  </si>
+  <si>
+    <t>DE LOS CABILDOS N40- 13 HIDALGO DE PINTO CasaCREMA 6 PISOS CASA-CREMA 6 PISOS---- SCT QUITO TENIS</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA ERIKA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>AV. 10 DE AGOSTO 10663 Y AV. LUIS TUFI�O OE1-</t>
+  </si>
+  <si>
+    <t>AYALA DAVILA JUAN LAUREANO</t>
+  </si>
+  <si>
+    <t>FDC CN GMNI SAN FERNANDO CALLE H LOTE 152 Y CALLE C</t>
+  </si>
+  <si>
+    <t>BENALCAZAR DAVILA AIDA MARINA</t>
+  </si>
+  <si>
+    <t>AVENIDA PERIMETRAL E1- 171 PASAJE 31 CASA2 PISOS TAXO PISO 2 TIMBRE CASA-2 PISOS TAXO-PISO-2 TIMBRE-- SECTOR CARCELEN BAJO FRENTE A LA URB VALLE DE CARCELEN DIAGO</t>
+  </si>
+  <si>
+    <t>AVENIDA PERIMETRAL 0 CASA EI-176 URBANIZACION VALLE DE CARCELE CASA EI-176 URB-VALLE DE CARCELE</t>
+  </si>
+  <si>
+    <t>BETTI NARCISA NAVARRETE DAVILA</t>
+  </si>
+  <si>
+    <t>CRLN CONJUNTO RESIDENCIAL NAZARETH CASA 2 CALLE NAZARETH LOTE 594 Y AVENIDA 10 DE AGOSTO ZARETH LOTE 594 Y AVENIDA 10 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>BLANCA JACQUELINE DEL ROCIO PINTO DAVILA</t>
+  </si>
+  <si>
+    <t>AVENIDA MALDONADO 14205 Y CENTRO COMERCIAL EL RECREO LOCAL L-33 LOCAL-L-33 AVENIDA MALDONADO</t>
+  </si>
+  <si>
+    <t>AVENIDA ELOY ALFARO 0 Y PABLO ARTURO SUAREZ EDIFICIO TERRA DEPARTAMENTO 402 SECTOR LA CAROLINA EDIF TERRA-DPTO 402-SECT-LA CAROLINA AVENIDA ELOY ALFARO</t>
+  </si>
+  <si>
+    <t>AVENIDA ELOY ALFARO 0 Y PABLO ARTURO SUAREZ EDIFICIO TERRA DEPARTAMENTO 401 SECTOR CAROLINA EDIF TERRA-DPTO 401-SECT-CAROLINA AVENIDA ELOY ALFARO</t>
+  </si>
+  <si>
+    <t>AVENIDA MALDONADO 14205 Y CENTRO COMERCIAL EL RECREO LOCAL L-13 LOCAL-L-13 AVENIDA MALDONADO</t>
+  </si>
+  <si>
+    <t>BLANCA VIOLETA DAVILA JARAMILLO</t>
+  </si>
+  <si>
+    <t>GUALAQUIZA 365 Y TUFI�O MARINO GUALAQUIZA SN 365 AVENIDA TUFI�O CASA2 PISOS ROSADA LOTE365</t>
+  </si>
+  <si>
+    <t>BUSTOS DAVILA JACINTO FERNANDO</t>
+  </si>
+  <si>
+    <t>BELGICA 283</t>
+  </si>
+  <si>
+    <t>CABEZAS DAVILA ENRIQUE ARTURO</t>
+  </si>
+  <si>
+    <t>DIEGO DE ALMAGRO N26 114 Y LA NI�A EDIFICIO HERMITAGE PISO 3 DEPARTAMENTO 301 EDF-HERMITAGE-PISO-3-DEPT-301 DIEGO DE ALMAGRO N26</t>
+  </si>
+  <si>
+    <t>CABEZAS DAVILA NELSON GERARDO</t>
+  </si>
+  <si>
+    <t>CONJUNTO HAB LA TOLITA BL M N DPTON1</t>
+  </si>
+  <si>
+    <t>CAIZAPANTA DAVILA EDGAR OSWALDO</t>
+  </si>
+  <si>
+    <t>CALLE F E18 158 Y CALLE E COOPERATIVA ELOY ALFARO DE PUENGASI COOP ELOY-ALFARO-DE-PUENGASI CALLE F E18</t>
+  </si>
+  <si>
+    <t>CAIZAPANTA DAVILA RAMIRO PATRICIO</t>
+  </si>
+  <si>
+    <t>VICENTE ROCAFUERTE E3- 165 Y ANTONIO SALAS S1</t>
+  </si>
+  <si>
+    <t>CALDERON DAVILA JOSE RIGOBERTO</t>
+  </si>
+  <si>
+    <t>CALLE 6 127L CASA-127 SECT. CORAZON DE JESUS</t>
+  </si>
+  <si>
+    <t>CAMACHO DAVILA EUGENIA ALICIA</t>
+  </si>
+  <si>
+    <t>SEGUNDA TRANSVERSAL 2 Y SAN JOSE PB BARRIO AMAGASI DEL INCA PB BRR AMAGASI-DEL INCA SEGUNDA TRANSVERSAL</t>
+  </si>
+  <si>
+    <t>CARDENAS DAVILA BOLIVAR GUSTAVO</t>
+  </si>
+  <si>
+    <t>CARLOS ALVARADO N52 61 Y JOSE BARREIRO SECTOR MATOVELLE</t>
+  </si>
+  <si>
+    <t>ALVARADO CARLOS 5261 Y BARREIRO JOSE PISO 2 PISO-2 ALVARADO CARLOS</t>
+  </si>
+  <si>
+    <t>CARLA RENATA BUENO DAVILA</t>
+  </si>
+  <si>
+    <t>DIEGO COCHA N60 215 Y AV DEL MAESTRO</t>
+  </si>
+  <si>
+    <t>CARLOS ANDRES FABARA DAVILA</t>
+  </si>
+  <si>
+    <t>AVENIDA DIEGO DE VASQUEZ N77- 166 Y JUAN DE SELIS AVENIDA DIEGO DE VASQUEZ N77-</t>
+  </si>
+  <si>
+    <t>JULIO RAMOS 0 Y -</t>
+  </si>
+  <si>
+    <t>CARLOS ENRIQUE DAVILA RIVERA</t>
+  </si>
+  <si>
+    <t>EL LABRADOR 0 Y PABLO CASALS CASA 107</t>
+  </si>
+  <si>
+    <t>CASTILLO DAVILA FAUSTO VICENTE</t>
+  </si>
+  <si>
+    <t>CALLE 6 N54 254 Y JOSE SANCHEZ CONJUNTO RESIDENCIAL HOLANDA PISO 4 DEPARTAMENTO B8 L HOLANDA PISO 4 DEPARTAMENTO B8</t>
+  </si>
+  <si>
+    <t>CASTRO DAVILA EDITH MARISOL</t>
+  </si>
+  <si>
+    <t>AVIGIRAS 54 Y GUAYACANES PISO 4 DEPARTAMENTO 4 A PISO 4-DEPT 4 A AVIGIRAS</t>
+  </si>
+  <si>
+    <t>CATALINA DEL ROCIO DAVILA PAZMI�O</t>
+  </si>
+  <si>
+    <t>BARCELONA 551</t>
+  </si>
+  <si>
+    <t>CECILIA MAGDALENA DE LOURDES DAVILA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>AVENIDA IO DE AGOSTO 6663 Y FALCONI AVENIDA IO DE AGOSTO</t>
+  </si>
+  <si>
+    <t>CEVALLOS DAVILA ANGELA VICTORIA</t>
+  </si>
+  <si>
+    <t>CRLN URBANIZACION LOS MASTODONTES CALLE 2/A LOTE 153 Y CALLE 2/5</t>
+  </si>
+  <si>
+    <t>CEVALLOS DAVILA FANNY EMPERATRIZ</t>
+  </si>
+  <si>
+    <t>CARCELEN BAJO PASAJE 12 N 91 54</t>
+  </si>
+  <si>
+    <t>CHAVEZ DAVILA AIDA GRIMANEZA</t>
+  </si>
+  <si>
+    <t>CALLE E3J 267 Y CALLE 5 CALLE E3J</t>
+  </si>
+  <si>
+    <t>CHAVEZ DAVILA GALO FERNANDO</t>
+  </si>
+  <si>
+    <t>INQ EDIFICIO MONTE ZERMAT DEPARTAMENTO 302 CALLE A LOTE A URBANIZACION COLINAS DEL PICHINCHA</t>
+  </si>
+  <si>
+    <t>CHIGUANO DAVILA DINA MARIA</t>
+  </si>
+  <si>
+    <t>CALLE B 507 Y CALLE G1 URBANIZACION PRADOS DEL CONDADO URB. PRADOS-DEL CONDADO CALLE B</t>
+  </si>
+  <si>
+    <t>CHRISTIAN LENIN RIJAS DAVILA</t>
+  </si>
+  <si>
+    <t>AV MARIANA DE JESUS 2E Y NU�O DE VALDERRAMA EDIFICIO SITIMED PISO 3 PEDP 305 EDIFICIO SITIMED PISO 3 PEDP 305</t>
+  </si>
+  <si>
+    <t>CISNEROS DAVILA MIRIAN JEANETTE</t>
+  </si>
+  <si>
+    <t>AVENIDA DE LOS SHYRIS N36- 90 Y SUECIA EDIFICIO HELEM PISO 7 DEPARTAMENTO 7 SUR EDF-HELEM-PISO-7-DEPT-7 SUR AVENIDA DE LOS SHYRIS N36-</t>
+  </si>
+  <si>
+    <t>IGNACIO BOSSANO E10 50 Y AVENIDA 6 DE DICIEMBRE EDIFICIO COLINAS DEL BATA N NOVENO PISO D PTO 9A EDF-COLINAS DEL BATA-N NOVENO PISO D-PTO 9A IGNACIO BOSSANO E10</t>
+  </si>
+  <si>
+    <t>CLARA LUZ DORILA DAVILA LLOCANA</t>
+  </si>
+  <si>
+    <t>ANDRES DE ARTIEDA OE4- 67 GASPAR CUJIAS ManzanaG Casa59 asa59</t>
+  </si>
+  <si>
+    <t>CONSTANTE DAVILA JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>SALEM JULIO TEODORO N57 217Y Y MZ 41 LOTE 5 LT 50 LT-50</t>
+  </si>
+  <si>
+    <t>CORREA DAVILA ISABEL DEL CISNE</t>
+  </si>
+  <si>
+    <t>LA FLORESTA</t>
+  </si>
+  <si>
+    <t>MERCEDES GONZALES OE4 118 Y EINSTEN ALBERTO URBANIZACION FLORESTA CRLEN URB-FLORESTA CRLEN MERCEDES GONZALEZ OE4</t>
+  </si>
+  <si>
+    <t>CRESPO DAVILA IVONNE CAROLINA</t>
+  </si>
+  <si>
+    <t>DIEGO DE VILLANUEVA E2- 26 Y BARTOLOME DE LA ROSA DIEGO DE VILLANUEVA E2-</t>
+  </si>
+  <si>
+    <t>CRESPO DAVILA LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t>SEVILLA N24- 473 Y VIZCAYA ----- SEVILLA N24-</t>
+  </si>
+  <si>
+    <t>CRESPO DAVILA VERONICA MARIA CONSUELO</t>
+  </si>
+  <si>
+    <t>GUANGUILTAGUA N36 231 Y AROSEMENA TOLA GUANGUILTAGUA N36</t>
+  </si>
+  <si>
+    <t>DANIEL OSWALDO COLA DAVILA</t>
+  </si>
+  <si>
+    <t>CALLE Z 0 L Y RICARDO IZURIETA DEL CASTILLO barrio obrero independiente barrio obrero independiente RICARDO IZURIETA DEL CASTILLO</t>
+  </si>
+  <si>
+    <t>DAVALOS DAVILA TANIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>VIRGIL MATIAS 144 GONZALO ZALDUMBIDE</t>
+  </si>
+  <si>
+    <t>DAVILA ABRIL ELSA PILAR</t>
+  </si>
+  <si>
+    <t>INQ EDIFICIO TORRE CRISTAL P4 CALLE SERGIO JATIVA 136 ENTRE BOSSANO Y BOSMEDIANO</t>
+  </si>
+  <si>
+    <t>DAVILA ABRIL NORA PATRICIA</t>
+  </si>
+  <si>
+    <t>EDIFICIO CENTRAL PARK DEPARTAMENTO 1C CARLOS TOBAR Y ELOY ALFARO ESQUINA</t>
+  </si>
+  <si>
+    <t>CARLOS TOBAR E6- 41 Y AVENIDA ELOY ALFARO CARLOS TOBAR E6-</t>
+  </si>
+  <si>
+    <t>SUIZA 209 Y AVENIDA ELOY ALFARO EDIFICIO CLINICA OFTALMOLOGICA SANTA LUCIA PISO 5 OF 501 EDF CLINICA-OFTALMOLOGICA-SANTA-LUCIA PISO 5-OF-501 SUIZA</t>
+  </si>
+  <si>
+    <t>AVENIDA MARIANA DE JESUS OE- 8 Y AVENIDA OCCIDENTAL EDIFICIO CENTRO MEDICO METROPOLI 0 EDF-CENTRO MEDICO-METROPOLI-0 AVENIDA MARIANA DE JESUS OE-</t>
+  </si>
+  <si>
+    <t>DAVILA ACOSTA CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>GUSTAVO VALLEJO 48 Y GONZALO ZALDUMBIDE</t>
+  </si>
+  <si>
+    <t>DAVILA AGUILAR FLAVIO JOEL</t>
+  </si>
+  <si>
+    <t>PEDRO CASTRILLON S42 289 Y Y CALLE S2H</t>
+  </si>
+  <si>
+    <t>DAVILA AGUILAR ROBERTO GUSTAVO</t>
+  </si>
+  <si>
+    <t>CALLE OE8F 32B Y CALLE S35D MANZANA SAN REMO CONJUNTO PALERMO SECTOR CHILLOGALLO MANZANA SAN-REMO-CONJUNTO-PALERMO-SECTOR-CHILLOGALLO CALLE OE8F</t>
+  </si>
+  <si>
+    <t>DAVILA AGUIRRE FAUSTO EDISON</t>
+  </si>
+  <si>
+    <t>ISLA SAN CRISTOBAL 546 Y ISLA FLOREANA PISO 3 PISO-3 ISLA SAN CRISTOBAL</t>
+  </si>
+  <si>
+    <t>DAVILA AGUIRRE RENE PAUL</t>
+  </si>
+  <si>
+    <t>JUAN PIO MONTUFAR 0A Y JOSE MEJIA LEQUERICA MZ 17 CASA 17 JUNTO A TIENDA</t>
+  </si>
+  <si>
+    <t>DAVILA ALARCON EULALIA SUSANA</t>
+  </si>
+  <si>
+    <t>LA LUZ KENEDY CONJUNTO COMENALCO 6 DE DICIEMBRE LOTE 11 Y FRESNOS</t>
+  </si>
+  <si>
+    <t>DAVILA ALBAN GUILLERMO NAPOLEON</t>
+  </si>
+  <si>
+    <t>CARAPUNGO SPMZ B 8 MANZANA O CASA 24</t>
+  </si>
+  <si>
+    <t>DAVILA ALBAN SILVIO MIGUEL</t>
+  </si>
+  <si>
+    <t>GUATEMALA 513 Y NUEVA YORK GUATEMALA</t>
+  </si>
+  <si>
+    <t>DAVILA ALFARO LUIS NAPOLEON</t>
+  </si>
+  <si>
+    <t>MARTINEZ MERA 123 Y AVENIDA CARLOS JULIO AROSEMENA MARTINEZ MERA</t>
+  </si>
+  <si>
+    <t>DAVILA ALFARO PIO ECUADOR</t>
+  </si>
+  <si>
+    <t>EL TIEMPO 7L DEPARTAMENTO 6 (ESTE) 6TO PISO EDIFICI ALCAZAR DEL ROCIO SECTOR EL BATAN DPTO 6 (ESTE)-6TO PISO EDIFICI-ALCAZAR DEL-ROCIO-SECT-EL BATAN</t>
+  </si>
+  <si>
+    <t>AVENIDA GASPAR DE VILLAROEL E11 95 Y AVENIDA 6 DE DICIEMBRE EDIFICIO MADERNA DEPARTAMENTO 801 EDF MADERNA-DPTO 801 AVENIDA GASPAR DE VILLAROEL E11</t>
+  </si>
+  <si>
+    <t>MSC CALLE CUERO Y CAICEDO OE453 Y CARVAJAL</t>
+  </si>
+  <si>
+    <t>DAVILA ALVAN CONSUELO LEONOR</t>
+  </si>
+  <si>
+    <t>LA PULIDA AVENIDA DE LA PRENSA 3389</t>
+  </si>
+  <si>
+    <t>DAVILA ALVAREZ CARLOS HERNAN</t>
+  </si>
+  <si>
+    <t>MARIANO HINOJOSA 0 DIEGO MONTANERO CONJUNTO RESIDENCIAL MADRIGAL CASA 3 DIEGO MONTANERO CONJUNTO RESIDENCIAL MADRIGAL CASA 3</t>
+  </si>
+  <si>
+    <t>DAVILA ALVAREZ MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ISLA MARCHENA N42 138 Y GRANADOS EDIFICIO PORTAL DE ARAGON TORRE 3 DEPARTAMENTO 604 PISO 6 EDF PORTAL DE-ARAGON TORRE 3-DP 604 PISO-6 ISLA MARCHENA N42</t>
+  </si>
+  <si>
+    <t>DAVILA ALVAREZ VIOLETA</t>
+  </si>
+  <si>
+    <t>AVENIDA GRANDA CENTENO 684 Y GALO ALVAREZ EDIFICIO MANSION IV PISO 5 DEPARTAMENTO B-502 SECTOR QUITO TENIS EDIF MANSION IV-PISO 5-DEPT B-502 SECT-QUITO TENIS AVENIDA GRANDA CENTENO</t>
+  </si>
+  <si>
+    <t>PAUL RIVET N31 02 Y WHYMPER PAUL RIVET</t>
+  </si>
+  <si>
+    <t>MULTF VERSALLES 1 SELVA ALEGRE Y VERSALLES DTO B11</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE MERCEDES SUSANA</t>
+  </si>
+  <si>
+    <t>LA NI�A 211 Y YANEZ PINZON EDIFICIO LAS CARABELAS 2DO PISO OFICINA 202 EDF LAS-CARABELAS-2DO PISO-OFICINA 202 LA NI�A</t>
+  </si>
+  <si>
+    <t>TORRES DEL PRADO BLOQUE 5 DEPARTAMENTO 401 INQ CALLE HERNANDEZ DE GIRON Y PEDREGAL</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE SYLVIA IVONNE</t>
+  </si>
+  <si>
+    <t>GARCIA MOREANO N57 86 Y NICOLAS ARTETA GARCIA MOREANO N57</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRANGO ENRIQUE DAVID</t>
+  </si>
+  <si>
+    <t>EL PINAR OE17 92 Y CAMACHO JUAN EL PINAR OE17</t>
+  </si>
+  <si>
+    <t>DAVILA ARAUJO BLANCA MARITZA</t>
+  </si>
+  <si>
+    <t>URBANIZACION MONJAS SECTOR 2 JARDIN DEL VALLE CALLE 22 CASA 616</t>
+  </si>
+  <si>
+    <t>DAVILA ARENA RUTH GEOCONDA</t>
+  </si>
+  <si>
+    <t>URBANIZACION EL BATAN LOTE 255</t>
+  </si>
+  <si>
+    <t>LA TIRRA 168 JUAN DE ALCANTARA</t>
+  </si>
+  <si>
+    <t>ANITA MARIANELA VELASCO DAVILA</t>
+  </si>
+  <si>
+    <t>PEDRO SOLANO 0 Y Y SAN JOSE DE OYAMBARILLO QUINTA CON PORTON LLAMDA EL CHINCHINAL QUINTA CON PORTON LLAMDA EL CHINCHINAL SAN JOSE DE OYAMBARILLO</t>
+  </si>
+  <si>
+    <t>PUEMBO</t>
+  </si>
+  <si>
+    <t>ARGUELLO DAVILA DIEGO OSWALDO</t>
+  </si>
+  <si>
+    <t>AV MANUEL CORDOVA GALARZA 0 Y MARCELINA NOLIVOS</t>
+  </si>
+  <si>
+    <t>POMASQUI</t>
+  </si>
+  <si>
+    <t>CARMEN ESTELA ACHIG DAVILA</t>
+  </si>
+  <si>
+    <t>AV. MANUEL CORDOVA GALARZA 0 Y EL EDEN CND LOS OLIVOS III CASA 35 CND-LOS OLIVOS III-CASA-35</t>
+  </si>
+  <si>
+    <t>CELSO HUMBERTO DAVILA HERRERA</t>
+  </si>
+  <si>
+    <t>EL ROSAL 160 Y LOS LUCEROS</t>
+  </si>
+  <si>
+    <t>CEVALLOS DAVILA JUAN ANGEL</t>
+  </si>
+  <si>
+    <t>DE LOS GUAYABOS 725 L Y LA PAMPA BL SEGUNDA AVENIDA BL-SEGUNDA AVENIDA</t>
+  </si>
+  <si>
+    <t>DE LOS GUAYABOS 725 L Y - BL AVELLANAS LA PAMPA BL-AVELLANAS LA PAMPA</t>
+  </si>
+  <si>
+    <t>DAVILA AGUILAR NELI HUILFRIDA</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL 252</t>
+  </si>
+  <si>
+    <t>PINTAG</t>
+  </si>
+  <si>
+    <t>AGUILERA DAVILA LUCRECIA BEATRIZ</t>
+  </si>
+  <si>
+    <t>NAYON 0 BARRIO SAN PEDRO LOTE 665 BRR. SAN PEDRO-LOTE 665</t>
+  </si>
+  <si>
+    <t>NAYON</t>
+  </si>
+  <si>
+    <t>ARGUELLO DAVILA HERMITA SOLEDAD</t>
+  </si>
+  <si>
+    <t>NAYON CALLE QUISQUIS 855 Y HUAYNA CAPAC NAYON CALLE QUISQUIS</t>
+  </si>
+  <si>
+    <t>QUISQUIS 451 N Y HUAYNA CAPAC</t>
+  </si>
+  <si>
+    <t>CALLE 1 5L Y CALLE A PRIMER PISO SECTOR MIRAVALLE PRIMER-PISO-SECTOR-MIRAVALLE CALLE 1</t>
+  </si>
+  <si>
+    <t>MIRAVALLE</t>
+  </si>
+  <si>
+    <t>CEVALLOS DAVILA ROSA YOLANDA</t>
+  </si>
+  <si>
+    <t>BENITEZ ANTONIO 9 COLOMBIA LT-9---- SECTOR MACHACHI CASA BLANCA 2 PISOS CASA ESQUINERA 3 CUADRAS AL NORTE DEL BANCO PICHINCHA</t>
+  </si>
+  <si>
+    <t>MACHACHI</t>
+  </si>
+  <si>
+    <t>CARLOS MANTILLA 0 Y Y LOS GERANIOS CONJ. KAIROS CASA 31</t>
+  </si>
+  <si>
+    <t>LAS NAVES</t>
+  </si>
+  <si>
+    <t>CORINA DE LAS MERCEDES NIVICELA DAVILA</t>
+  </si>
+  <si>
+    <t>CALLE L 397 Y CALLE N CALLE L</t>
+  </si>
+  <si>
+    <t>ANDREA MARIBEL DAVILA FEIJO</t>
+  </si>
+  <si>
+    <t>AV ILALO 0 Y CESAR ENRIQUE BALSECA CONJUNTO SAN FRANCISCO DE L AMERCED</t>
+  </si>
+  <si>
+    <t>LAS GOLONDRINAS</t>
+  </si>
+  <si>
+    <t>AVENDA�O DAVILA SEGUNDO RAFAEL</t>
+  </si>
+  <si>
+    <t>AVENIDA PATRICIO ROMERO 12 Y CALLE F MANZANA 26 SECTOR 2 DE MAYO NATIVIDAD MZ 26 SEC. 2 DE-MAYO NATIVIDAD AVENIDA PATRICIO ROMERO</t>
+  </si>
+  <si>
+    <t>LA VICTORIA COTOPAXI</t>
+  </si>
+  <si>
+    <t>BLANCA ROSA DEL CARMEN DAVILA ESPINOZA</t>
+  </si>
+  <si>
+    <t>PASAJE 8 37A Y PASAJE 7 PORTAL DEL LAGO</t>
+  </si>
+  <si>
+    <t>CARMEN DAVILA NUNGUI</t>
+  </si>
+  <si>
+    <t>VALLE HERMOSO 0 Y LA CONCORDIA casa color caf� de un piso frente a la tienda// contrato para 36 meses casa color caf� de un piso frente a la tienda// contrato para 36 meses LA CONCORDIA</t>
+  </si>
+  <si>
+    <t>CARRERA DAVILA FRANKLIN ORLANDO</t>
+  </si>
+  <si>
+    <t>JOSE GOMEZ 118 Y BORJA</t>
+  </si>
+  <si>
+    <t>CAJAS DAVILA MARIA LUISA</t>
+  </si>
+  <si>
+    <t>AMBATO 510 0 Y PICHINCHA</t>
+  </si>
+  <si>
+    <t>EL QUINCHE</t>
+  </si>
+  <si>
+    <t>ACOSTA DAVILA FABIAN OSWALDO</t>
+  </si>
+  <si>
+    <t>VALDIVIA 0 LOTE 4 DEPARTAMENTO 2A SECTOR SAN PATRICIO LOTE-4-DPTO-2A-SECTOR-SAN PATRICIO</t>
+  </si>
+  <si>
+    <t>CUMBAYA</t>
+  </si>
+  <si>
+    <t>CUMBAYA URBANIZACION REAL ALTO MACHALILLA CASA 51 Y COTOCOCHA</t>
+  </si>
+  <si>
+    <t>BUGANVILLAS 32L URBANIZACION AUQUI CHICO URB-AUQUI CHICO</t>
+  </si>
+  <si>
+    <t>CABEZAS DAVILA MARTHA JUDITH</t>
+  </si>
+  <si>
+    <t>LA PRIMAVERA I ETAPA LOTE 211</t>
+  </si>
+  <si>
+    <t>CARRILLO DAVILA LUIS RAMIRO</t>
+  </si>
+  <si>
+    <t>CUMBAYA URBANIZACION JARDINES DEL ESTE SEGUNDA ETAPA LOTE 43</t>
+  </si>
+  <si>
+    <t>CECILIA MAGDALENA DAVILA MOLINA</t>
+  </si>
+  <si>
+    <t>BARRIO LUMBISI CUMBAYA CALLE 89 LOTE SN FRENTE CENTRO ESPANOL</t>
+  </si>
+  <si>
+    <t>DAVILA ALVAREZ MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>URBANIZACION LA CA�ADA 3C Y VIA AL LIMONAR CUMBAYA</t>
+  </si>
+  <si>
+    <t>DAVILA ANDRADE JORGE RAUL</t>
+  </si>
+  <si>
+    <t>CUMBAYA URBANIZACION JARDINES DEL ESTE CALLE PEDRO CARLOS LOTE 27 CARLOS LOTE 27</t>
+  </si>
+  <si>
+    <t>PADRE CARLOS SN 27 FRAY FRANCISCO BENITEZ CasaCOLOR BLANCO 1 PISO R BLANCO 1 PISO</t>
+  </si>
+  <si>
+    <t>ALBERTO ALEJANDRO DAVILA JARA</t>
+  </si>
+  <si>
+    <t>CALLE OE7H- 7274O SECTOR 14 DE MARZO CONOCOTO // CASA IE7-274// FRANCISCO ROBLES SECTOR 14 DE MARZO CONOCOTO // CASA IE7-274// FRANCISCO ROBLES</t>
+  </si>
+  <si>
+    <t>CONOCOTO</t>
+  </si>
+  <si>
+    <t>ANA GABRIELA ESPINOSA DAVILA</t>
+  </si>
+  <si>
+    <t>CALLE C 67 Y CALLE A CIUDAD DE QUITO</t>
+  </si>
+  <si>
+    <t>ARAGON DAVILA JAIME ANDRES</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL LEON 0 Y ISMAEL SOLIS MIGUEL ANGEL LEON</t>
+  </si>
+  <si>
+    <t>CHAGUAY DAVILA FELIX ADOLFO</t>
+  </si>
+  <si>
+    <t>LLOQUE YUPANQUI N3- 214 Y HUAYNA - CAPAC</t>
+  </si>
+  <si>
+    <t>CORDOVA DAVILA HERNAN MARCELO</t>
+  </si>
+  <si>
+    <t>HUAYNA CAPAC N2 190 Y CAPAC YUPANQUI SECTOR SANATA MONICA HUAYNA CAPAC</t>
+  </si>
+  <si>
+    <t>CORREA DAVILA BELJICA IRENE</t>
+  </si>
+  <si>
+    <t>CALLE A 519 Y CALLE 1 BARRIO SANTA TERESITA DEL VAL BARRIO STA-TERESITA DEL VAL CALLE A</t>
+  </si>
+  <si>
+    <t>DAVILA AGUILAR LUIS PATRICIO</t>
+  </si>
+  <si>
+    <t>CONOCOTO 0 Y JUNTO LA SEVILLANA CASA 35 FRENTE AL COMPLEJO MEDICO DE PICHINCHA CONOCOTO</t>
+  </si>
+  <si>
+    <t>CALDERON DAVILA WILMA DIOCELINA</t>
+  </si>
+  <si>
+    <t>CALLE TULIPANES 48 Y CRISANTEMOS CALLE TULIPANES</t>
+  </si>
+  <si>
+    <t>CAYAMBE</t>
+  </si>
+  <si>
+    <t>DANIEL ADOLFO DAVILA HERRERA</t>
+  </si>
+  <si>
+    <t>23 DE JULIO 76 L Y VIA SANTO DOMINGO DE GUZMAN FRENTE A LA PARADA DE CAMIONETAS TRASNLEONES LOCAL CASA DE LA HUMITA FRENTE A LA PARADA DE CAMIONETAS TRASNLEONES LOCAL CASA DE LA HUMITA VIA SANTO DOMINGO DE GUZMAN</t>
+  </si>
+  <si>
+    <t>BOADA DAVILA JANNETH ALEXANDRA</t>
+  </si>
+  <si>
+    <t>PANAMERICANA NORTE KILOMETRO 14 1/2 8L Y PASAJE CENEPA JUNTO A CARPAG SECTOR SAN CAMILO DE CALDERON JUNTO A CARPAG-SECTOR SAN-CAMILO-DE CALDERON</t>
+  </si>
+  <si>
+    <t>CALDERON</t>
+  </si>
+  <si>
+    <t>CABEZAS DAVILA SEGUNDO RICARDO</t>
+  </si>
+  <si>
+    <t>CALDERON BARRIO MARIANA DE JESUS JUNTO A EMETEL</t>
+  </si>
+  <si>
+    <t>CASTRO DAVILA HECTOR GERMAN</t>
+  </si>
+  <si>
+    <t>EL ARENAL 26 Y PANAMERICANA NORTE SECTOR CARAPUNGO CASALES BUENAVENTURA ETAPA II CASA 26 SECTOR CARAPUNGO CASALES BUENAVENTURA ETAPA II CASA 26</t>
+  </si>
+  <si>
+    <t>CRISTELA MATILDE DAVILA DAVILA</t>
+  </si>
+  <si>
+    <t>NUEVA YORK 0 Y LUGO LUGO</t>
+  </si>
+  <si>
+    <t>CUEVA DAVILA JEAN PAUL</t>
+  </si>
+  <si>
+    <t>UNION Y JORGE MURILLO 54L</t>
+  </si>
+  <si>
+    <t>ATAHUALPA BARRIO EL TRIUNFO CALLE PRINCIPAL 905 CALLE K</t>
+  </si>
+  <si>
+    <t>ATAHUALPA</t>
+  </si>
+  <si>
+    <t>ALICIA MARIA DE LOURDES TALAVERA DAVILA</t>
+  </si>
+  <si>
+    <t>FEDERICO GONZALES SUAREZ 0 Y MANUEL DURINI</t>
+  </si>
+  <si>
+    <t>AMAGUANA</t>
+  </si>
+  <si>
+    <t>CARMEN NARCISA DEL JESUS DAVILA TOLEDO</t>
+  </si>
+  <si>
+    <t>JOSE DE LA CUADRA 0 Y ALVAREZ RICARDO CASA 2 PISOS CASA-2 PISOS JOSE DE LA CUADRA</t>
   </si>
 </sst>
 </file>
@@ -1559,35 +1520,35 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>63051064</v>
+        <v>22376717</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>62918920</v>
+        <v>24777777</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>62652836</v>
+        <v>22379961</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1596,172 +1557,172 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>63017631</v>
+        <v>23549016</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>62932053</v>
+        <v>23525575</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>62550142</v>
+        <v>23525138</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>62932543</v>
+        <v>22331333</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>62932054</v>
+        <v>22871028</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>62631007</v>
+        <v>22871158</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>62630529</v>
+        <v>22087319</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>62937749</v>
+        <v>22081957</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>62937398</v>
+        <v>22871168</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>62569082</v>
+        <v>22864494</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>62569086</v>
+        <v>22851677</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>62569036</v>
+        <v>22302236</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
         <v>39</v>
@@ -1769,13 +1730,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>62569117</v>
+        <v>23613441</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
@@ -1783,2718 +1744,2718 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>62528003</v>
+        <v>22302237</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>62923139</v>
+        <v>24518925</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>62525898</v>
+        <v>22396525</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>62520655</v>
+        <v>22394192</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>62520598</v>
+        <v>22035740</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>62903674</v>
+        <v>22437075</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>62923898</v>
+        <v>22537260</v>
       </c>
       <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
         <v>58</v>
       </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>62928763</v>
+        <v>22481231</v>
       </c>
       <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
         <v>60</v>
       </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>62920074</v>
+        <v>22593912</v>
       </c>
       <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
         <v>62</v>
       </c>
-      <c r="C26" t="s">
-        <v>63</v>
-      </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>62927375</v>
+        <v>22472529</v>
       </c>
       <c r="B27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" t="s">
         <v>64</v>
       </c>
-      <c r="C27" t="s">
-        <v>65</v>
-      </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>62927684</v>
+        <v>22800425</v>
       </c>
       <c r="B28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" t="s">
         <v>66</v>
       </c>
-      <c r="C28" t="s">
-        <v>67</v>
-      </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>62930476</v>
+        <v>23060391</v>
       </c>
       <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
         <v>68</v>
       </c>
-      <c r="C29" t="s">
-        <v>69</v>
-      </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>62920866</v>
+        <v>22731951</v>
       </c>
       <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
         <v>70</v>
       </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>62668347</v>
+        <v>22730722</v>
       </c>
       <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" t="s">
         <v>72</v>
       </c>
-      <c r="C31" t="s">
-        <v>73</v>
-      </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>62668190</v>
+        <v>22480079</v>
       </c>
       <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
         <v>74</v>
       </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>62520803</v>
+        <v>22482795</v>
       </c>
       <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" t="s">
         <v>76</v>
       </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>62520348</v>
+        <v>22430938</v>
       </c>
       <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" t="s">
         <v>78</v>
       </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>62521775</v>
+        <v>23360424</v>
       </c>
       <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
         <v>80</v>
       </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>62520818</v>
+        <v>22297543</v>
       </c>
       <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
         <v>82</v>
       </c>
-      <c r="C36" t="s">
-        <v>83</v>
-      </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>62927902</v>
+        <v>22267556</v>
       </c>
       <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
         <v>84</v>
       </c>
-      <c r="C37" t="s">
-        <v>85</v>
-      </c>
       <c r="D37" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>62922997</v>
+        <v>22439780</v>
       </c>
       <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
         <v>86</v>
       </c>
-      <c r="C38" t="s">
-        <v>87</v>
-      </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>62921650</v>
+        <v>24517524</v>
       </c>
       <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
         <v>88</v>
       </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>62922849</v>
+        <v>24525162</v>
       </c>
       <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
         <v>90</v>
       </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>62521380</v>
+        <v>22447754</v>
       </c>
       <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
         <v>92</v>
       </c>
-      <c r="C41" t="s">
-        <v>93</v>
-      </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>62523753</v>
+        <v>22407193</v>
       </c>
       <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
         <v>94</v>
       </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>62921512</v>
+        <v>22541912</v>
       </c>
       <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
         <v>96</v>
       </c>
-      <c r="C43" t="s">
-        <v>97</v>
-      </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>62920494</v>
+        <v>22236239</v>
       </c>
       <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
         <v>98</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>22271367</v>
+      </c>
+      <c r="B45" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" t="s">
         <v>99</v>
       </c>
-      <c r="D44" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
-        <v>4</v>
-      </c>
       <c r="D45" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>4</v>
+      <c r="A46">
+        <v>22448898</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>4</v>
+      <c r="A47">
+        <v>22231199</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>4</v>
+      <c r="A48">
+        <v>22521395</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
-        <v>4</v>
+      <c r="A49">
+        <v>23289254</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>4</v>
+      <c r="A50">
+        <v>22273396</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>4</v>
+      <c r="A51">
+        <v>22444465</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="D51" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>4</v>
+      <c r="A52">
+        <v>22444032</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>0</v>
+      <c r="A53">
+        <v>22529949</v>
       </c>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>0</v>
+      <c r="A54">
+        <v>24788397</v>
       </c>
       <c r="B54" t="s">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="C54" t="s">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="D54" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>0</v>
+      <c r="A55">
+        <v>22253174</v>
       </c>
       <c r="B55" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
-        <v>0</v>
+      <c r="A56">
+        <v>22580607</v>
       </c>
       <c r="B56" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>0</v>
+      <c r="A57">
+        <v>22283092</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>0</v>
+      <c r="A58">
+        <v>22600222</v>
       </c>
       <c r="B58" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>0</v>
+      <c r="A59">
+        <v>22288129</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>0</v>
+      <c r="A60">
+        <v>22920494</v>
       </c>
       <c r="B60" t="s">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="D60" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>0</v>
+      <c r="A61">
+        <v>22478688</v>
       </c>
       <c r="B61" t="s">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="D61" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
-        <v>0</v>
+      <c r="A62">
+        <v>22495329</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="D62" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>62516222</v>
+        <v>22401357</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>62539292</v>
+        <v>23317903</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>62569037</v>
+        <v>22541350</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>62585846</v>
+        <v>22836391</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>62679043</v>
+        <v>22646999</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D67" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>62615580</v>
+        <v>22732703</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>62952013</v>
+        <v>22459091</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>62951868</v>
+        <v>22484395</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>62540277</v>
+        <v>23018099</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>62569004</v>
+        <v>22803693</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>62956658</v>
+        <v>23441213</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="D73" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>62600228</v>
+        <v>22479535</v>
       </c>
       <c r="B74" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>62950109</v>
+        <v>22660859</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>62641557</v>
+        <v>23237553</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>62957877</v>
+        <v>23238625</v>
       </c>
       <c r="B77" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>62952847</v>
+        <v>22663685</v>
       </c>
       <c r="B78" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="D78" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>62644586</v>
+        <v>22590333</v>
       </c>
       <c r="B79" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="D79" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>62954310</v>
+        <v>22237519</v>
       </c>
       <c r="B80" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="D80" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81">
-        <v>62612346</v>
+        <v>22526853</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>62958515</v>
+        <v>22283828</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C82" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D82" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>62641586</v>
+        <v>22321136</v>
       </c>
       <c r="B83" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="D83" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>62959723</v>
+        <v>22285027</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C84" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D84" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>62616099</v>
+        <v>23412736</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="D85" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>62612844</v>
+        <v>23260213</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D86" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>62605505</v>
+        <v>22411865</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C87" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="D87" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>63022057</v>
+        <v>22814510</v>
       </c>
       <c r="B88" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="D88" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89">
-        <v>62950099</v>
+        <v>22537958</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90">
-        <v>62641881</v>
+        <v>22800685</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C90" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="D90" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91">
-        <v>62954209</v>
+        <v>23477153</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C91" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="D91" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>62950031</v>
+        <v>22418598</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="D92" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>62958641</v>
+        <v>23400161</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="C93" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="D93" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>62950140</v>
+        <v>23284862</v>
       </c>
       <c r="B94" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C94" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="D94" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95">
-        <v>62615800</v>
+        <v>22234664</v>
       </c>
       <c r="B95" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C95" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>62601656</v>
+        <v>22260319</v>
       </c>
       <c r="B96" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C96" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="D96" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>62569041</v>
+        <v>22483590</v>
       </c>
       <c r="B97" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C97" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D97" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>62606442</v>
+        <v>22804051</v>
       </c>
       <c r="B98" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C98" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>62539261</v>
+        <v>23069083</v>
       </c>
       <c r="B99" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C99" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="D99" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>62505138</v>
+        <v>23310485</v>
       </c>
       <c r="B100" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C100" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D100" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101">
-        <v>62585254</v>
+        <v>23570721</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C101" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D101" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102">
-        <v>62603923</v>
+        <v>24523926</v>
       </c>
       <c r="B102" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C102" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="D102" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103">
-        <v>62641627</v>
+        <v>22466596</v>
       </c>
       <c r="B103" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C103" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D103" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104">
-        <v>62955989</v>
+        <v>22467674</v>
       </c>
       <c r="B104" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C104" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="D104" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105">
-        <v>62602721</v>
+        <v>22628663</v>
       </c>
       <c r="B105" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C105" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106">
-        <v>63048245</v>
+        <v>22408988</v>
       </c>
       <c r="B106" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C106" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="D106" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107">
-        <v>62958522</v>
+        <v>22473403</v>
       </c>
       <c r="B107" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C107" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="D107" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108">
-        <v>62950155</v>
+        <v>23440433</v>
       </c>
       <c r="B108" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C108" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109">
-        <v>62600450</v>
+        <v>22481324</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C109" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D109" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110">
-        <v>62952898</v>
+        <v>23230468</v>
       </c>
       <c r="B110" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="D110" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A111">
-        <v>62956805</v>
+        <v>23332577</v>
       </c>
       <c r="B111" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C111" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="D111" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112">
-        <v>62651397</v>
+        <v>22602378</v>
       </c>
       <c r="B112" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C112" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="D112" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A113">
-        <v>62610693</v>
+        <v>22404999</v>
       </c>
       <c r="B113" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C113" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="D113" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A114">
-        <v>62951218</v>
+        <v>22266106</v>
       </c>
       <c r="B114" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C114" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="D114" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A115">
-        <v>62652921</v>
+        <v>22220536</v>
       </c>
       <c r="B115" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="D115" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A116">
-        <v>62511184</v>
+        <v>22224851</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="C116" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="D116" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A117">
-        <v>62604106</v>
+        <v>22279366</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C117" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="D117" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118">
-        <v>62511967</v>
+        <v>22449209</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C118" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="D118" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119">
-        <v>62546138</v>
+        <v>22413754</v>
       </c>
       <c r="B119" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C119" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="D119" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120">
-        <v>62603619</v>
+        <v>23690401</v>
       </c>
       <c r="B120" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C120" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="D120" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121">
-        <v>62951027</v>
+        <v>23033100</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="C121" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="D121" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A122">
-        <v>62955017</v>
+        <v>22447048</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="C122" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="D122" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A123">
-        <v>62958048</v>
+        <v>23447277</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>239</v>
       </c>
       <c r="C123" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="D123" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A124">
-        <v>62953606</v>
+        <v>22811380</v>
       </c>
       <c r="B124" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="C124" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="D124" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A125">
-        <v>62951209</v>
+        <v>22423965</v>
       </c>
       <c r="B125" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C125" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="D125" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A126">
-        <v>62505159</v>
+        <v>22510164</v>
       </c>
       <c r="B126" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C126" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="D126" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A127">
-        <v>62641357</v>
+        <v>22248981</v>
       </c>
       <c r="B127" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C127" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="D127" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A128">
-        <v>62952487</v>
+        <v>22244134</v>
       </c>
       <c r="B128" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C128" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="D128" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A129">
-        <v>62512586</v>
+        <v>22434380</v>
       </c>
       <c r="B129" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C129" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D129" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A130">
-        <v>62632125</v>
+        <v>22907448</v>
       </c>
       <c r="B130" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C130" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="D130" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A131">
-        <v>62539103</v>
+        <v>22447246</v>
       </c>
       <c r="B131" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="D131" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A132">
-        <v>62511872</v>
+        <v>24515070</v>
       </c>
       <c r="B132" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="C132" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="D132" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A133">
-        <v>62953213</v>
+        <v>23342937</v>
       </c>
       <c r="B133" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C133" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="D133" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A134">
-        <v>62510003</v>
+        <v>23520068</v>
       </c>
       <c r="B134" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="D134" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A135">
-        <v>62957147</v>
+        <v>23819105</v>
       </c>
       <c r="B135" t="s">
-        <v>237</v>
+        <v>30</v>
       </c>
       <c r="C135" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="D135" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A136">
-        <v>62641007</v>
+        <v>22565437</v>
       </c>
       <c r="B136" t="s">
-        <v>239</v>
+        <v>6</v>
       </c>
       <c r="C136" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A137">
-        <v>62609729</v>
+        <v>22238222</v>
       </c>
       <c r="B137" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C137" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="D137" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A138">
-        <v>62953073</v>
+        <v>22268048</v>
       </c>
       <c r="B138" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C138" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="D138" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A139">
-        <v>62956932</v>
+        <v>22408970</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C139" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A140">
-        <v>62956753</v>
+        <v>23151651</v>
       </c>
       <c r="B140" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C140" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="D140" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A141">
-        <v>62606752</v>
+        <v>22600273</v>
       </c>
       <c r="B141" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="D141" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A142">
-        <v>62609753</v>
+        <v>22244862</v>
       </c>
       <c r="B142" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C142" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="D142" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A143">
-        <v>62609755</v>
+        <v>22248259</v>
       </c>
       <c r="B143" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C143" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="D143" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A144">
-        <v>62505030</v>
+        <v>24759365</v>
       </c>
       <c r="B144" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="C144" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="D144" t="s">
-        <v>102</v>
+        <v>277</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A145">
-        <v>63051249</v>
+        <v>22354214</v>
       </c>
       <c r="B145" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="C145" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="D145" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A146">
-        <v>63016179</v>
+        <v>23430475</v>
       </c>
       <c r="B146" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C146" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="D146" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A147">
-        <v>62679181</v>
+        <v>23430669</v>
       </c>
       <c r="B147" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="D147" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A148">
-        <v>63051996</v>
+        <v>23490259</v>
       </c>
       <c r="B148" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="D148" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A149">
-        <v>63016125</v>
+        <v>23490774</v>
       </c>
       <c r="B149" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C149" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="D149" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A150">
-        <v>63016171</v>
+        <v>22384869</v>
       </c>
       <c r="B150" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C150" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="D150" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A151">
-        <v>63016353</v>
+      <c r="A151" t="s">
+        <v>4</v>
       </c>
       <c r="B151" t="s">
-        <v>266</v>
+        <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>267</v>
+        <v>4</v>
       </c>
       <c r="D151" t="s">
-        <v>257</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A152">
-        <v>63016312</v>
+      <c r="A152" t="s">
+        <v>4</v>
       </c>
       <c r="B152" t="s">
-        <v>268</v>
+        <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>4</v>
       </c>
       <c r="D152" t="s">
-        <v>257</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A153">
-        <v>63016355</v>
+      <c r="A153" t="s">
+        <v>4</v>
       </c>
       <c r="B153" t="s">
-        <v>270</v>
+        <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>271</v>
+        <v>4</v>
       </c>
       <c r="D153" t="s">
-        <v>257</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A154">
-        <v>63016163</v>
+      <c r="A154" t="s">
+        <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>273</v>
+        <v>4</v>
       </c>
       <c r="D154" t="s">
-        <v>257</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A155">
-        <v>62537311</v>
+      <c r="A155" t="s">
+        <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>274</v>
+        <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>275</v>
+        <v>4</v>
       </c>
       <c r="D155" t="s">
-        <v>276</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A156">
-        <v>62907942</v>
+      <c r="A156" t="s">
+        <v>4</v>
       </c>
       <c r="B156" t="s">
-        <v>277</v>
+        <v>4</v>
       </c>
       <c r="C156" t="s">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="D156" t="s">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A157">
-        <v>62530020</v>
+      <c r="A157" t="s">
+        <v>4</v>
       </c>
       <c r="B157" t="s">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>281</v>
+        <v>4</v>
       </c>
       <c r="D157" t="s">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A158">
-        <v>62910178</v>
+      <c r="A158" t="s">
+        <v>4</v>
       </c>
       <c r="B158" t="s">
-        <v>282</v>
+        <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>283</v>
+        <v>4</v>
       </c>
       <c r="D158" t="s">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A159">
-        <v>62907857</v>
+      <c r="A159" t="s">
+        <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>284</v>
+        <v>4</v>
       </c>
       <c r="C159" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
       <c r="D159" t="s">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A160">
-        <v>62909842</v>
+      <c r="A160" t="s">
+        <v>4</v>
       </c>
       <c r="B160" t="s">
-        <v>286</v>
+        <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>287</v>
+        <v>4</v>
       </c>
       <c r="D160" t="s">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A161">
-        <v>62530136</v>
+      <c r="A161" t="s">
+        <v>4</v>
       </c>
       <c r="B161" t="s">
-        <v>288</v>
+        <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>289</v>
+        <v>4</v>
       </c>
       <c r="D161" t="s">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A162">
-        <v>62530699</v>
+        <v>22058382</v>
       </c>
       <c r="B162" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C162" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D162" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A163">
-        <v>62907624</v>
+        <v>22885076</v>
       </c>
       <c r="B163" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C163" t="s">
+        <v>295</v>
+      </c>
+      <c r="D163" t="s">
         <v>293</v>
-      </c>
-      <c r="D163" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A164">
-        <v>62907814</v>
+        <v>22885528</v>
       </c>
       <c r="B164" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C164" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D164" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A165">
-        <v>62907946</v>
+        <v>22899293</v>
       </c>
       <c r="B165" t="s">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="C165" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D165" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A166">
-        <v>62530739</v>
+        <v>22316218</v>
       </c>
       <c r="B166" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C166" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D166" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A167">
-        <v>62530584</v>
+      <c r="A167" t="s">
+        <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>299</v>
+        <v>1</v>
       </c>
       <c r="C167" t="s">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="D167" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A168">
-        <v>62530583</v>
+      <c r="A168" t="s">
+        <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>302</v>
+        <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A169">
-        <v>62530657</v>
+      <c r="A169" t="s">
+        <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>303</v>
+        <v>1</v>
       </c>
       <c r="C169" t="s">
-        <v>304</v>
+        <v>2</v>
       </c>
       <c r="D169" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A170">
-        <v>62907179</v>
+      <c r="A170" t="s">
+        <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>305</v>
+        <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>306</v>
+        <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A171">
-        <v>62530190</v>
+      <c r="A171" t="s">
+        <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>307</v>
+        <v>1</v>
       </c>
       <c r="C171" t="s">
-        <v>308</v>
+        <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A172">
-        <v>62530769</v>
+      <c r="A172" t="s">
+        <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>307</v>
+        <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>309</v>
+        <v>2</v>
       </c>
       <c r="D172" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A173">
-        <v>62906599</v>
+      <c r="A173" t="s">
+        <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="C173" t="s">
-        <v>310</v>
+        <v>2</v>
       </c>
       <c r="D173" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A174">
-        <v>62908902</v>
+      <c r="A174" t="s">
+        <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>311</v>
+        <v>1</v>
       </c>
       <c r="C174" t="s">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="D174" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A175">
-        <v>62906523</v>
+      <c r="A175" t="s">
+        <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="C175" t="s">
-        <v>314</v>
+        <v>2</v>
       </c>
       <c r="D175" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A176">
-        <v>62906212</v>
+      <c r="A176" t="s">
+        <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>315</v>
+        <v>1</v>
       </c>
       <c r="C176" t="s">
-        <v>316</v>
+        <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A177">
-        <v>62906091</v>
+        <v>22199077</v>
       </c>
       <c r="B177" t="s">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="C177" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="D177" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A178">
-        <v>62910244</v>
+        <v>22032568</v>
       </c>
       <c r="B178" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C178" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="D178" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A179">
-        <v>62907739</v>
+        <v>22386470</v>
       </c>
       <c r="B179" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="C179" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D179" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A180">
-        <v>62908341</v>
+        <v>23762126</v>
       </c>
       <c r="B180" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C180" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="D180" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A181">
-        <v>62617467</v>
+        <v>22710322</v>
       </c>
       <c r="B181" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C181" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D181" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A182">
-        <v>62906564</v>
+        <v>22714388</v>
       </c>
       <c r="B182" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C182" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D182" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A183">
-        <v>62530124</v>
+        <v>23708181</v>
       </c>
       <c r="B183" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C183" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D183" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A184">
-        <v>62530781</v>
+        <v>22120047</v>
       </c>
       <c r="B184" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C184" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="D184" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A185">
-        <v>62530040</v>
+        <v>23804286</v>
       </c>
       <c r="B185" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C185" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D185" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A186">
-        <v>62906186</v>
+        <v>23804424</v>
       </c>
       <c r="B186" t="s">
-        <v>335</v>
+        <v>132</v>
       </c>
       <c r="C186" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D186" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A187">
-        <v>62909405</v>
+        <v>23560115</v>
       </c>
       <c r="B187" t="s">
-        <v>337</v>
+        <v>40</v>
       </c>
       <c r="C187" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A188">
-        <v>62906565</v>
+        <v>23560172</v>
       </c>
       <c r="B188" t="s">
-        <v>339</v>
+        <v>40</v>
       </c>
       <c r="C188" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A189">
-        <v>62908014</v>
+        <v>23550104</v>
       </c>
       <c r="B189" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="C189" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="D189" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A190">
-        <v>62530566</v>
+        <v>22894115</v>
       </c>
       <c r="B190" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C190" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="D190" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A191">
-        <v>62909183</v>
+        <v>23806662</v>
       </c>
       <c r="B191" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C191" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D191" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A192">
-        <v>62910193</v>
+        <v>23806145</v>
       </c>
       <c r="B192" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C192" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="D192" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A193">
-        <v>62530593</v>
+        <v>22895323</v>
       </c>
       <c r="B193" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C193" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="D193" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A194">
-        <v>62530624</v>
+        <v>22895333</v>
       </c>
       <c r="B194" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C194" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="D194" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A195">
-        <v>62530610</v>
+        <v>24519535</v>
       </c>
       <c r="B195" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C195" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="D195" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A196">
-        <v>62530629</v>
+        <v>22343172</v>
       </c>
       <c r="B196" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C196" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D196" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A197">
-        <v>62530715</v>
+        <v>22190866</v>
       </c>
       <c r="B197" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C197" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D197" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A198">
-        <v>62617623</v>
+        <v>24502907</v>
       </c>
       <c r="B198" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C198" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D198" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A199">
-        <v>62908130</v>
+        <v>22346661</v>
       </c>
       <c r="B199" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C199" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D199" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A200">
-        <v>62906044</v>
+        <v>23182250</v>
       </c>
       <c r="B200" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C200" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D200" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A201">
-        <v>62617977</v>
+        <v>23503014</v>
       </c>
       <c r="B201" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C201" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D201" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A202">
-        <v>62908186</v>
+        <v>22133034</v>
       </c>
       <c r="B202" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C202" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D202" t="s">
-        <v>279</v>
+        <v>354</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A203">
-        <v>62637257</v>
+        <v>23533083</v>
       </c>
       <c r="B203" t="s">
+        <v>355</v>
+      </c>
+      <c r="C203" t="s">
+        <v>356</v>
+      </c>
+      <c r="D203" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A204">
+        <v>22827600</v>
+      </c>
+      <c r="B204" t="s">
+        <v>357</v>
+      </c>
+      <c r="C204" t="s">
+        <v>358</v>
+      </c>
+      <c r="D204" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A205">
+        <v>22065581</v>
+      </c>
+      <c r="B205" t="s">
+        <v>360</v>
+      </c>
+      <c r="C205" t="s">
+        <v>361</v>
+      </c>
+      <c r="D205" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A206">
+        <v>23478033</v>
+      </c>
+      <c r="B206" t="s">
+        <v>362</v>
+      </c>
+      <c r="C206" t="s">
+        <v>363</v>
+      </c>
+      <c r="D206" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A207">
+        <v>22825904</v>
+      </c>
+      <c r="B207" t="s">
+        <v>364</v>
+      </c>
+      <c r="C207" t="s">
+        <v>365</v>
+      </c>
+      <c r="D207" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A208">
+        <v>24532232</v>
+      </c>
+      <c r="B208" t="s">
+        <v>366</v>
+      </c>
+      <c r="C208" t="s">
+        <v>367</v>
+      </c>
+      <c r="D208" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A209">
+        <v>22304327</v>
+      </c>
+      <c r="B209" t="s">
+        <v>174</v>
+      </c>
+      <c r="C209" t="s">
+        <v>368</v>
+      </c>
+      <c r="D209" t="s">
         <v>369</v>
       </c>
-      <c r="C203" t="s">
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A210">
+        <v>22877504</v>
+      </c>
+      <c r="B210" t="s">
         <v>370</v>
       </c>
-      <c r="D203" t="s">
+      <c r="C210" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A204" t="s">
-        <v>5</v>
-      </c>
-      <c r="B204" t="s">
-        <v>5</v>
-      </c>
-      <c r="C204" t="s">
-        <v>5</v>
-      </c>
-      <c r="D204" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A205" t="s">
-        <v>5</v>
-      </c>
-      <c r="B205" t="s">
-        <v>5</v>
-      </c>
-      <c r="C205" t="s">
-        <v>5</v>
-      </c>
-      <c r="D205" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A206" t="s">
-        <v>5</v>
-      </c>
-      <c r="B206" t="s">
-        <v>5</v>
-      </c>
-      <c r="C206" t="s">
-        <v>5</v>
-      </c>
-      <c r="D206" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A207" t="s">
-        <v>5</v>
-      </c>
-      <c r="B207" t="s">
-        <v>5</v>
-      </c>
-      <c r="C207" t="s">
-        <v>5</v>
-      </c>
-      <c r="D207" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A208" t="s">
-        <v>5</v>
-      </c>
-      <c r="B208" t="s">
-        <v>5</v>
-      </c>
-      <c r="C208" t="s">
-        <v>5</v>
-      </c>
-      <c r="D208" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A209" t="s">
-        <v>5</v>
-      </c>
-      <c r="B209" t="s">
-        <v>5</v>
-      </c>
-      <c r="C209" t="s">
-        <v>5</v>
-      </c>
-      <c r="D209" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A210" t="s">
-        <v>5</v>
-      </c>
-      <c r="B210" t="s">
-        <v>5</v>
-      </c>
-      <c r="C210" t="s">
-        <v>5</v>
-      </c>
       <c r="D210" t="s">
-        <v>5</v>
+        <v>372</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A211" t="s">
-        <v>5</v>
+      <c r="A211">
+        <v>23821416</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>373</v>
       </c>
       <c r="C211" t="s">
-        <v>5</v>
+        <v>374</v>
       </c>
       <c r="D211" t="s">
-        <v>5</v>
+        <v>372</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -4526,91 +4487,115 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A214">
-        <v>62530932</v>
+      <c r="A214" t="s">
+        <v>5</v>
       </c>
       <c r="B214" t="s">
-        <v>372</v>
+        <v>5</v>
       </c>
       <c r="C214" t="s">
-        <v>373</v>
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A215">
-        <v>62586305</v>
+      <c r="A215" t="s">
+        <v>5</v>
       </c>
       <c r="B215" t="s">
-        <v>374</v>
+        <v>5</v>
       </c>
       <c r="C215" t="s">
-        <v>375</v>
+        <v>5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A216">
-        <v>62585418</v>
+      <c r="A216" t="s">
+        <v>5</v>
       </c>
       <c r="B216" t="s">
-        <v>376</v>
+        <v>5</v>
       </c>
       <c r="C216" t="s">
-        <v>377</v>
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A217">
-        <v>62585862</v>
+      <c r="A217" t="s">
+        <v>5</v>
       </c>
       <c r="B217" t="s">
-        <v>378</v>
+        <v>5</v>
       </c>
       <c r="C217" t="s">
-        <v>379</v>
+        <v>5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A218">
-        <v>62903577</v>
+      <c r="A218" t="s">
+        <v>5</v>
       </c>
       <c r="B218" t="s">
-        <v>380</v>
+        <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>381</v>
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A219">
-        <v>62904484</v>
+      <c r="A219" t="s">
+        <v>5</v>
       </c>
       <c r="B219" t="s">
-        <v>382</v>
+        <v>5</v>
       </c>
       <c r="C219" t="s">
-        <v>383</v>
+        <v>5</v>
+      </c>
+      <c r="D219" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A220">
-        <v>62580296</v>
+      <c r="A220" t="s">
+        <v>5</v>
       </c>
       <c r="B220" t="s">
-        <v>384</v>
+        <v>5</v>
       </c>
       <c r="C220" t="s">
-        <v>385</v>
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A221">
-        <v>62581163</v>
+      <c r="A221" t="s">
+        <v>5</v>
       </c>
       <c r="B221" t="s">
-        <v>386</v>
+        <v>5</v>
       </c>
       <c r="C221" t="s">
-        <v>387</v>
+        <v>5</v>
+      </c>
+      <c r="D221" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Output/ContactosReporte.xlsx
+++ b/Data/Output/ContactosReporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frank\OneDrive\Documents\UiPath\UiPath_RPA_Adriana_Carrillo\Data\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660AC96D-6328-45FB-9307-469946BB40E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A94915-0135-47D4-A49C-28814A85FCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1817" yWindow="1817" windowWidth="16457" windowHeight="8966" xr2:uid="{723EF56F-89BA-4F5A-8EA8-F9BDFCB60ACD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="399">
   <si>
     <t>Número Telefónico</t>
   </si>
@@ -45,1111 +45,1183 @@
     <t>:: DATOS TELEFONICOS ::</t>
   </si>
   <si>
-    <t>DAVILA ANDRADE MERCEDES CECILIA DE LOS DOLORES</t>
-  </si>
-  <si>
-    <t>GALARZA DAVILA JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>NOVENA TRANSVERSAL 30 Y INTERVALLES NOVENA TRANSVERSAL</t>
-  </si>
-  <si>
-    <t>TUMBACO</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA SERGIO FRANCISCO</t>
-  </si>
-  <si>
-    <t>CALLE 1 0L Y CALLE 3 LOS ARUPOS S4-75 RUTA VIVA KM 8 TORRE A SAIN JOSEPH 305A TUMBACO LOS ARUPOS S4-75 RUTA VIVA KM 8 TORRE A SAIN JOSEPH 305A TUMBACO</t>
-  </si>
-  <si>
-    <t>CARLOS GUILLERMO DAVILA ARREGUI</t>
-  </si>
-  <si>
-    <t>ABDON CALDERON 0 L Y GONZALO DE VERA</t>
-  </si>
-  <si>
-    <t>DAVILA AGUILERA LUCRECIA MERCEDES</t>
-  </si>
-  <si>
-    <t>CAMINO DE LA VI�A 0 CONJUNTO ACANTHUS CASA 2 SECTOR LA VI�A TUMBACO JUANTO A CASETA DE LOS GUARDIAS CJT ACANTHUS-CASA 2-SECT LA VI�A-TUMBACO-JUANTO A CASETA-DE LOS GUARDIAS</t>
-  </si>
-  <si>
-    <t>ALBA DEL ROCIO DAVILA BAQUERO</t>
-  </si>
-  <si>
-    <t>ZARUMA 7N Y GENERAL RUMI�AHUI SECTOR EL RANCHO CONJ VICTTORIA CASA B7 SECTOR EL RANCHO CONJ VICTTORIA CASA B7</t>
-  </si>
-  <si>
-    <t>SANGOLQUI</t>
-  </si>
-  <si>
-    <t>ANDREA DAVILA VINTIMILLA</t>
-  </si>
-  <si>
-    <t>12 DE FEBRERO 0L 27 DE FEBRERO CONJUNTO EL CANELO CASA 8 27 DE FEBRERO CONJUNTO EL CANELO CASA 8</t>
-  </si>
-  <si>
-    <t>ARIAS DAVILA IVONNE ALEXANDRA</t>
-  </si>
-  <si>
-    <t>REINALDO FLOR 1L Y ANTONIO TANDAZO</t>
-  </si>
-  <si>
-    <t>AVILA DAVILA CESAR AUGUSTO</t>
-  </si>
-  <si>
-    <t>SELVA ALEGRE JATUMPUNGO AVENIDA ATAHUALPA 1087</t>
-  </si>
-  <si>
-    <t>BLANCA CECILIA DAVILA GUALOTU�A</t>
-  </si>
-  <si>
-    <t>AV JUAN SALINAS 0 Y NICOLAS PE�A BARRIO SELVA ALEGRE FRENTE AL COMPLEJO LA CASCADA</t>
-  </si>
-  <si>
-    <t>SANGOLQUI BARRIO INCHALILLO AUTOPISTA GENERAL RUMINIAHUI LOTE 11 E INES GANGOTENA JIJON</t>
-  </si>
-  <si>
-    <t>DAVILA ALVAREZ ELSA CECILIA</t>
-  </si>
-  <si>
-    <t>PASTAZA S21- 224 MANUEL CORDOVA GALARZA CASA 1 PISO CASA LADRILLO VISTO CASA-1 PISO-CASA-LADRILLO VISTO-- BARRIO SAN FRANCISCO DE CONOCOTO SECTOR EXTREMO SUR OCCIDENTAL A LADO DE CAPILLA</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE CARLOS HUMBERTO</t>
-  </si>
-  <si>
-    <t>CLUB LOS CHILLOS NARDOS LOTE 407</t>
-  </si>
-  <si>
-    <t>ASTUDILLO DAVILA FANNY LETICIA</t>
-  </si>
-  <si>
-    <t>LAS ALONDRAS 0 Y AV ILALO (CONJUNTO VALENCIA PLAZA CASA 22)</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO HARO DAVILA</t>
-  </si>
-  <si>
-    <t>ISLA PUNA 2L Y ISLA RABIDA</t>
-  </si>
-  <si>
-    <t>ALMEIDA DAVILA LUIS ULPIANO</t>
-  </si>
-  <si>
-    <t>SAN JOSE DE MINAS CALLE ANTONIO FLORES SN Y ELOY ALFARO</t>
-  </si>
-  <si>
-    <t>SAN JOSE DE MINAS</t>
-  </si>
-  <si>
-    <t>BURBANO DAVILA MARIA DE LAS MERCEDES FRANCISC</t>
-  </si>
-  <si>
-    <t>ALBERTO FREILE 0L HACIENDA LA VICTORIA HACIENDA- LA VICTORIA</t>
-  </si>
-  <si>
-    <t>CABEZAS DAVILA JOSE ENRIQUE</t>
-  </si>
-  <si>
-    <t>GARCIA MORENO SN 0 HERMANO MIGUEL CASACELESTE 2 PISOS CASA-CELESTE 2PS---- SECTOR 14 DE SEPTIEMBRE FRENTE DE LA ESCUELA CUMANDA</t>
-  </si>
-  <si>
-    <t>DAVILA ALARCON DAYSI JACQUELINE</t>
-  </si>
-  <si>
-    <t>LULUBAMBA 19Y Y ACURIA CND PARIS II CASA 1</t>
-  </si>
-  <si>
-    <t>SAN ANTONIO DE PICHINCHA</t>
-  </si>
-  <si>
-    <t>DAVILA ALBAN JORGE ANTONIO</t>
-  </si>
-  <si>
-    <t>SAN ANTONIO CALLE SN 200 METROS AL SUR DEL COLEGIO V DEL CONSUELO</t>
-  </si>
-  <si>
-    <t>DAVILA ANGELICA ANDRADE DE</t>
-  </si>
-  <si>
-    <t>AV. EQUINOCCIAL 0A Y AV. 13 DE JUNIO</t>
-  </si>
-  <si>
-    <t>CRESPO DAVILA GRACIELA JOHANNE</t>
-  </si>
-  <si>
-    <t>PASAJE E 276 ENTRE PASAJE I Y AVENIDA MARIANA DE JESUS COOPERATIVA JULIO ZABALA ENTRE PASAJE I Y-AV MARIANA DE-JESUS COOP JULIO-ZABALA</t>
-  </si>
-  <si>
-    <t>ROCAFUERTE (ESMERALDAS)</t>
-  </si>
-  <si>
-    <t>ACOSTA DAVILA RAFAEL ENRIQUE MANUEL</t>
-  </si>
-  <si>
-    <t>AVENIDA 10 DE AGOSTO 5019</t>
-  </si>
-  <si>
-    <t>QUITO</t>
-  </si>
-  <si>
-    <t>AGUILAR DAVILA GEORGINA PURIFICACION</t>
-  </si>
-  <si>
-    <t>LIZARDO RUIZ OE4- 747 DIEGO DE TAPIA ----- SECTOR BANCO DEL PICHINCHA BARRIO COTOCOLLAO TIENDA VIVERES EN GENERAL COLOR MOSTAZA 1PISO</t>
-  </si>
-  <si>
-    <t>AGUINAGA DAVILA CARLOS ANIBAL</t>
-  </si>
-  <si>
-    <t>PASAJE 6B-N69- 18 Y FRANCISCO DALMAU EDIFICIO VENTURA PISO 4 DEPARTAMENTO PH2 EDF-VENTURA-PISO-4-DEPT-PH2 SECTOR URB MARISOL</t>
-  </si>
-  <si>
-    <t>AGUINAGA DAVILA CECILIA VIOLETA</t>
-  </si>
-  <si>
-    <t>CTLL CONJUNTO HABT MABEREY CASA 15 AVENIDA DE LA PRENSA ENTRE GUALAQUIZA Y VALVERDE</t>
-  </si>
-  <si>
-    <t>AGUINAGA DAVILA FAUSTO MARINO</t>
-  </si>
-  <si>
-    <t>CALLE N74B E4-67 CERCA DE JOAQUIN MANCHENO Y ELOY ALFARO PANAMERICANA NORTE KILOMETRO 7 1/2 PANAMERICANA NORTE KM 7 1/2</t>
-  </si>
-  <si>
-    <t>AGUINAGA DAVILA JOSE MARIA</t>
-  </si>
-  <si>
-    <t>CARCELEN ALTO CALLE JOAQUIN MANCHENO E/4 65 Y AVENIDA ELOY ALFARO CARCELEN ALTO CALLE JOAQUIN MANCHENO E/4</t>
-  </si>
-  <si>
-    <t>ALBA ELIZABETH DAVILA ANDRADE</t>
-  </si>
-  <si>
-    <t>JOSE ARAGON OE3- 66 Y Y SALVADOR BRAVO solanda solanda SALVADOR BRAVO</t>
-  </si>
-  <si>
-    <t>ALEGRIA DAVILA BELGICA NIEVES ESTHER</t>
-  </si>
-  <si>
-    <t>SECTOR 1 SPMZ 3 MANZANA N CASA 2</t>
-  </si>
-  <si>
-    <t>ALEGRIA DAVILA BLANCA ELICIA</t>
-  </si>
-  <si>
-    <t>SECTOR LA ISLA MANZANA 3 CASA 18 PASAJE F</t>
-  </si>
-  <si>
-    <t>ALEXANDER PATRICIO DAVILA GRANIZO</t>
-  </si>
-  <si>
-    <t>CALLE 8 N67 148 Y FRANCISCO DALMAU URBANIZACION MAR Y SOL EDIFICIO SARA MARIA DEPARTAMENTO 2 URB MAR Y SOL-EDF SARA MARIA-DPTO-2 CALLE 8 N67</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO DAVILA SYLVITA MIREYA</t>
-  </si>
-  <si>
-    <t>MXA CONJUNTO XIMENA DEL ESTE CASA C SABANILLA Y MELCHOR TOAZA</t>
-  </si>
-  <si>
-    <t>ALVARADO DAVILA LUCIA EUGENIA</t>
-  </si>
-  <si>
-    <t>ESTOCOLMO 0 Y AVENIDA RIO AMAZONAS</t>
-  </si>
-  <si>
-    <t>ALVARADO DAVILA OSCAR MAURICIO</t>
-  </si>
-  <si>
-    <t>AVENIDA GASPAR DE VILLAROEL 1100 Y AVENIDA 6 DE DICIEMBRE CONJUNTO PARQUE REAL TORRE NOGAL 1 DEPARTAMENTO 84 AVENIDA GASPAR DE VILLAROEL</t>
-  </si>
-  <si>
-    <t>ALVAREZ DAVILA SILVIA KARINA</t>
-  </si>
-  <si>
-    <t>GUALAQUIZA OE4 88 Y AVENIDA DE LA PRENSA GUALAQUIZA OE4</t>
-  </si>
-  <si>
-    <t>AMORES DAVILA JOSE ARMANDO</t>
-  </si>
-  <si>
-    <t>FDC CN INQ CALLE LA TIERRA 358 Y AVENIDA DE LOS SHYRIS FDC CN INQ CALLE LA TIERRA</t>
-  </si>
-  <si>
-    <t>ANA KARIM ELIZABETH DAVILA CAICEDO</t>
-  </si>
-  <si>
-    <t>ANTONIO GRANDA CENTENO 0 Y ALVAREZ DEL CORRO EDIFICIO MANSION II / DEPARTAMENTO 501A EDIFICIO MANSION II / DEPARTAMENTO 501A ALVAREZ DEL CORRO</t>
-  </si>
-  <si>
-    <t>ANA LUCIA DAVILA PASTOR</t>
-  </si>
-  <si>
-    <t>AVIGIRAS 0Y Y DE LOS GUAYACANES EDIFICIO AMANECER, LOTE 241, PISO 3, DEPARTAMENTO 3 EDIFICIO AMANECER, LOTE 241, PISO 3, DEPARTAMENTO 3</t>
-  </si>
-  <si>
-    <t>ANA MARIA DAVILA LOPEZ</t>
-  </si>
-  <si>
-    <t>AVENIDA DE LA PRENSA 146 Y Y EDMUNDO CARVAJAL PASAJE ERNESTO MU�OZ PASAJE ERNESTO MU�OZ EDMUNDO CARVAJAL</t>
-  </si>
-  <si>
-    <t>A�AZCO DAVILA SARA BEATRIZ</t>
-  </si>
-  <si>
-    <t>INQ URBANIZACION INECEL CALLE A LOTE 15 Y DE LOS MOTILONES</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA CARLOS ARTURO</t>
-  </si>
-  <si>
-    <t>DIOGENES PAREDES PB D13 C1A</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>AVENIDA 9 DE OCTUBRE 729 PB ENTRE RAMIREZ DAVALOS Y VEINTIMILLA</t>
-  </si>
-  <si>
-    <t>ANDRADE DAVILA VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS TAMAYO 0 IGNACIO DE VEINTIMILLA EDIF TIZIANO PISO 7 DPTO 7E IGNACIO DE-VEINTIMILLA-EDIF TIZIANO-PISO 7 DPTO 7E SECT MARISCAL</t>
-  </si>
-  <si>
-    <t>AZCUNAGA 344 Y AVENIDA BRASIL EDIFICIO AQUAZUL PISO CUARTO DEPARTAMENTO 4C EDIFICIO-AQUAZUL-PISO-CUARTO-DEPARTAMENTO-4C AZCUNAGA</t>
-  </si>
-  <si>
-    <t>MARIANO HURTADO 175L Y ANTONIO ROMAN EDIF LA RIOJA-PISO 7-DEPT 7D-SECT MARISCAL-DEPT 7D-SECT MARISCAL MARIANO HURTADO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS TAMAYO 0 IGNACIO DE VEINTIMILLA EDIF TIZIANO PB LOCAL 3 IGNACIO DE-VEINTIMILLA-EDIF TIZIANO PB-LOCAL 3 SECT MARISCAL</t>
-  </si>
-  <si>
-    <t>ANDRADE ELDA DAVILA DE</t>
-  </si>
-  <si>
-    <t>SAN GREGORIO 270</t>
-  </si>
-  <si>
-    <t>ANDREA FERNANDA GRIJALVA DAVILA</t>
-  </si>
-  <si>
-    <t>DE LAS ANONAS 0 Y E12A esquinera en un edificio de 4 pisos esquinera en un edificio de 4 pisos E12A</t>
-  </si>
-  <si>
-    <t>ANDREA SOLEDAD GOMEZ DAVILA</t>
-  </si>
-  <si>
-    <t>SEYMUR SN</t>
-  </si>
-  <si>
-    <t>ANDRES VICENTE PRADO DAVILA</t>
-  </si>
-  <si>
-    <t>GUANGUILTAGUA N39 36 Y TOMAS BERMUR EDIF VISTA REAL PISO 3 DPTO 301 SECT PARQUE METROPOLITANO AL PISO 3 DPTO 301 SECT PARQUE METROPOLITANO</t>
-  </si>
-  <si>
-    <t>ANGELICA CRISTINA DAVILA PORTUGAL</t>
-  </si>
-  <si>
-    <t>JORGE GONZALEZ 0 Y CALLE RODRIGO MURIEL CONJ BRISAS DE CRISTAL BLOQUE C DPTO C23 SECTOR I�AQUITO ALTO FRENTE AL BOSQUE CONJ BRISAS DE CRISTAL BLOQUE C DPTO C23 SECTOR I�AQUITO ALTO FRENTE AL BOSQUE CALLE RODRIGO MURIEL</t>
-  </si>
-  <si>
-    <t>ANGULO DAVILA GLORIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>RAMIREZ DAVALOS E3- 42 Y AVENIDA 9 DE OCTUBRE EDIFICIO CONSULTORIO S MEDICOS ASOCIA PISO 6 CONSULTORIO 23 EDIF CONSULTORIO-S MEDICOS ASOCIA-PISO 6-CONSULTORIO 23 RAMIREZ DAVALOS E3-</t>
-  </si>
-  <si>
-    <t>ANIBAL AURELIANO SILVA DAVILA</t>
-  </si>
-  <si>
-    <t>RAFAEL CALVACHE N 954 Y Y LEONIDAS PUEBLA CJNT VENTURADA 2 PISO 3 CJNT VENTURADA 2 PISO 3 LEONIDAS PUEBLA</t>
-  </si>
-  <si>
-    <t>ARAUJO DAVILA CESAR AUGUSTO</t>
-  </si>
-  <si>
-    <t>EDIFICIO CIUDAD DE QUITO OFICINA 806 P8 AVENIDA NACIONES UNIDAS 193 Y AVENIDA 10 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>FERRUZOLA 0 CASA OE7-31 Y CRNL PINTAG CASA OE7-31 Y-CRNL.PINTAG. CDLA.YAGUACHI</t>
-  </si>
-  <si>
-    <t>ARAUJO DAVILA JOSE MARIA</t>
-  </si>
-  <si>
-    <t>GENERAL FLORES JUAN JOSE 150 Y VICENTE ROCAFUERTE GENERAL FLORES JUAN JOSE</t>
-  </si>
-  <si>
-    <t>ARAUJO DAVILA MARIA LUISA DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>MANABI SN 201 MONTUFAR CasaAMARILLA DE 2 PISOS CASA-AMARILLA DE 2 PISOS---- ALMACEN TUNGURAHUA FRENTE AL REGIMIENTO QUITO NUMERO 2</t>
-  </si>
-  <si>
-    <t>QC CALLE MANABI 201 Y MONTUFAR QC CALLE MANABI</t>
-  </si>
-  <si>
-    <t>ARBOLEDA DAVILA JOSE MARCO</t>
-  </si>
-  <si>
-    <t>CALLE SENA E8 44 Y PARIS PB ATRAS PB-ATRAS CALLE SENA E8</t>
-  </si>
-  <si>
-    <t>ARGUELLO DAVILA ESTEBAN ADRIANO</t>
-  </si>
-  <si>
-    <t>DE LOS TULIPANES 155 Y DE LOS ARUPOS CONJUNTO LA MIRAGE CASA 7B CJTO LA MIRAGE-CASA 7B DE LOS TULIPANES</t>
-  </si>
-  <si>
-    <t>ARIZAGA DAVILA LEONCIO ABELARDO</t>
-  </si>
-  <si>
-    <t>URBANIZACION EL CONDADO CALLE B LOTE 13</t>
-  </si>
-  <si>
-    <t>ARMIJOS DAVILA ANGEL GUSTAVO</t>
-  </si>
-  <si>
-    <t>URBANIZACION SANTA CECILIA DE LAS ACACIAS BEETHOVEN D 44</t>
-  </si>
-  <si>
-    <t>ARREGUI DAVILA SILVIA MORAYMA</t>
-  </si>
-  <si>
-    <t>TERESA DE CEPEDA 216 Y IGNACIO SAN MARIA URB-REAL ALTO TERESA DE CEPEDA</t>
-  </si>
-  <si>
-    <t>ARTURO DAVILA GLORIA DE LOURDES</t>
-  </si>
-  <si>
-    <t>VERSALLES 2039 Y BOLIVIA VERSALLES</t>
-  </si>
-  <si>
-    <t>ASTUDILLO DAVILA GLADYS ELENA</t>
-  </si>
-  <si>
-    <t>LUIS CADENA OE8- 173 Y CALLE OE8C -----</t>
-  </si>
-  <si>
-    <t>AULESTIA DAVILA CARLOS GUILLERMO</t>
-  </si>
-  <si>
-    <t>VF CONJUNTO HABT LOS LIBERTADORES DEPARTAMENTO A 6 23 P2 AVENIDA LOS LIBERTADORES Y CARANQUI</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA CLARA TERESA DE JESUS</t>
-  </si>
-  <si>
-    <t>SOLANDA SECTOR 3 SPMZ 1 MANZANA W CASA 12</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA ELENA NANCY ANGELICA</t>
-  </si>
-  <si>
-    <t>DE LOS CABILDOS N40- 13 HIDALGO DE PINTO CasaCREMA 6 PISOS CASA-CREMA 6 PISOS---- SCT QUITO TENIS</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA ERIKA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>AV. 10 DE AGOSTO 10663 Y AV. LUIS TUFI�O OE1-</t>
-  </si>
-  <si>
-    <t>AYALA DAVILA JUAN LAUREANO</t>
-  </si>
-  <si>
-    <t>FDC CN GMNI SAN FERNANDO CALLE H LOTE 152 Y CALLE C</t>
-  </si>
-  <si>
-    <t>BENALCAZAR DAVILA AIDA MARINA</t>
-  </si>
-  <si>
-    <t>AVENIDA PERIMETRAL E1- 171 PASAJE 31 CASA2 PISOS TAXO PISO 2 TIMBRE CASA-2 PISOS TAXO-PISO-2 TIMBRE-- SECTOR CARCELEN BAJO FRENTE A LA URB VALLE DE CARCELEN DIAGO</t>
-  </si>
-  <si>
-    <t>AVENIDA PERIMETRAL 0 CASA EI-176 URBANIZACION VALLE DE CARCELE CASA EI-176 URB-VALLE DE CARCELE</t>
-  </si>
-  <si>
-    <t>BETTI NARCISA NAVARRETE DAVILA</t>
-  </si>
-  <si>
-    <t>CRLN CONJUNTO RESIDENCIAL NAZARETH CASA 2 CALLE NAZARETH LOTE 594 Y AVENIDA 10 DE AGOSTO ZARETH LOTE 594 Y AVENIDA 10 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>BLANCA JACQUELINE DEL ROCIO PINTO DAVILA</t>
-  </si>
-  <si>
-    <t>AVENIDA MALDONADO 14205 Y CENTRO COMERCIAL EL RECREO LOCAL L-33 LOCAL-L-33 AVENIDA MALDONADO</t>
-  </si>
-  <si>
-    <t>AVENIDA ELOY ALFARO 0 Y PABLO ARTURO SUAREZ EDIFICIO TERRA DEPARTAMENTO 402 SECTOR LA CAROLINA EDIF TERRA-DPTO 402-SECT-LA CAROLINA AVENIDA ELOY ALFARO</t>
-  </si>
-  <si>
-    <t>AVENIDA ELOY ALFARO 0 Y PABLO ARTURO SUAREZ EDIFICIO TERRA DEPARTAMENTO 401 SECTOR CAROLINA EDIF TERRA-DPTO 401-SECT-CAROLINA AVENIDA ELOY ALFARO</t>
-  </si>
-  <si>
-    <t>AVENIDA MALDONADO 14205 Y CENTRO COMERCIAL EL RECREO LOCAL L-13 LOCAL-L-13 AVENIDA MALDONADO</t>
-  </si>
-  <si>
-    <t>BLANCA VIOLETA DAVILA JARAMILLO</t>
-  </si>
-  <si>
-    <t>GUALAQUIZA 365 Y TUFI�O MARINO GUALAQUIZA SN 365 AVENIDA TUFI�O CASA2 PISOS ROSADA LOTE365</t>
-  </si>
-  <si>
-    <t>BUSTOS DAVILA JACINTO FERNANDO</t>
-  </si>
-  <si>
-    <t>BELGICA 283</t>
-  </si>
-  <si>
-    <t>CABEZAS DAVILA ENRIQUE ARTURO</t>
-  </si>
-  <si>
-    <t>DIEGO DE ALMAGRO N26 114 Y LA NI�A EDIFICIO HERMITAGE PISO 3 DEPARTAMENTO 301 EDF-HERMITAGE-PISO-3-DEPT-301 DIEGO DE ALMAGRO N26</t>
-  </si>
-  <si>
-    <t>CABEZAS DAVILA NELSON GERARDO</t>
-  </si>
-  <si>
-    <t>CONJUNTO HAB LA TOLITA BL M N DPTON1</t>
-  </si>
-  <si>
-    <t>CAIZAPANTA DAVILA EDGAR OSWALDO</t>
-  </si>
-  <si>
-    <t>CALLE F E18 158 Y CALLE E COOPERATIVA ELOY ALFARO DE PUENGASI COOP ELOY-ALFARO-DE-PUENGASI CALLE F E18</t>
-  </si>
-  <si>
-    <t>CAIZAPANTA DAVILA RAMIRO PATRICIO</t>
-  </si>
-  <si>
-    <t>VICENTE ROCAFUERTE E3- 165 Y ANTONIO SALAS S1</t>
-  </si>
-  <si>
-    <t>CALDERON DAVILA JOSE RIGOBERTO</t>
-  </si>
-  <si>
-    <t>CALLE 6 127L CASA-127 SECT. CORAZON DE JESUS</t>
-  </si>
-  <si>
-    <t>CAMACHO DAVILA EUGENIA ALICIA</t>
-  </si>
-  <si>
-    <t>SEGUNDA TRANSVERSAL 2 Y SAN JOSE PB BARRIO AMAGASI DEL INCA PB BRR AMAGASI-DEL INCA SEGUNDA TRANSVERSAL</t>
-  </si>
-  <si>
-    <t>CARDENAS DAVILA BOLIVAR GUSTAVO</t>
-  </si>
-  <si>
-    <t>CARLOS ALVARADO N52 61 Y JOSE BARREIRO SECTOR MATOVELLE</t>
-  </si>
-  <si>
-    <t>ALVARADO CARLOS 5261 Y BARREIRO JOSE PISO 2 PISO-2 ALVARADO CARLOS</t>
-  </si>
-  <si>
-    <t>CARLA RENATA BUENO DAVILA</t>
-  </si>
-  <si>
-    <t>DIEGO COCHA N60 215 Y AV DEL MAESTRO</t>
-  </si>
-  <si>
-    <t>CARLOS ANDRES FABARA DAVILA</t>
-  </si>
-  <si>
-    <t>AVENIDA DIEGO DE VASQUEZ N77- 166 Y JUAN DE SELIS AVENIDA DIEGO DE VASQUEZ N77-</t>
-  </si>
-  <si>
-    <t>JULIO RAMOS 0 Y -</t>
-  </si>
-  <si>
-    <t>CARLOS ENRIQUE DAVILA RIVERA</t>
-  </si>
-  <si>
-    <t>EL LABRADOR 0 Y PABLO CASALS CASA 107</t>
-  </si>
-  <si>
-    <t>CASTILLO DAVILA FAUSTO VICENTE</t>
-  </si>
-  <si>
-    <t>CALLE 6 N54 254 Y JOSE SANCHEZ CONJUNTO RESIDENCIAL HOLANDA PISO 4 DEPARTAMENTO B8 L HOLANDA PISO 4 DEPARTAMENTO B8</t>
-  </si>
-  <si>
-    <t>CASTRO DAVILA EDITH MARISOL</t>
-  </si>
-  <si>
-    <t>AVIGIRAS 54 Y GUAYACANES PISO 4 DEPARTAMENTO 4 A PISO 4-DEPT 4 A AVIGIRAS</t>
-  </si>
-  <si>
-    <t>CATALINA DEL ROCIO DAVILA PAZMI�O</t>
-  </si>
-  <si>
-    <t>BARCELONA 551</t>
-  </si>
-  <si>
-    <t>CECILIA MAGDALENA DE LOURDES DAVILA FERNANDEZ</t>
-  </si>
-  <si>
-    <t>AVENIDA IO DE AGOSTO 6663 Y FALCONI AVENIDA IO DE AGOSTO</t>
-  </si>
-  <si>
-    <t>CEVALLOS DAVILA ANGELA VICTORIA</t>
-  </si>
-  <si>
-    <t>CRLN URBANIZACION LOS MASTODONTES CALLE 2/A LOTE 153 Y CALLE 2/5</t>
-  </si>
-  <si>
-    <t>CEVALLOS DAVILA FANNY EMPERATRIZ</t>
-  </si>
-  <si>
-    <t>CARCELEN BAJO PASAJE 12 N 91 54</t>
-  </si>
-  <si>
-    <t>CHAVEZ DAVILA AIDA GRIMANEZA</t>
-  </si>
-  <si>
-    <t>CALLE E3J 267 Y CALLE 5 CALLE E3J</t>
-  </si>
-  <si>
-    <t>CHAVEZ DAVILA GALO FERNANDO</t>
-  </si>
-  <si>
-    <t>INQ EDIFICIO MONTE ZERMAT DEPARTAMENTO 302 CALLE A LOTE A URBANIZACION COLINAS DEL PICHINCHA</t>
-  </si>
-  <si>
-    <t>CHIGUANO DAVILA DINA MARIA</t>
-  </si>
-  <si>
-    <t>CALLE B 507 Y CALLE G1 URBANIZACION PRADOS DEL CONDADO URB. PRADOS-DEL CONDADO CALLE B</t>
-  </si>
-  <si>
-    <t>CHRISTIAN LENIN RIJAS DAVILA</t>
-  </si>
-  <si>
-    <t>AV MARIANA DE JESUS 2E Y NU�O DE VALDERRAMA EDIFICIO SITIMED PISO 3 PEDP 305 EDIFICIO SITIMED PISO 3 PEDP 305</t>
-  </si>
-  <si>
-    <t>CISNEROS DAVILA MIRIAN JEANETTE</t>
-  </si>
-  <si>
-    <t>AVENIDA DE LOS SHYRIS N36- 90 Y SUECIA EDIFICIO HELEM PISO 7 DEPARTAMENTO 7 SUR EDF-HELEM-PISO-7-DEPT-7 SUR AVENIDA DE LOS SHYRIS N36-</t>
-  </si>
-  <si>
-    <t>IGNACIO BOSSANO E10 50 Y AVENIDA 6 DE DICIEMBRE EDIFICIO COLINAS DEL BATA N NOVENO PISO D PTO 9A EDF-COLINAS DEL BATA-N NOVENO PISO D-PTO 9A IGNACIO BOSSANO E10</t>
-  </si>
-  <si>
-    <t>CLARA LUZ DORILA DAVILA LLOCANA</t>
-  </si>
-  <si>
-    <t>ANDRES DE ARTIEDA OE4- 67 GASPAR CUJIAS ManzanaG Casa59 asa59</t>
-  </si>
-  <si>
-    <t>CONSTANTE DAVILA JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>SALEM JULIO TEODORO N57 217Y Y MZ 41 LOTE 5 LT 50 LT-50</t>
-  </si>
-  <si>
-    <t>CORREA DAVILA ISABEL DEL CISNE</t>
-  </si>
-  <si>
-    <t>LA FLORESTA</t>
-  </si>
-  <si>
-    <t>MERCEDES GONZALES OE4 118 Y EINSTEN ALBERTO URBANIZACION FLORESTA CRLEN URB-FLORESTA CRLEN MERCEDES GONZALEZ OE4</t>
-  </si>
-  <si>
-    <t>CRESPO DAVILA IVONNE CAROLINA</t>
-  </si>
-  <si>
-    <t>DIEGO DE VILLANUEVA E2- 26 Y BARTOLOME DE LA ROSA DIEGO DE VILLANUEVA E2-</t>
-  </si>
-  <si>
-    <t>CRESPO DAVILA LUIS ANTONIO</t>
-  </si>
-  <si>
-    <t>SEVILLA N24- 473 Y VIZCAYA ----- SEVILLA N24-</t>
-  </si>
-  <si>
-    <t>CRESPO DAVILA VERONICA MARIA CONSUELO</t>
-  </si>
-  <si>
-    <t>GUANGUILTAGUA N36 231 Y AROSEMENA TOLA GUANGUILTAGUA N36</t>
-  </si>
-  <si>
-    <t>DANIEL OSWALDO COLA DAVILA</t>
-  </si>
-  <si>
-    <t>CALLE Z 0 L Y RICARDO IZURIETA DEL CASTILLO barrio obrero independiente barrio obrero independiente RICARDO IZURIETA DEL CASTILLO</t>
-  </si>
-  <si>
-    <t>DAVALOS DAVILA TANIA ELIZABETH</t>
-  </si>
-  <si>
-    <t>VIRGIL MATIAS 144 GONZALO ZALDUMBIDE</t>
-  </si>
-  <si>
-    <t>DAVILA ABRIL ELSA PILAR</t>
-  </si>
-  <si>
-    <t>INQ EDIFICIO TORRE CRISTAL P4 CALLE SERGIO JATIVA 136 ENTRE BOSSANO Y BOSMEDIANO</t>
-  </si>
-  <si>
-    <t>DAVILA ABRIL NORA PATRICIA</t>
-  </si>
-  <si>
-    <t>EDIFICIO CENTRAL PARK DEPARTAMENTO 1C CARLOS TOBAR Y ELOY ALFARO ESQUINA</t>
-  </si>
-  <si>
-    <t>CARLOS TOBAR E6- 41 Y AVENIDA ELOY ALFARO CARLOS TOBAR E6-</t>
-  </si>
-  <si>
-    <t>SUIZA 209 Y AVENIDA ELOY ALFARO EDIFICIO CLINICA OFTALMOLOGICA SANTA LUCIA PISO 5 OF 501 EDF CLINICA-OFTALMOLOGICA-SANTA-LUCIA PISO 5-OF-501 SUIZA</t>
-  </si>
-  <si>
-    <t>AVENIDA MARIANA DE JESUS OE- 8 Y AVENIDA OCCIDENTAL EDIFICIO CENTRO MEDICO METROPOLI 0 EDF-CENTRO MEDICO-METROPOLI-0 AVENIDA MARIANA DE JESUS OE-</t>
-  </si>
-  <si>
-    <t>DAVILA ACOSTA CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>GUSTAVO VALLEJO 48 Y GONZALO ZALDUMBIDE</t>
-  </si>
-  <si>
-    <t>DAVILA AGUILAR FLAVIO JOEL</t>
-  </si>
-  <si>
-    <t>PEDRO CASTRILLON S42 289 Y Y CALLE S2H</t>
-  </si>
-  <si>
-    <t>DAVILA AGUILAR ROBERTO GUSTAVO</t>
-  </si>
-  <si>
-    <t>CALLE OE8F 32B Y CALLE S35D MANZANA SAN REMO CONJUNTO PALERMO SECTOR CHILLOGALLO MANZANA SAN-REMO-CONJUNTO-PALERMO-SECTOR-CHILLOGALLO CALLE OE8F</t>
-  </si>
-  <si>
-    <t>DAVILA AGUIRRE FAUSTO EDISON</t>
-  </si>
-  <si>
-    <t>ISLA SAN CRISTOBAL 546 Y ISLA FLOREANA PISO 3 PISO-3 ISLA SAN CRISTOBAL</t>
-  </si>
-  <si>
-    <t>DAVILA AGUIRRE RENE PAUL</t>
-  </si>
-  <si>
-    <t>JUAN PIO MONTUFAR 0A Y JOSE MEJIA LEQUERICA MZ 17 CASA 17 JUNTO A TIENDA</t>
-  </si>
-  <si>
-    <t>DAVILA ALARCON EULALIA SUSANA</t>
-  </si>
-  <si>
-    <t>LA LUZ KENEDY CONJUNTO COMENALCO 6 DE DICIEMBRE LOTE 11 Y FRESNOS</t>
-  </si>
-  <si>
-    <t>DAVILA ALBAN GUILLERMO NAPOLEON</t>
-  </si>
-  <si>
-    <t>CARAPUNGO SPMZ B 8 MANZANA O CASA 24</t>
-  </si>
-  <si>
-    <t>DAVILA ALBAN SILVIO MIGUEL</t>
-  </si>
-  <si>
-    <t>GUATEMALA 513 Y NUEVA YORK GUATEMALA</t>
-  </si>
-  <si>
-    <t>DAVILA ALFARO LUIS NAPOLEON</t>
-  </si>
-  <si>
-    <t>MARTINEZ MERA 123 Y AVENIDA CARLOS JULIO AROSEMENA MARTINEZ MERA</t>
-  </si>
-  <si>
-    <t>DAVILA ALFARO PIO ECUADOR</t>
-  </si>
-  <si>
-    <t>EL TIEMPO 7L DEPARTAMENTO 6 (ESTE) 6TO PISO EDIFICI ALCAZAR DEL ROCIO SECTOR EL BATAN DPTO 6 (ESTE)-6TO PISO EDIFICI-ALCAZAR DEL-ROCIO-SECT-EL BATAN</t>
-  </si>
-  <si>
-    <t>AVENIDA GASPAR DE VILLAROEL E11 95 Y AVENIDA 6 DE DICIEMBRE EDIFICIO MADERNA DEPARTAMENTO 801 EDF MADERNA-DPTO 801 AVENIDA GASPAR DE VILLAROEL E11</t>
-  </si>
-  <si>
-    <t>MSC CALLE CUERO Y CAICEDO OE453 Y CARVAJAL</t>
-  </si>
-  <si>
-    <t>DAVILA ALVAN CONSUELO LEONOR</t>
-  </si>
-  <si>
-    <t>LA PULIDA AVENIDA DE LA PRENSA 3389</t>
-  </si>
-  <si>
-    <t>DAVILA ALVAREZ CARLOS HERNAN</t>
-  </si>
-  <si>
-    <t>MARIANO HINOJOSA 0 DIEGO MONTANERO CONJUNTO RESIDENCIAL MADRIGAL CASA 3 DIEGO MONTANERO CONJUNTO RESIDENCIAL MADRIGAL CASA 3</t>
-  </si>
-  <si>
-    <t>DAVILA ALVAREZ MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ISLA MARCHENA N42 138 Y GRANADOS EDIFICIO PORTAL DE ARAGON TORRE 3 DEPARTAMENTO 604 PISO 6 EDF PORTAL DE-ARAGON TORRE 3-DP 604 PISO-6 ISLA MARCHENA N42</t>
-  </si>
-  <si>
-    <t>DAVILA ALVAREZ VIOLETA</t>
-  </si>
-  <si>
-    <t>AVENIDA GRANDA CENTENO 684 Y GALO ALVAREZ EDIFICIO MANSION IV PISO 5 DEPARTAMENTO B-502 SECTOR QUITO TENIS EDIF MANSION IV-PISO 5-DEPT B-502 SECT-QUITO TENIS AVENIDA GRANDA CENTENO</t>
-  </si>
-  <si>
-    <t>PAUL RIVET N31 02 Y WHYMPER PAUL RIVET</t>
-  </si>
-  <si>
-    <t>MULTF VERSALLES 1 SELVA ALEGRE Y VERSALLES DTO B11</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE MERCEDES SUSANA</t>
-  </si>
-  <si>
-    <t>LA NI�A 211 Y YANEZ PINZON EDIFICIO LAS CARABELAS 2DO PISO OFICINA 202 EDF LAS-CARABELAS-2DO PISO-OFICINA 202 LA NI�A</t>
-  </si>
-  <si>
-    <t>TORRES DEL PRADO BLOQUE 5 DEPARTAMENTO 401 INQ CALLE HERNANDEZ DE GIRON Y PEDREGAL</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE SYLVIA IVONNE</t>
-  </si>
-  <si>
-    <t>GARCIA MOREANO N57 86 Y NICOLAS ARTETA GARCIA MOREANO N57</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRANGO ENRIQUE DAVID</t>
-  </si>
-  <si>
-    <t>EL PINAR OE17 92 Y CAMACHO JUAN EL PINAR OE17</t>
-  </si>
-  <si>
-    <t>DAVILA ARAUJO BLANCA MARITZA</t>
-  </si>
-  <si>
-    <t>URBANIZACION MONJAS SECTOR 2 JARDIN DEL VALLE CALLE 22 CASA 616</t>
-  </si>
-  <si>
-    <t>DAVILA ARENA RUTH GEOCONDA</t>
-  </si>
-  <si>
-    <t>URBANIZACION EL BATAN LOTE 255</t>
-  </si>
-  <si>
-    <t>LA TIRRA 168 JUAN DE ALCANTARA</t>
-  </si>
-  <si>
-    <t>ANITA MARIANELA VELASCO DAVILA</t>
-  </si>
-  <si>
-    <t>PEDRO SOLANO 0 Y Y SAN JOSE DE OYAMBARILLO QUINTA CON PORTON LLAMDA EL CHINCHINAL QUINTA CON PORTON LLAMDA EL CHINCHINAL SAN JOSE DE OYAMBARILLO</t>
-  </si>
-  <si>
-    <t>PUEMBO</t>
-  </si>
-  <si>
-    <t>ARGUELLO DAVILA DIEGO OSWALDO</t>
-  </si>
-  <si>
-    <t>AV MANUEL CORDOVA GALARZA 0 Y MARCELINA NOLIVOS</t>
-  </si>
-  <si>
-    <t>POMASQUI</t>
-  </si>
-  <si>
-    <t>CARMEN ESTELA ACHIG DAVILA</t>
-  </si>
-  <si>
-    <t>AV. MANUEL CORDOVA GALARZA 0 Y EL EDEN CND LOS OLIVOS III CASA 35 CND-LOS OLIVOS III-CASA-35</t>
-  </si>
-  <si>
-    <t>CELSO HUMBERTO DAVILA HERRERA</t>
-  </si>
-  <si>
-    <t>EL ROSAL 160 Y LOS LUCEROS</t>
-  </si>
-  <si>
-    <t>CEVALLOS DAVILA JUAN ANGEL</t>
-  </si>
-  <si>
-    <t>DE LOS GUAYABOS 725 L Y LA PAMPA BL SEGUNDA AVENIDA BL-SEGUNDA AVENIDA</t>
-  </si>
-  <si>
-    <t>DE LOS GUAYABOS 725 L Y - BL AVELLANAS LA PAMPA BL-AVELLANAS LA PAMPA</t>
-  </si>
-  <si>
-    <t>DAVILA AGUILAR NELI HUILFRIDA</t>
-  </si>
-  <si>
-    <t>CALLE PRINCIPAL 252</t>
-  </si>
-  <si>
-    <t>PINTAG</t>
-  </si>
-  <si>
-    <t>AGUILERA DAVILA LUCRECIA BEATRIZ</t>
-  </si>
-  <si>
-    <t>NAYON 0 BARRIO SAN PEDRO LOTE 665 BRR. SAN PEDRO-LOTE 665</t>
-  </si>
-  <si>
-    <t>NAYON</t>
-  </si>
-  <si>
-    <t>ARGUELLO DAVILA HERMITA SOLEDAD</t>
-  </si>
-  <si>
-    <t>NAYON CALLE QUISQUIS 855 Y HUAYNA CAPAC NAYON CALLE QUISQUIS</t>
-  </si>
-  <si>
-    <t>QUISQUIS 451 N Y HUAYNA CAPAC</t>
-  </si>
-  <si>
-    <t>CALLE 1 5L Y CALLE A PRIMER PISO SECTOR MIRAVALLE PRIMER-PISO-SECTOR-MIRAVALLE CALLE 1</t>
-  </si>
-  <si>
-    <t>MIRAVALLE</t>
-  </si>
-  <si>
-    <t>CEVALLOS DAVILA ROSA YOLANDA</t>
-  </si>
-  <si>
-    <t>BENITEZ ANTONIO 9 COLOMBIA LT-9---- SECTOR MACHACHI CASA BLANCA 2 PISOS CASA ESQUINERA 3 CUADRAS AL NORTE DEL BANCO PICHINCHA</t>
-  </si>
-  <si>
-    <t>MACHACHI</t>
-  </si>
-  <si>
-    <t>CARLOS MANTILLA 0 Y Y LOS GERANIOS CONJ. KAIROS CASA 31</t>
-  </si>
-  <si>
-    <t>LAS NAVES</t>
-  </si>
-  <si>
-    <t>CORINA DE LAS MERCEDES NIVICELA DAVILA</t>
-  </si>
-  <si>
-    <t>CALLE L 397 Y CALLE N CALLE L</t>
-  </si>
-  <si>
-    <t>ANDREA MARIBEL DAVILA FEIJO</t>
-  </si>
-  <si>
-    <t>AV ILALO 0 Y CESAR ENRIQUE BALSECA CONJUNTO SAN FRANCISCO DE L AMERCED</t>
-  </si>
-  <si>
-    <t>LAS GOLONDRINAS</t>
-  </si>
-  <si>
-    <t>AVENDA�O DAVILA SEGUNDO RAFAEL</t>
-  </si>
-  <si>
-    <t>AVENIDA PATRICIO ROMERO 12 Y CALLE F MANZANA 26 SECTOR 2 DE MAYO NATIVIDAD MZ 26 SEC. 2 DE-MAYO NATIVIDAD AVENIDA PATRICIO ROMERO</t>
-  </si>
-  <si>
-    <t>LA VICTORIA COTOPAXI</t>
-  </si>
-  <si>
-    <t>BLANCA ROSA DEL CARMEN DAVILA ESPINOZA</t>
-  </si>
-  <si>
-    <t>PASAJE 8 37A Y PASAJE 7 PORTAL DEL LAGO</t>
-  </si>
-  <si>
-    <t>CARMEN DAVILA NUNGUI</t>
-  </si>
-  <si>
-    <t>VALLE HERMOSO 0 Y LA CONCORDIA casa color caf� de un piso frente a la tienda// contrato para 36 meses casa color caf� de un piso frente a la tienda// contrato para 36 meses LA CONCORDIA</t>
-  </si>
-  <si>
-    <t>CARRERA DAVILA FRANKLIN ORLANDO</t>
-  </si>
-  <si>
-    <t>JOSE GOMEZ 118 Y BORJA</t>
-  </si>
-  <si>
-    <t>CAJAS DAVILA MARIA LUISA</t>
-  </si>
-  <si>
-    <t>AMBATO 510 0 Y PICHINCHA</t>
-  </si>
-  <si>
-    <t>EL QUINCHE</t>
-  </si>
-  <si>
-    <t>ACOSTA DAVILA FABIAN OSWALDO</t>
-  </si>
-  <si>
-    <t>VALDIVIA 0 LOTE 4 DEPARTAMENTO 2A SECTOR SAN PATRICIO LOTE-4-DPTO-2A-SECTOR-SAN PATRICIO</t>
-  </si>
-  <si>
-    <t>CUMBAYA</t>
-  </si>
-  <si>
-    <t>CUMBAYA URBANIZACION REAL ALTO MACHALILLA CASA 51 Y COTOCOCHA</t>
-  </si>
-  <si>
-    <t>BUGANVILLAS 32L URBANIZACION AUQUI CHICO URB-AUQUI CHICO</t>
-  </si>
-  <si>
-    <t>CABEZAS DAVILA MARTHA JUDITH</t>
-  </si>
-  <si>
-    <t>LA PRIMAVERA I ETAPA LOTE 211</t>
-  </si>
-  <si>
-    <t>CARRILLO DAVILA LUIS RAMIRO</t>
-  </si>
-  <si>
-    <t>CUMBAYA URBANIZACION JARDINES DEL ESTE SEGUNDA ETAPA LOTE 43</t>
-  </si>
-  <si>
-    <t>CECILIA MAGDALENA DAVILA MOLINA</t>
-  </si>
-  <si>
-    <t>BARRIO LUMBISI CUMBAYA CALLE 89 LOTE SN FRENTE CENTRO ESPANOL</t>
-  </si>
-  <si>
-    <t>DAVILA ALVAREZ MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>URBANIZACION LA CA�ADA 3C Y VIA AL LIMONAR CUMBAYA</t>
-  </si>
-  <si>
-    <t>DAVILA ANDRADE JORGE RAUL</t>
-  </si>
-  <si>
-    <t>CUMBAYA URBANIZACION JARDINES DEL ESTE CALLE PEDRO CARLOS LOTE 27 CARLOS LOTE 27</t>
-  </si>
-  <si>
-    <t>PADRE CARLOS SN 27 FRAY FRANCISCO BENITEZ CasaCOLOR BLANCO 1 PISO R BLANCO 1 PISO</t>
-  </si>
-  <si>
-    <t>ALBERTO ALEJANDRO DAVILA JARA</t>
-  </si>
-  <si>
-    <t>CALLE OE7H- 7274O SECTOR 14 DE MARZO CONOCOTO // CASA IE7-274// FRANCISCO ROBLES SECTOR 14 DE MARZO CONOCOTO // CASA IE7-274// FRANCISCO ROBLES</t>
-  </si>
-  <si>
-    <t>CONOCOTO</t>
-  </si>
-  <si>
-    <t>ANA GABRIELA ESPINOSA DAVILA</t>
-  </si>
-  <si>
-    <t>CALLE C 67 Y CALLE A CIUDAD DE QUITO</t>
-  </si>
-  <si>
-    <t>ARAGON DAVILA JAIME ANDRES</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL LEON 0 Y ISMAEL SOLIS MIGUEL ANGEL LEON</t>
-  </si>
-  <si>
-    <t>CHAGUAY DAVILA FELIX ADOLFO</t>
-  </si>
-  <si>
-    <t>LLOQUE YUPANQUI N3- 214 Y HUAYNA - CAPAC</t>
-  </si>
-  <si>
-    <t>CORDOVA DAVILA HERNAN MARCELO</t>
-  </si>
-  <si>
-    <t>HUAYNA CAPAC N2 190 Y CAPAC YUPANQUI SECTOR SANATA MONICA HUAYNA CAPAC</t>
-  </si>
-  <si>
-    <t>CORREA DAVILA BELJICA IRENE</t>
-  </si>
-  <si>
-    <t>CALLE A 519 Y CALLE 1 BARRIO SANTA TERESITA DEL VAL BARRIO STA-TERESITA DEL VAL CALLE A</t>
-  </si>
-  <si>
-    <t>DAVILA AGUILAR LUIS PATRICIO</t>
-  </si>
-  <si>
-    <t>CONOCOTO 0 Y JUNTO LA SEVILLANA CASA 35 FRENTE AL COMPLEJO MEDICO DE PICHINCHA CONOCOTO</t>
-  </si>
-  <si>
-    <t>CALDERON DAVILA WILMA DIOCELINA</t>
-  </si>
-  <si>
-    <t>CALLE TULIPANES 48 Y CRISANTEMOS CALLE TULIPANES</t>
-  </si>
-  <si>
-    <t>CAYAMBE</t>
-  </si>
-  <si>
-    <t>DANIEL ADOLFO DAVILA HERRERA</t>
-  </si>
-  <si>
-    <t>23 DE JULIO 76 L Y VIA SANTO DOMINGO DE GUZMAN FRENTE A LA PARADA DE CAMIONETAS TRASNLEONES LOCAL CASA DE LA HUMITA FRENTE A LA PARADA DE CAMIONETAS TRASNLEONES LOCAL CASA DE LA HUMITA VIA SANTO DOMINGO DE GUZMAN</t>
-  </si>
-  <si>
-    <t>BOADA DAVILA JANNETH ALEXANDRA</t>
-  </si>
-  <si>
-    <t>PANAMERICANA NORTE KILOMETRO 14 1/2 8L Y PASAJE CENEPA JUNTO A CARPAG SECTOR SAN CAMILO DE CALDERON JUNTO A CARPAG-SECTOR SAN-CAMILO-DE CALDERON</t>
-  </si>
-  <si>
-    <t>CALDERON</t>
-  </si>
-  <si>
-    <t>CABEZAS DAVILA SEGUNDO RICARDO</t>
-  </si>
-  <si>
-    <t>CALDERON BARRIO MARIANA DE JESUS JUNTO A EMETEL</t>
-  </si>
-  <si>
-    <t>CASTRO DAVILA HECTOR GERMAN</t>
-  </si>
-  <si>
-    <t>EL ARENAL 26 Y PANAMERICANA NORTE SECTOR CARAPUNGO CASALES BUENAVENTURA ETAPA II CASA 26 SECTOR CARAPUNGO CASALES BUENAVENTURA ETAPA II CASA 26</t>
-  </si>
-  <si>
-    <t>CRISTELA MATILDE DAVILA DAVILA</t>
-  </si>
-  <si>
-    <t>NUEVA YORK 0 Y LUGO LUGO</t>
-  </si>
-  <si>
-    <t>CUEVA DAVILA JEAN PAUL</t>
-  </si>
-  <si>
-    <t>UNION Y JORGE MURILLO 54L</t>
-  </si>
-  <si>
-    <t>ATAHUALPA BARRIO EL TRIUNFO CALLE PRINCIPAL 905 CALLE K</t>
-  </si>
-  <si>
-    <t>ATAHUALPA</t>
-  </si>
-  <si>
-    <t>ALICIA MARIA DE LOURDES TALAVERA DAVILA</t>
-  </si>
-  <si>
-    <t>FEDERICO GONZALES SUAREZ 0 Y MANUEL DURINI</t>
-  </si>
-  <si>
-    <t>AMAGUANA</t>
-  </si>
-  <si>
-    <t>CARMEN NARCISA DEL JESUS DAVILA TOLEDO</t>
-  </si>
-  <si>
-    <t>JOSE DE LA CUADRA 0 Y ALVAREZ RICARDO CASA 2 PISOS CASA-2 PISOS JOSE DE LA CUADRA</t>
+    <t>CABRERA CADENA WILSON EDMUNDO</t>
+  </si>
+  <si>
+    <t>CADENA FELIX CARMEN DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>SUCRE 0 Y ANTONIO ANTE CASA DE 1PISO MELON FRENTE AL ESTADIO CASA DE 1PISO-MELON FRENTE AL SUCRE</t>
+  </si>
+  <si>
+    <t>URCUQUI</t>
+  </si>
+  <si>
+    <t>CADENA RAMOS EDMUNDO FABIAN</t>
+  </si>
+  <si>
+    <t>MAGDALENA VARELA 1916 Y Y CALLE SIN NOMBRE CALLE SIN NOMBRE</t>
+  </si>
+  <si>
+    <t>BOADA CADENA ISOLINA JUDITH</t>
+  </si>
+  <si>
+    <t>JUAN MONTALVO 0 Y ATAHUALPA CASA DOS PISOS CASA DOS PISOS ATAHUALPA</t>
+  </si>
+  <si>
+    <t>SAN PABLO</t>
+  </si>
+  <si>
+    <t>CADENA GARCIA MARIA VIRGINIA JUDITH</t>
+  </si>
+  <si>
+    <t>ABDON CALDERON SN 0 CHIRIBOGA CasaPORTON NEGRO CASA-PORTON NEGRO---- JUNTO EL COLISEO DEL COLEGIO NORMAL</t>
+  </si>
+  <si>
+    <t>CADENA CANDO ALVARO DANIEL</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO DAVILA 873 Y ARMANDO HIDROVO YUYUCOCHA LUIS EDUARDO DAVILA</t>
+  </si>
+  <si>
+    <t>SAN LUIS DE CARANQUI</t>
+  </si>
+  <si>
+    <t>CADENA CHAFUEL YOLANDA PATRICIA</t>
+  </si>
+  <si>
+    <t>PRINCESA PACHA 840 Y Y AV. EL RETORNO</t>
+  </si>
+  <si>
+    <t>CADENA CHILUISA DAVID ANDRES</t>
+  </si>
+  <si>
+    <t>AV ATAHUALPA 61 Y RIO TIPUTINI CONJUNTO LA CASTELLANA CASA 61</t>
+  </si>
+  <si>
+    <t>CADENA REVELO MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JACINTO COLLAHUAZO 0 Y NAZACOTA PUENTO JUNTO A EDIFICIO, PORTON BLANCO</t>
+  </si>
+  <si>
+    <t>CADENA TARAMUEL MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>PASAJE SIN NOMBRE 0 CIUDADELA MUNICIPAL 1 PISO TOMATE CDLA MUNICIPAL-1 PISO TOMATE FRENTE AL DIVINO NI�O</t>
+  </si>
+  <si>
+    <t>CAZARES CADENA ROSARIO BEATRIZ</t>
+  </si>
+  <si>
+    <t>HERNAN GONZALEZ DE SAA 0 Y PRINCESA PACHA HERNAN GONZALEZ DE SAA</t>
+  </si>
+  <si>
+    <t>DE LA CADENA SIMON BOLIVAR</t>
+  </si>
+  <si>
+    <t>LOS INCAS 11 Y ERNESTO FLORES</t>
+  </si>
+  <si>
+    <t>GUERRERO CADENA CLEMENCIA MAGOLA</t>
+  </si>
+  <si>
+    <t>HUIRACOCHA 1086 Y DUCHICELA HUIRACOCHA</t>
+  </si>
+  <si>
+    <t>CADENA ALMEIDA MARTHA CECILIA</t>
+  </si>
+  <si>
+    <t>VIA A BELLAVISTA 0 Y PANAMERICANA NORTE CASA 1 PISO CASA-1 PISO VIA A BELLAVISTA</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO DE IBARRA</t>
+  </si>
+  <si>
+    <t>27 DE NOVIEMBRE 827L Y GUILLON PONTON</t>
+  </si>
+  <si>
+    <t>CADENA CEVALLOS ROSA MAGDALENA</t>
+  </si>
+  <si>
+    <t>CARLOS MONTUFAR 0 Y HERMANOS MIDEROS 2 PISOS NARANJA CARLOS MONTUFAR</t>
+  </si>
+  <si>
+    <t>CADENA MORALES CARLOS VINICIO</t>
+  </si>
+  <si>
+    <t>LINEA FERREA 0 Y CALLE SIN NOMBRE BARRIO SANTA CLARA</t>
+  </si>
+  <si>
+    <t>CADENA PINEDA SARA BEATRIZ</t>
+  </si>
+  <si>
+    <t>27 DE NOVIEMBRE SN 337 CAMILO POMPEYO CasaSALNOM 3 PISOS CASA-SALNOM 3 PISOS---- BARRIO NORTE FRENTE AL PARQUE ELEODORO AYALA HAY ROTULO ARTESANIAS ESPINOZA</t>
+  </si>
+  <si>
+    <t>CADENA ZUMARRAGA JAVIER ANGEL</t>
+  </si>
+  <si>
+    <t>RAMON TEANGA 0 Y CALLE SIN NOMBRE</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA LIDIA MADALUN</t>
+  </si>
+  <si>
+    <t>PANAMERICANA 0 Y CORREDOR PERIFERICO SUR CHORLAVI ALTO CHORLAVI ALTO CORREDOR PERIFERICO SUR</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA PAZ VICTORIA</t>
+  </si>
+  <si>
+    <t>CALLE SIN NOMBRE 0 Y LUIS ENRIQUE CEVALLOS FRENTE A JARDIN 2 PISOS ROSADA CALLE SIN NOMBRE</t>
+  </si>
+  <si>
+    <t>CADENA CACUANGO ELSA GUADALUPE</t>
+  </si>
+  <si>
+    <t>LAS MAGNOLIAS 0 Y EL ROSAL LAS MAGNOLIAS</t>
+  </si>
+  <si>
+    <t>PUGACHO</t>
+  </si>
+  <si>
+    <t>GARCIA CADENA GLORIA MARLENE</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL ROSITA PAREDES 451 Y PASAJE A CALLE PRINCIPAL ROSITA PAREDES</t>
+  </si>
+  <si>
+    <t>CADENA GONZALEZ MARICELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>VIA MARIANO ACOSTA SN 0 CASAROSADA 1 PISO CASA-ROSADA 1 PISO---- BARRIO MIRADOR EN LA TIENDA VIVERES EL MIRADOR A MEDIA CUADR</t>
+  </si>
+  <si>
+    <t>PIMAMPIRO</t>
+  </si>
+  <si>
+    <t>CADENA NARVAEZ MARIA DEL CARMEN AMELIA</t>
+  </si>
+  <si>
+    <t>CERRO DE LOS PICACHOS SN 3048 RIO CORDOVA Casa1 PISO CasaBLANCA CASA-1 PISO-CASA-BLANCA-- SECT PIMAMPIRO BARRIO SANTA LUCIA;FRENTE A UNA EN CONSTRUCION CON VENTANAS VERDE</t>
+  </si>
+  <si>
+    <t>GUERRON CADENA MERY LILIAN</t>
+  </si>
+  <si>
+    <t>VIA ORIENTAL 0 Y AYACUCHO VIA ORIENTAL</t>
+  </si>
+  <si>
+    <t>CADENA AYALA HIPATIA SHOVASQUY</t>
+  </si>
+  <si>
+    <t>GALO PLAZA 1327 Y CALLE SIN NOMBRE</t>
+  </si>
+  <si>
+    <t>PASTOCALLE</t>
+  </si>
+  <si>
+    <t>CADENA BAEZ LUIS ERNESTO</t>
+  </si>
+  <si>
+    <t>OTAVALO CIUDADELA COLLAHUASO 1 PEDRO NARVAEZ 405</t>
+  </si>
+  <si>
+    <t>OTAVALO</t>
+  </si>
+  <si>
+    <t>CADENA BAEZ WASHINGTON MARCELO</t>
+  </si>
+  <si>
+    <t>OTAVALO LEOPOLDO CHAVEZ 188 CIUDADELA 31 DE OCTUBRE</t>
+  </si>
+  <si>
+    <t>CADENA CIFUENTES SOFIA ROXANA</t>
+  </si>
+  <si>
+    <t>CORAZAS 331 Y Y JUAN ALVARRACIN CASA CO LA PALMERA GRANDE</t>
+  </si>
+  <si>
+    <t>CADENA DELGADO ANA CRISTINA</t>
+  </si>
+  <si>
+    <t>PANAMAERICANA 0Y Y AURELIO UBIDIA CONJUNTO SAN MARTIN FRENTE UPC</t>
+  </si>
+  <si>
+    <t>LOS CORAZAS 0 Y JOSE SANCHEZ</t>
+  </si>
+  <si>
+    <t>CADENA HERRERA PATRICIO URIBE</t>
+  </si>
+  <si>
+    <t>MORALES 208 Y SUCRE FRENTE YURATOURS FRENTE-YURATOURS MORALES</t>
+  </si>
+  <si>
+    <t>CADENA VIZCAINO JESUS MESIAS</t>
+  </si>
+  <si>
+    <t>CALLE 5 238 Y VIA A SELVA ALEGRE CALLE 5</t>
+  </si>
+  <si>
+    <t>CEVALLOS CADENA MYRIAN SOLEDAD</t>
+  </si>
+  <si>
+    <t>VICENTE ZAMORA 47 Y JUAN ROJAS CASA DE DOS PISOS DE LADRILLO, A MANO IZQUIERDA DE LA CALLE JUAN ROJAS</t>
+  </si>
+  <si>
+    <t>EUGENIA MARGARITA CUASPUD CADENA</t>
+  </si>
+  <si>
+    <t>MOJANDA 0Y Y TEJERIA PUNYARO JUNTO A LA CASA VERDE</t>
+  </si>
+  <si>
+    <t>JUAN FRANCISCO CADENA CARVAJAL</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL 8 Y CALLE SIN NOMBRE CDLA MARIA JOSE CASA 1P/ JUNTO AL POSTE FRENTE A UNA TIENDA CERCA AL ESTADIO CERCA AL ESTADIO</t>
+  </si>
+  <si>
+    <t>LUPE IRENE PADILLA CADENA</t>
+  </si>
+  <si>
+    <t>ROCAFUERTE 0 Y GUAYAQUIL</t>
+  </si>
+  <si>
+    <t>FAUSTO POLIVIO LUCERO CADENA</t>
+  </si>
+  <si>
+    <t>29 DE JULIO 0 Y VELASCO IBARRA</t>
+  </si>
+  <si>
+    <t>NATABUELA</t>
+  </si>
+  <si>
+    <t>GERMAN AQUILINO CADENA</t>
+  </si>
+  <si>
+    <t>VENCEDORES 0 Y FLORES VASQUEZ</t>
+  </si>
+  <si>
+    <t>CEVALLOS CADENA ALVARO NAPOLEON</t>
+  </si>
+  <si>
+    <t>IMBABURA 0 Y BOLIVAR CASA 1P CON CERAMICA NEGRA EN DEPODITO DE GAS</t>
+  </si>
+  <si>
+    <t>ILUMAN</t>
+  </si>
+  <si>
+    <t>CEVALLOS CADENA MARLENE AMPARO</t>
+  </si>
+  <si>
+    <t>ILUMAN CALLE PRINCIPAL VIA A SAN PABLO</t>
+  </si>
+  <si>
+    <t>AIDA ANGELICA USI�A CADENA</t>
+  </si>
+  <si>
+    <t>ARMANDO HIDROVO 137 Y CALLE SIN NOMBRE</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>AIDA MARIA CADENA AIDA</t>
+  </si>
+  <si>
+    <t>JUAN MARTINEZ DE ORBE 0 Y Y VIA URCUQUI VIA URCUQUI</t>
+  </si>
+  <si>
+    <t>ALBERTO JAVIER POZO CADENA</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO DEL TEJAR 0 Y CALLE SIN NOMBRE LA BOLA VERDE CERCA A LA CARPINTERIA</t>
+  </si>
+  <si>
+    <t>ANDINO CADENA ERCILIA MARGOTH</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA LOS CEIBOS RIO DAULE 249</t>
+  </si>
+  <si>
+    <t>ARMAS CADENA ZOILA GUADALUPE</t>
+  </si>
+  <si>
+    <t>IBARRA ELIAS ALMEIDA 827 Y GABRIELA MISTRAL IBARRA ELIAS ALMEIDA</t>
+  </si>
+  <si>
+    <t>ARTEAGA CADENA HERIBERTO NEPTALI</t>
+  </si>
+  <si>
+    <t>URUGUAY 426 Y VENEZUELA CIUDADELA CIUDAD DE IBARRA CDLA. CIUDAD DE-IBARRA URUGUAY</t>
+  </si>
+  <si>
+    <t>URUGUAY 426 Y VENEZUELA ATRAS DEL ESTADIO RANKIN SKINER</t>
+  </si>
+  <si>
+    <t>ARTEAGA CADENA HILDA XIMENA</t>
+  </si>
+  <si>
+    <t>PARAGUAY 342 Y MEXICO</t>
+  </si>
+  <si>
+    <t>ARTEAGA CADENA MERCEDES FRANDILA</t>
+  </si>
+  <si>
+    <t>IBARRRA URBANIZACION SAN ANDRES LATACUNGA Y ARTURO H R LOTE 62</t>
+  </si>
+  <si>
+    <t>BENAVIDES CADENA GONZALO ELOY</t>
+  </si>
+  <si>
+    <t>PORTOVIEJO 0 Y Y RIOBAMBA CASA CASA CASA-CASA</t>
+  </si>
+  <si>
+    <t>BENAVIDES CADENA ROSA ISABEL</t>
+  </si>
+  <si>
+    <t>IBARRA ZUMBA 642</t>
+  </si>
+  <si>
+    <t>BETTY SULAY PROA�O CADENA</t>
+  </si>
+  <si>
+    <t>IBARRA MEJIA 677</t>
+  </si>
+  <si>
+    <t>BOANERGES RENEY CADENA ESCOBAR</t>
+  </si>
+  <si>
+    <t>AV JOSE TOBAR 681 Y ELEODORO AYALA</t>
+  </si>
+  <si>
+    <t>IBARRA YACUCALLE LUIS E DAVILA 3157 Y RICARDO SANCHEZ IBARRA YACUCALLE LUIS E DAVILA</t>
+  </si>
+  <si>
+    <t>CADENA ALMEIDA DORA PILAR</t>
+  </si>
+  <si>
+    <t>RIO CHIMBO 0 Y RIO BLANCO CASA 2 PISOS COLOR BLANCA CON FRANJA ROSADA CA CON FRANJA ROSADA</t>
+  </si>
+  <si>
+    <t>CADENA ALVEAR JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>PEDRO CARVALLO 0 Y JOSE NICOLAS HIDALGO</t>
+  </si>
+  <si>
+    <t>CADENA ANDINO MARIA DE LOURDES</t>
+  </si>
+  <si>
+    <t>IBARRA 540 Y ISLA FERNANDINA 2 PISOS OBRA NEGRA 2 PISOS-OBRA NEGRA IBARRA</t>
+  </si>
+  <si>
+    <t>CADENA ARIAS NAYBE MARLENE</t>
+  </si>
+  <si>
+    <t>JOSE NICOLAS VACAS 146 Y LUIS VARGAS TORRES JOSE NICOLAS VACAS</t>
+  </si>
+  <si>
+    <t>CADENA ARMAS DIEGO VINICIO</t>
+  </si>
+  <si>
+    <t>PI�AN 977 Y VELASCO PI�AN</t>
+  </si>
+  <si>
+    <t>CADENA BENALCAZAR WILSON HUMBERTO</t>
+  </si>
+  <si>
+    <t>RAFAEL DE TROYA 846 Y JUAN HERNANDEZ INSTALACION A CUALQUIER DIA A PARTIR DE 10 AM</t>
+  </si>
+  <si>
+    <t>SANCHEZ Y CIFUENTES 447</t>
+  </si>
+  <si>
+    <t>CADENA BLANCA BLANCA ESPERANZA</t>
+  </si>
+  <si>
+    <t>CALLE S/N 2 MANZANA B LOS LAURELES</t>
+  </si>
+  <si>
+    <t>CADENA CADENA CONSUELO DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ROCAFUERTE 433 Y GARCIA MORENO CASA 2 PISOS</t>
+  </si>
+  <si>
+    <t>CADENA CARLOS EDUARDO</t>
+  </si>
+  <si>
+    <t>SAN CRISTOBAL 241 Y ENTRE RIOBAMBA Y AMBATO IBARRA SAN CRISTOBAL 241</t>
+  </si>
+  <si>
+    <t>CADENA CHAFUEL LUIS ANIBAL</t>
+  </si>
+  <si>
+    <t>IBARRA AVENIDA EL RETORNO 2973</t>
+  </si>
+  <si>
+    <t>CADENA DAVILA FABRICIO ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAMON ALARCON 0 Y AV. JAIME ROLDOS AGUILERA AV. JAIME ROLDOS AGUILERA</t>
+  </si>
+  <si>
+    <t>AV. CAP. CRISTOBAL DE TROYA 1045 Y PIEDAD GOMEZ JURADO CASA 1 CASA-1 MIGRACION LINEA</t>
+  </si>
+  <si>
+    <t>CADENA DIAZ YOLANDA CATALINA</t>
+  </si>
+  <si>
+    <t>IBARRA PASAJE B MANZANA 14 CASA 26</t>
+  </si>
+  <si>
+    <t>CADENA EGAS MARIA ELENA</t>
+  </si>
+  <si>
+    <t>AV EL RETORNO 14 Y NAZACOTA PUENTO CONJUNTO CASALES VI�A II CASA 14</t>
+  </si>
+  <si>
+    <t>CADENA ESCOBAR JORGE ABRAHAM</t>
+  </si>
+  <si>
+    <t>OVIEDO 0 Y SUCRE</t>
+  </si>
+  <si>
+    <t>CADENA ESTRADA ANIBAL ADRIANO</t>
+  </si>
+  <si>
+    <t>NICOLAS GOMEZ TOBAR 140 Y - BARRIO GALO LARREA</t>
+  </si>
+  <si>
+    <t>CADENA ESTRADA LIBIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>REDONDEL DE AJAVI 1 Y - PLZ DE AJAVI GRANDE SN</t>
+  </si>
+  <si>
+    <t>CADENA FELIX FELIX HIPOLITO</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA C DE IBARRA VENEZUELA Y BRASIL S/N</t>
+  </si>
+  <si>
+    <t>CADENA GONZALEZ BERTILDE</t>
+  </si>
+  <si>
+    <t>RIO JUBONES 396 Y RIO AMBI ..</t>
+  </si>
+  <si>
+    <t>CADENA GUATEMAL HUMBERTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ Y CIFUENTES 2199 Y TOBIAS MENA PLANTA BAJA .</t>
+  </si>
+  <si>
+    <t>CADENA GUATEMAL MARIA ERNESTINA</t>
+  </si>
+  <si>
+    <t>LOJA 434 Y AV. 13 DE ABRIL CASA DE DOS PISOS LADRILLO A UNA CUADRA MAS ARRIBA DEL IDCA</t>
+  </si>
+  <si>
+    <t>CADENA HONORIO RICARDO</t>
+  </si>
+  <si>
+    <t>J M LEORO IBARRA FRAY BARTOLOME DE LAS CASAS 1128</t>
+  </si>
+  <si>
+    <t>CADENA JORGE JORGE AMADOR</t>
+  </si>
+  <si>
+    <t>IBARRA PASAJE E MANZANA 29 CASA 21</t>
+  </si>
+  <si>
+    <t>CADENA LOMAS ANGEL ISAAC</t>
+  </si>
+  <si>
+    <t>NELSON MANDELA 105 Y DIEGO DE ALMAGRO CASA DE UN PISO LA PRIMAVERA/LA CAMPI�A CASA-DE UN PISO NELSON MANDELA</t>
+  </si>
+  <si>
+    <t>NELSON MANDELA 1120 Y DIEGO DE ALMAGRO NELSON MANDELA 1120 Y DIEGO DE ALMAGRO</t>
+  </si>
+  <si>
+    <t>CADENA MARIA FIDELINA</t>
+  </si>
+  <si>
+    <t>IBARRA 0 Y ISLA SANTA ISABEL</t>
+  </si>
+  <si>
+    <t>CADENA MIER SANDRA ZULAY</t>
+  </si>
+  <si>
+    <t>PASAJE 0Y Y COTOPAXI CASA 2 PISOS COLOR CREMA CON CAFE HUERTOS FAMILIARES</t>
+  </si>
+  <si>
+    <t>CADENA MIRA ANGEL POLIBIO</t>
+  </si>
+  <si>
+    <t>NICOLAS GOMEZ TOBAR 161 BARRIO GALO LARREA</t>
+  </si>
+  <si>
+    <t>CADENA MORALES LIGIA DEL ROCIO</t>
+  </si>
+  <si>
+    <t>VIA A LULUQUI-SAN EDUARDO 0 Y CALLE SIN NOMBRE CASA COLOR BLANCO 2 PISOS A 1 CUADRA DE LA SEGUNDA TIENDA CASA-COLOR BLANCO 2 PISOS A 1 CUADRA DE LA SEGUNDA TIENDA</t>
+  </si>
+  <si>
+    <t>CADENA NAVARRO RUBEN DARIO</t>
+  </si>
+  <si>
+    <t>JORGE DAVILA MEZA 2105 Y ABELARDO MORAN JORGE DAVILA MEZA</t>
+  </si>
+  <si>
+    <t>CADENA OJEDA CAMPO EDGAR</t>
+  </si>
+  <si>
+    <t>IBARRA COLINAS DEL SUR CCL 2 AGOSTO Y DAQUILEMA ESQUINA</t>
+  </si>
+  <si>
+    <t>CADENA PASPUEL BLANCA OTILIA</t>
+  </si>
+  <si>
+    <t>RIO MACHINAZA 1107 Y RIO QUININDE CASA DE DOS PISOS ESQUINERA</t>
+  </si>
+  <si>
+    <t>CADENA PASPUEL EUGENIA ESPERANZA</t>
+  </si>
+  <si>
+    <t>RIO AGUARICO 11H Y CALLE S/N</t>
+  </si>
+  <si>
+    <t>CADENA PASPUEL JOSE ARCENIO</t>
+  </si>
+  <si>
+    <t>IBARRA BENJAMIN CARRION 217 PASQUEL MONGE</t>
+  </si>
+  <si>
+    <t>CADENA PASPUEL ZOILA LUZ</t>
+  </si>
+  <si>
+    <t>CUENCA 0 Y ISLA FERNANDINA</t>
+  </si>
+  <si>
+    <t>CADENA POZO EVILA SUSANA</t>
+  </si>
+  <si>
+    <t>SANCHEZ Y CIFUENTES 1465 Y ZENOM VILLACIS</t>
+  </si>
+  <si>
+    <t>CADENA PULLES HILDA CARLOTA</t>
+  </si>
+  <si>
+    <t>AV. CAP. CRISTOBAL DE TROYA 5261 L Y CALLE SIN NOMBRE</t>
+  </si>
+  <si>
+    <t>CADENA RAMIREZ CLELIA OLIVIA</t>
+  </si>
+  <si>
+    <t>IBARRA JOSE M LEORO 726</t>
+  </si>
+  <si>
+    <t>IBARRA PARR CARANQUI PRICESA CORY CORY S/N</t>
+  </si>
+  <si>
+    <t>CADENA REINA SEGUNDO HONORIO</t>
+  </si>
+  <si>
+    <t>IBARRA EL ORO SN E ISLA FERNANDINA HUERTOS FAMILIARES AZAY</t>
+  </si>
+  <si>
+    <t>CADENA RUANO EDELIN ANDREA</t>
+  </si>
+  <si>
+    <t>CALIXTO MIRANDA 378 Y TEODORO GOMEZ</t>
+  </si>
+  <si>
+    <t>CADENA VILATU�A EDUARDO</t>
+  </si>
+  <si>
+    <t>LA PORTADA 555 EL OLIVO ALTO</t>
+  </si>
+  <si>
+    <t>CADENA VILATUNA MARIA LUZ</t>
+  </si>
+  <si>
+    <t>CALLE A 441 Y AUTODROMO YAGUARCOCHA CALLE A</t>
+  </si>
+  <si>
+    <t>CADENA VILATU�A SEGUNDO MANUEL</t>
+  </si>
+  <si>
+    <t>HERMOGENES DAVILA 0 Y LOS ESPINOS</t>
+  </si>
+  <si>
+    <t>CADENA ZUMARRAGA EDWIN MAURICIO</t>
+  </si>
+  <si>
+    <t>SIMON BOLIVAR 0 Y JOSE MEJIA LEQUERICA CASA 1P / ESQUINERA BLANCA, CAFE / JUNTO ESCUELA 28 CASA 1P / ESQUINERA BLANCA, CAFE / JUNTO ESCUELA 28 JOSE MEJIA LEQUERICA</t>
+  </si>
+  <si>
+    <t>CEVALLOS CADENA HERNAN MARCELO</t>
+  </si>
+  <si>
+    <t>AV EL RETORNO 0 Y NAZACOTA PUENTO</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA FLORISELDA GERMANIA</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA EMELNORTE CALLE NR 7 JORGE DAVILA M</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA ISAURO SALOMON</t>
+  </si>
+  <si>
+    <t>RIO CHIMBO 15 Y RIO TIPUTINI</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LAS MALVINAS 0 Y CALLE SIN SALIDA SECTOR EL ROSAL</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA JULIO MIGUEL</t>
+  </si>
+  <si>
+    <t>EL ROSAL 0 SECTOR LAS MALVINAS</t>
+  </si>
+  <si>
+    <t>CHANDI CADENA LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL LULUNQUI 93 MALVINAS</t>
+  </si>
+  <si>
+    <t>CHAUCA CADENA ZOILA AMABLE</t>
+  </si>
+  <si>
+    <t>ISLA FERNANDINA 1650 Y GUARANDA ISLA FERNANDINA</t>
+  </si>
+  <si>
+    <t>DE LA CADENA BAEZ LAURO HUMBERTO</t>
+  </si>
+  <si>
+    <t>RIO QUILAGO 0 CASA 2 D CASA-2 D COLINAS DEL RETORNO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ CADENA BLANCA INES</t>
+  </si>
+  <si>
+    <t>OBISPO MOSQUERA SN Y SANCHEZ Y CIFUENTES</t>
+  </si>
+  <si>
+    <t>ELSA JIMENA CADENA REYES</t>
+  </si>
+  <si>
+    <t>RIO CHIMBO 7 Y RIO TIPUTINI FRENTE A JARDINES DEL RETORNO ETAPA 2</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ CADENA ROMMEL ALEXIS</t>
+  </si>
+  <si>
+    <t>RIO MACHINAZA 0 Y RIO QUININDE CIUDADELA LOS CEIBOS CDLA-LOS CEIBOS RIO MACHINAZA</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ CADENA SAULO EMILIO</t>
+  </si>
+  <si>
+    <t>CALIXTO MIRANDA 110 Y OBISPO MOSQUERA CALIXTO MIRANDA</t>
+  </si>
+  <si>
+    <t>ESMERALDA SIRLEY POZO CADENA</t>
+  </si>
+  <si>
+    <t>JOSE DOMINGO ALBUJA 0 Y RIO TUMBEZ RIO TUMBEZ</t>
+  </si>
+  <si>
+    <t>FABRICIO ALEXANDER CADENA DAVILA</t>
+  </si>
+  <si>
+    <t>NELSON LOPEZ OBANDO 0 Y MARIANA DE JESUS PAREDES POR EL 2X1</t>
+  </si>
+  <si>
+    <t>FERNANDO SEBASTIAN ARBOLEDA CADENA</t>
+  </si>
+  <si>
+    <t>JUAN JOSE PAEZ 39 Y VIRGINIA PEREZ ----- CASA 3 PISOS COLOR BLANCO CON AMARILLO CONJUNTO TERRA SOL</t>
+  </si>
+  <si>
+    <t>FLORES CADENA CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>AVENIDA CAMILO PONCE ENRIQUE 0 Y CORREDOR PERIFERICO FRENTE AL PARQUE CIUDAD BLANCA FRENTE AL PARQUE CIUDAD BLANCA CORREDOR PERIFERICO</t>
+  </si>
+  <si>
+    <t>FLORES CADENA SILVIA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>AV DEL PELICANO 176 Y TENA ALPACHACA</t>
+  </si>
+  <si>
+    <t>GALVEZ CADENA ERIKA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LOS GALEANOS 2G Y LAS GARDENIAS URB. NUEVA ESPERANZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ CADENA SUSANA</t>
+  </si>
+  <si>
+    <t>RIO BLANCO 0 Y RIO VINCES</t>
+  </si>
+  <si>
+    <t>IBARRA CIUDADELA LOS CEIBOS RIO VINCES 4110</t>
+  </si>
+  <si>
+    <t>GUACHAN CADENA LUZMILA</t>
+  </si>
+  <si>
+    <t>CRISTOCOCHA 158 Y CUBILCHE CERCA DE CASA PARROQUIAL CASA DE 2 PISOS BLOQUE TECHO ZIN A 60 METROS AL FONDO</t>
+  </si>
+  <si>
+    <t>GUEVARA CADENA IMELDA MARINA</t>
+  </si>
+  <si>
+    <t>IBARRA LA FLORIDA ENTRAD PRINCIPAL LOTE 1</t>
+  </si>
+  <si>
+    <t>INES GUADALUPE CADENA BENAVIDES</t>
+  </si>
+  <si>
+    <t>13 DE ABRIL 11 Y IMBABURA CONJUNTO INNOVA I CASA 11 SECTOR HUERTOS FAMILLARES CONJUNTO INNOVA I CASA 11 SECTOR HUERTOS FAMILLARES IMBABURA</t>
+  </si>
+  <si>
+    <t>KETTY AZUCENA CADENA ROMERO</t>
+  </si>
+  <si>
+    <t>RIO AGUARICO 0 Y CALLE SIN NOMBRE CASA BLANCA CONJUNTO BOSQUE DE LOS CEIBOS CASA-BLANCA CONJUNTO BOSQUE DE LOS CEIBOS</t>
+  </si>
+  <si>
+    <t>LIGIA ELENA CADENA QUENAN</t>
+  </si>
+  <si>
+    <t>LA PORTADA 34 Y - CASA 3 PISOS COLOR BLANCO POR EL ESTADIO YAGUARCOCHA CASA 3 PISOS COLOR BLANCO POR EL ESTADIO YAGUARCOCHA -</t>
+  </si>
+  <si>
+    <t>LOPEZ CADENA LUCIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>JUAN MONTALVO 175 Y BORRERO</t>
+  </si>
+  <si>
+    <t>LOPEZ CADENA MARIA ALICIA SUSANA</t>
+  </si>
+  <si>
+    <t>COLON 872 Y SANCHEZ Y CIFUENTES COLON</t>
+  </si>
+  <si>
+    <t>LUCIA YOLANDA CHAMORRO CADENA</t>
+  </si>
+  <si>
+    <t>AV EL RETORNO 0 Y CALLE SIN NOMBRE CONJUNTO ECOVIDA</t>
+  </si>
+  <si>
+    <t>GRANIZO CADENA BLANCA HILDA</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL 0 Y CALLE SIN NOMBRE BARRIO SAN ALBERTO CASA 1 PISO DE MADERA CALLE PRINCIPAL</t>
+  </si>
+  <si>
+    <t>CUELLAJE</t>
+  </si>
+  <si>
+    <t>GRANIZO CADENA MARIA TERESA</t>
+  </si>
+  <si>
+    <t>6 DE JULIO 0 Y ALEJANDRO AYALA SECTOR CUELLAJE SECTOR-CUELLAJE 6 DE JULIO</t>
+  </si>
+  <si>
+    <t>ARTIEDA CADENA ROSARIO NOEMI</t>
+  </si>
+  <si>
+    <t>TARQUI 0 N Y JUAN MONTALVO</t>
+  </si>
+  <si>
+    <t>COTACACHI</t>
+  </si>
+  <si>
+    <t>CADENA CRUZ SHANNON VERONICA</t>
+  </si>
+  <si>
+    <t>10 DE AGOSTO 0 Y CALLE A CASA 1P GRIS PORTON CAFE ENTRADA LA MIRASH CASA-1P GRIS PORTON CAFE</t>
+  </si>
+  <si>
+    <t>CADENA GUILLEN CHRISTIAN RICARDO</t>
+  </si>
+  <si>
+    <t>MANUEL LARREA 0 Y SEGUNDO L. MORENO CASA PORTON MADERA CASA PORTON-MADERA</t>
+  </si>
+  <si>
+    <t>JENIFFER ESTEFANIA MENDEZ CADENA</t>
+  </si>
+  <si>
+    <t>CALLE SIN NOMBRE 0 LUIS AYALA SCTOR CUELLAJE TORRE LUIS AYALA-SCTOR CUELLAJE ...</t>
+  </si>
+  <si>
+    <t>CADENA CORDOVA CARLOS EDMUNDO</t>
+  </si>
+  <si>
+    <t>SEGUNDO LUIS MORENO 184 Y Y GUAYAS</t>
+  </si>
+  <si>
+    <t>AZAYA</t>
+  </si>
+  <si>
+    <t>CADENA CRUZ ELENA</t>
+  </si>
+  <si>
+    <t>EL CARMEN 0</t>
+  </si>
+  <si>
+    <t>EL ORO 0 Y Y ISLA FERNANDINA N</t>
+  </si>
+  <si>
+    <t>CADENA REINA EDGAR NEPTALI</t>
+  </si>
+  <si>
+    <t>PICHINCHA 1229 Y 13 DE ABRIL HUERTOS FAMILIARES HUERTOS-FAMILIARES PICHINCHA</t>
+  </si>
+  <si>
+    <t>CADENA REINA MARIA ELISA</t>
+  </si>
+  <si>
+    <t>LUCIANO SOLANO DE LA SALA 0 Y MORONA SANTIAGO HUERTOS FAMILIARES LUCIANO SOLANO DE LA SALA</t>
+  </si>
+  <si>
+    <t>CHAMORRO CADENA LUISA CARMELA</t>
+  </si>
+  <si>
+    <t>CALLE PRINCIPAL 10 Y ESMERALDAS N- CASA DE CERRAMIENTO CON CERAMICACS# 10 DENTRO DEL CONJUNTO LILETH</t>
+  </si>
+  <si>
+    <t>MARCO EDUARDO CADENA CORAL</t>
+  </si>
+  <si>
+    <t>CALLE O 0 Y ESMERALDAS SECTOR SAN FRANCISCO DE AZAYA</t>
+  </si>
+  <si>
+    <t>ALIPIO ABSALON CADENA POSSO</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI CALLE ESPEJO Y OLMEDO</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI</t>
+  </si>
+  <si>
+    <t>ANITA PAZ CADENA IPIALES</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y LOS GERANIOS</t>
+  </si>
+  <si>
+    <t>BLANCA ROCIO CADENA CHIRAN</t>
+  </si>
+  <si>
+    <t>CELIANO AGUINAGA 1212 N Y BOLIVAR N12125 N12125 BOLIVAR</t>
+  </si>
+  <si>
+    <t>CADENA ALMEIDA VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>BOLIVAR 1823 Y DAVID MANANGON BARRIO-SAN LUIS</t>
+  </si>
+  <si>
+    <t>CADENA ANDRADE ENRIQUE FELIX</t>
+  </si>
+  <si>
+    <t>BOLIVAR 289 BRR LA DELICIA</t>
+  </si>
+  <si>
+    <t>CADENA CABASCANGO HERNA CUMANDA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCO MANTILLA 640 Y BOLIVAR MARCO MANTILLA</t>
+  </si>
+  <si>
+    <t>CADENA CABASCANGO MARIA TERESA DE JESUS</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI ROCAFUERTE 01W45</t>
+  </si>
+  <si>
+    <t>CADENA CADENA ELSA CONCEPCION</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y 12 DE FEBRERO BOLIVAR</t>
+  </si>
+  <si>
+    <t>CADENA CALDERON MARIO AUGUSTO</t>
+  </si>
+  <si>
+    <t>CALLE 0 Y BOLIVAR SANTO DOMINDO</t>
+  </si>
+  <si>
+    <t>CADENA CALDERON SIMON BOLIVAR</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 N Y CELIANO AGUINAGA SANTO DOMINGO CALLE BOLIVAR N0 CL CELIANO AGUINAGA SANTO DOMINGO CALLE BOLIVAR N0 CL CELIANO AGUINAGA CELIANO AGUINAGA</t>
+  </si>
+  <si>
+    <t>CADENA CHIRIBOGA CARLOS ANDRES</t>
+  </si>
+  <si>
+    <t>GARCIA MORENO 932 Y ELOY ALFARO GARCIA MORENO</t>
+  </si>
+  <si>
+    <t>CADENA CORDOVA GALO MARCELO</t>
+  </si>
+  <si>
+    <t>BOLIVAR 1268 SECTOR SAN LUIS</t>
+  </si>
+  <si>
+    <t>CADENA DAVILA KAREN DOMINIC</t>
+  </si>
+  <si>
+    <t>GONZALEZ SUAREZ 0 Y BOLIVAR GONZALEZ SUAREZ</t>
+  </si>
+  <si>
+    <t>CADENA ECHEVERRIA ROCIO DEL PILAR</t>
+  </si>
+  <si>
+    <t>CALLE S/N 69 SAN ALFONSO BAJO - SAN ROQUE</t>
+  </si>
+  <si>
+    <t>CADENA ESTEVEZ PAULINA MARIBEL</t>
+  </si>
+  <si>
+    <t>RIO AMAZONAS 0 Y BOLIVAR HOGARS</t>
+  </si>
+  <si>
+    <t>CADENA ESTEVEZ WILSON OSWALDO</t>
+  </si>
+  <si>
+    <t>JOSE IGNACIO PE�AHERRERA 161 Y CRISTOBAL COLON JOSE IGNACIO PE�AHERRERA</t>
+  </si>
+  <si>
+    <t>CADENA FIERRO CARLOS EFRAIN</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI MALDONADO 1261 Y OLMEDO ATUNTAQUI MALDONADO</t>
+  </si>
+  <si>
+    <t>CADENA GONZALES GONZALO RUBEN</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI IMBABURA SN Y RIOFRIO</t>
+  </si>
+  <si>
+    <t>CADENA LOPEZ EMMA ROMELIA</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GARCIA MORENO 02S26</t>
+  </si>
+  <si>
+    <t>CADENA LOPEZ HECTOR EFREN</t>
+  </si>
+  <si>
+    <t>GARCIA MORENO 0 Y GONZALEZ SUAREZ CASA ESQUINERA COLOR ROSADA</t>
+  </si>
+  <si>
+    <t>CADENA MARIA CLEMENCIA</t>
+  </si>
+  <si>
+    <t>AV. CORNELIO VELASCO 0 Y GONZALEZ SUAREZ GONZALEZ SUAREZ</t>
+  </si>
+  <si>
+    <t>CADENA MENESES OSWALDO ANIBAL</t>
+  </si>
+  <si>
+    <t>SIMON BOLIVAR SN</t>
+  </si>
+  <si>
+    <t>CADENA MIGUEL GERARDO</t>
+  </si>
+  <si>
+    <t>PROA�O MAYA 0 Y ALIPIO CADENA</t>
+  </si>
+  <si>
+    <t>CADENA MONTALVO CARLOS PATRICIO</t>
+  </si>
+  <si>
+    <t>BOLIVAR 820 Y ROCAFUERTE BOLIVAR</t>
+  </si>
+  <si>
+    <t>CADENA NAVARRO NANCY MERCEDES DEL ROCIO</t>
+  </si>
+  <si>
+    <t>ATAHUALPA SN 0 GONZALEZ SUAREZCasa CERRAMIENTO BLANCO CASA- CERRAMIENTO BLANCO---- PARROQUIA ATUNTAQUI BARRIO SANTA MARIANITA A MEDIA CUADRA DE RADIO POPULAR</t>
+  </si>
+  <si>
+    <t>CADENA POSSO JAIME RODRIGO</t>
+  </si>
+  <si>
+    <t>PANAMERICANA SUR SN 0 LOCALDE POLLOS FAINAVI LOCAL-DE POLLOS FAINAVI---- VIA A SANTO DOMINGO</t>
+  </si>
+  <si>
+    <t>CADENA POSSO VINICIO ELIAS</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y ROCAFUERTE ENTRE ROCAFUERTE Y 12 DE FEBRERO ENTRE ROCAFUERTE Y 12 DE FEBRERO</t>
+  </si>
+  <si>
+    <t>CADENA ROSA MATILDE</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GARCIA MORENO SN</t>
+  </si>
+  <si>
+    <t>CADENA SALAS LUIS ALFONSO</t>
+  </si>
+  <si>
+    <t>SUCRE SN 0810 ROCAFUERTE Casa1 PISO CREMA CASA-1 PISO CREMA---- SEC CENTRO BRR CENTRAL FRENTE TIENDA VIVERES JACOME</t>
+  </si>
+  <si>
+    <t>CADENA VALLEJOS CARLOS ALFONSO</t>
+  </si>
+  <si>
+    <t>JUAN MONTALVO 0157</t>
+  </si>
+  <si>
+    <t>CADENA VALLEJOS LUIS ARTURO</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI GARCIA MORENO 909</t>
+  </si>
+  <si>
+    <t>CADENA VILLEGAS ANITA BEATRIZ</t>
+  </si>
+  <si>
+    <t>SUCRE 1355 Y ROSALIA ROSALES DE FIERRO SUCRE</t>
+  </si>
+  <si>
+    <t>GENERAL ENRIQUEZ 0 Y RIVERA GENERAL ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>ALEJANDRO ANDRADE 1030 Y GENERAL ENRIQUEZ ALEJANDRO ANDRADE</t>
+  </si>
+  <si>
+    <t>CALDERON CADENA LUZ CELINA</t>
+  </si>
+  <si>
+    <t>GONZALEZ SUAREZ 11- 54 SUCRE CasaVERDE 1 PISO CASA-VERDE 1 PISO---- SEC CENTRO BARR CENTRAL A MEDIA CUADRA DE LA TIENDA VIVERES OLGA</t>
+  </si>
+  <si>
+    <t>CALDERON CADENA ROSA BEATRIZ</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y CALLE S/N JUNTO A IGLESIA CASA 2PS COLOR BLANCA</t>
+  </si>
+  <si>
+    <t>CRISTIAN PAUL CADENA DAVILA</t>
+  </si>
+  <si>
+    <t>BOLIVAR 0 Y AV. PICHINCHA</t>
+  </si>
+  <si>
+    <t>DAVILA CADENA SANDRA LUCIA</t>
+  </si>
+  <si>
+    <t>JUAN MONTALVO 0 Y QUITO JUAN MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ CADENA BLANCA CECILIA</t>
+  </si>
+  <si>
+    <t>PABLO RIVERA 358 Y NAPO PABLO RIVERA</t>
+  </si>
+  <si>
+    <t>DIGNA SUZANA CADENA PONCE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO ANDRADE 1244 Y OLMEDO ALEJANDRO ANDRADE</t>
+  </si>
+  <si>
+    <t>GARZON CADENA CRUZ TARQUINO</t>
+  </si>
+  <si>
+    <t>ATUNTAQUI RIO AMAZONAS SN Y VELASCO</t>
+  </si>
+  <si>
+    <t>GUIDVIA ZELANDIA CADENA POSSO</t>
+  </si>
+  <si>
+    <t>CELIANO AGUINAGA 1269 Y BOLIVAR SECTOR SANTO DOMINGO ATUNTAQUI SECT STO DOMINGO-ATUNTAQUI CELIANO AGUINAGA</t>
+  </si>
+  <si>
+    <t>JOSE CARLOS CADENA ESTEVEZ</t>
+  </si>
+  <si>
+    <t>SIN NOMBRE 0 Y BOLIVAR PLAZA DEL SALADO</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO CADENA LOPEZ</t>
+  </si>
+  <si>
+    <t>LOS GERANIOS 0 Y CALLE PRINCIPAL</t>
+  </si>
+  <si>
+    <t>MANUEL MESIAS MIRA CADENA</t>
+  </si>
+  <si>
+    <t>SIMON BOLIVAR 0 Y Y LUIS OLMEDO JATIVA DIAGONAL A CONFECCIONES MARY CASA GRIS DIAGONAL A CONFECCIONES MARY CASA GRIS LUIS OLMEDO JATIVA</t>
+  </si>
+  <si>
+    <t>CADENA JUSTO PASTOR</t>
+  </si>
+  <si>
+    <t>ARELLANO RAFAEL 666 Y PICHINCHA ----- ARELLANO RAFAEL</t>
+  </si>
+  <si>
+    <t>AMBUQUI</t>
+  </si>
+  <si>
+    <t>AGUIRRE CADENA MONICA MARLENE</t>
+  </si>
+  <si>
+    <t>ROSA ANDRADE DE LARREA 0 Y HUGO GUZMAN LARA SECTOR LA VICTORIA CASA DE DOS PISOS ROSA ANDRADE DE LARREA</t>
+  </si>
+  <si>
+    <t>MIGUEL SANCHEZ 0 Y CARLOS PROA�O CASA ESQUINERA DE 3 PISOS COLOR TRIGO CON BLANCO CASA-ESQUINERA DE 3 PISOS</t>
+  </si>
+  <si>
+    <t>JUNIN 0 Y AYACUCHO</t>
+  </si>
+  <si>
+    <t>CADENA IPIALES MARIA ESTELA</t>
+  </si>
+  <si>
+    <t>CALLE B 0 Y CALLE 1 CASA DOS PISOS TOMATE URBANIZACION FEPCOMI CASA-DOS PISOS CALLE B</t>
+  </si>
+  <si>
+    <t>CARMEN JANET CADENA FLORES</t>
+  </si>
+  <si>
+    <t>AMAZONAS 0 Y JUAN BOSCO CASA FRENTE AL CHOZON 2 CASA-FRENTE AL CHOZON 2 AMAZONAS</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH FIERRO CADENA</t>
+  </si>
+  <si>
+    <t>VIA EL CARMEN 0 Y CALLE 1</t>
+  </si>
+  <si>
+    <t>GONZALEZ CADENA JORGE ARTURO</t>
+  </si>
+  <si>
+    <t>MOJANDA 171 Y PIMAN MOJANDA</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +1592,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>22376717</v>
+        <v>62939266</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -1534,7 +1606,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>24777777</v>
+        <v>62590463</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1548,7 +1620,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>22379961</v>
+        <v>62523094</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -1557,180 +1629,180 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>23549016</v>
+        <v>62918050</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>23525575</v>
+        <v>62652292</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>23525138</v>
+        <v>62652139</v>
       </c>
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>22331333</v>
+        <v>62650002</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>22871028</v>
+        <v>62650528</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>22871158</v>
+        <v>62652090</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>22087319</v>
+        <v>62651559</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>22081957</v>
+        <v>62653310</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>22871168</v>
+        <v>62653498</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>22864494</v>
+        <v>62550942</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>22851677</v>
+        <v>62512347</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
         <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>22302236</v>
+        <v>62550110</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>23613441</v>
+        <v>62933005</v>
       </c>
       <c r="B17" t="s">
         <v>40</v>
@@ -1739,12 +1811,12 @@
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>22302237</v>
+        <v>62551334</v>
       </c>
       <c r="B18" t="s">
         <v>42</v>
@@ -1753,12 +1825,12 @@
         <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>24518925</v>
+        <v>62933541</v>
       </c>
       <c r="B19" t="s">
         <v>44</v>
@@ -1767,124 +1839,124 @@
         <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>22396525</v>
+        <v>62512950</v>
       </c>
       <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>22394192</v>
+        <v>62550060</v>
       </c>
       <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>22035740</v>
+        <v>62632681</v>
       </c>
       <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>22437075</v>
+        <v>62632448</v>
       </c>
       <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
         <v>54</v>
       </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>22537260</v>
+        <v>62937785</v>
       </c>
       <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
         <v>57</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>22481231</v>
+        <v>62937306</v>
       </c>
       <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
         <v>59</v>
       </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>22593912</v>
+        <v>62937183</v>
       </c>
       <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
         <v>61</v>
       </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>22472529</v>
+        <v>62660018</v>
       </c>
       <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
         <v>63</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>22800425</v>
+        <v>62926876</v>
       </c>
       <c r="B28" t="s">
         <v>65</v>
@@ -1893,68 +1965,68 @@
         <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>23060391</v>
+        <v>62927919</v>
       </c>
       <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
         <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>22731951</v>
+        <v>62920202</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>22730722</v>
+        <v>62924840</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>22480079</v>
+        <v>62928639</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>22482795</v>
+        <v>62927473</v>
       </c>
       <c r="B33" t="s">
         <v>75</v>
@@ -1963,12 +2035,12 @@
         <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>22430938</v>
+        <v>62903238</v>
       </c>
       <c r="B34" t="s">
         <v>77</v>
@@ -1977,12 +2049,12 @@
         <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>23360424</v>
+        <v>62922193</v>
       </c>
       <c r="B35" t="s">
         <v>79</v>
@@ -1991,12 +2063,12 @@
         <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>22297543</v>
+        <v>62520490</v>
       </c>
       <c r="B36" t="s">
         <v>81</v>
@@ -2005,12 +2077,12 @@
         <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>22267556</v>
+        <v>62930500</v>
       </c>
       <c r="B37" t="s">
         <v>83</v>
@@ -2019,12 +2091,12 @@
         <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>22439780</v>
+        <v>62928475</v>
       </c>
       <c r="B38" t="s">
         <v>85</v>
@@ -2033,2429 +2105,2429 @@
         <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A39">
-        <v>24517524</v>
+      <c r="A39" t="s">
+        <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A40">
-        <v>24525162</v>
+      <c r="A40" t="s">
+        <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A41">
-        <v>22447754</v>
+      <c r="A41" t="s">
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A42">
-        <v>22407193</v>
+      <c r="A42" t="s">
+        <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>22541912</v>
+        <v>62535624</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>22236239</v>
+        <v>62535484</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45">
-        <v>22271367</v>
+      <c r="A45" t="s">
+        <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A46">
-        <v>22448898</v>
+      <c r="A46" t="s">
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A47">
-        <v>22231199</v>
+      <c r="A47" t="s">
+        <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A48">
-        <v>22521395</v>
+      <c r="A48" t="s">
+        <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A49">
-        <v>23289254</v>
+      <c r="A49" t="s">
+        <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A50">
-        <v>22273396</v>
+      <c r="A50" t="s">
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A51">
-        <v>22444465</v>
+      <c r="A51" t="s">
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A52">
-        <v>22444032</v>
+      <c r="A52" t="s">
+        <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A53">
-        <v>22529949</v>
+      <c r="A53" t="s">
+        <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A54">
-        <v>24788397</v>
+      <c r="A54" t="s">
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>22253174</v>
+        <v>62572123</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>22580607</v>
+        <v>62946171</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>22283092</v>
+        <v>62510533</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="D57" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>22600222</v>
+        <v>62514623</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>22288129</v>
+        <v>62511093</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>22920494</v>
+        <v>62954049</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>22478688</v>
+        <v>62954993</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C61" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>22495329</v>
+        <v>62602959</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>22401357</v>
+        <v>62511046</v>
       </c>
       <c r="B63" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>23317903</v>
+        <v>62602266</v>
       </c>
       <c r="B64" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>22541350</v>
+        <v>62547182</v>
       </c>
       <c r="B65" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>22836391</v>
+        <v>62602424</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>22646999</v>
+        <v>62602740</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>22732703</v>
+        <v>62641513</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>22459091</v>
+        <v>62952089</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>22484395</v>
+        <v>62585783</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>23018099</v>
+        <v>62609629</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D71" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>22803693</v>
+        <v>62601969</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>23441213</v>
+        <v>62546264</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>22479535</v>
+        <v>62957528</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D74" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>22660859</v>
+        <v>62580049</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>23237553</v>
+        <v>62607373</v>
       </c>
       <c r="B76" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="D76" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>23238625</v>
+        <v>62950681</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>22663685</v>
+        <v>62615303</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>22590333</v>
+        <v>62610871</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C79" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>22237519</v>
+        <v>62547108</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C80" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="D80" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81">
-        <v>22526853</v>
+        <v>62650264</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>22283828</v>
+        <v>62952013</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C82" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>22321136</v>
+        <v>62658251</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="C83" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>22285027</v>
+        <v>62643722</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C84" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>23412736</v>
+        <v>62510700</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="C85" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="D85" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>23260213</v>
+        <v>62958838</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D86" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>22411865</v>
+        <v>62546379</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C87" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>22814510</v>
+        <v>62951472</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89">
-        <v>22537958</v>
+        <v>62958465</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C89" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90">
-        <v>22800685</v>
+        <v>62510655</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C90" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91">
-        <v>23477153</v>
+        <v>62954027</v>
       </c>
       <c r="B91" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="C91" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>22418598</v>
+        <v>62545488</v>
       </c>
       <c r="B92" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C92" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>23400161</v>
+        <v>62956272</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="C93" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>23284862</v>
+        <v>62644992</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95">
-        <v>22234664</v>
+        <v>62954942</v>
       </c>
       <c r="B95" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>22260319</v>
+        <v>62600953</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C96" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>22483590</v>
+        <v>62545477</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C97" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>22804051</v>
+        <v>62510593</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="C98" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D98" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>23069083</v>
+        <v>62545785</v>
       </c>
       <c r="B99" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="C99" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>23310485</v>
+        <v>62664008</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="C100" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101">
-        <v>23570721</v>
+        <v>62959814</v>
       </c>
       <c r="B101" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C101" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102">
-        <v>24523926</v>
+        <v>62631273</v>
       </c>
       <c r="B102" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C102" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="D102" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103">
-        <v>22466596</v>
+        <v>62510864</v>
       </c>
       <c r="B103" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="C103" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D103" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104">
-        <v>22467674</v>
+        <v>62511125</v>
       </c>
       <c r="B104" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="C104" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D104" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105">
-        <v>22628663</v>
+        <v>62642321</v>
       </c>
       <c r="B105" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="C105" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="D105" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106">
-        <v>22408988</v>
+        <v>62602536</v>
       </c>
       <c r="B106" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C106" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="D106" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107">
-        <v>22473403</v>
+        <v>62608381</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="C107" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D107" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108">
-        <v>23440433</v>
+        <v>62956371</v>
       </c>
       <c r="B108" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C108" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D108" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109">
-        <v>22481324</v>
+        <v>62641210</v>
       </c>
       <c r="B109" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="C109" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="D109" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110">
-        <v>23230468</v>
+        <v>62650816</v>
       </c>
       <c r="B110" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="C110" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="D110" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A111">
-        <v>23332577</v>
+        <v>62547010</v>
       </c>
       <c r="B111" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D111" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112">
-        <v>22602378</v>
+        <v>62600455</v>
       </c>
       <c r="B112" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="C112" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A113">
-        <v>22404999</v>
+        <v>62577188</v>
       </c>
       <c r="B113" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="C113" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="D113" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A114">
-        <v>22266106</v>
+        <v>62577012</v>
       </c>
       <c r="B114" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C114" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D114" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A115">
-        <v>22220536</v>
+        <v>62577269</v>
       </c>
       <c r="B115" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C115" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D115" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A116">
-        <v>22224851</v>
+        <v>62607253</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C116" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="D116" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A117">
-        <v>22279366</v>
+        <v>62602443</v>
       </c>
       <c r="B117" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C117" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="D117" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A118">
-        <v>22449209</v>
+        <v>62952669</v>
       </c>
       <c r="B118" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C118" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A119">
-        <v>22413754</v>
+        <v>62505129</v>
       </c>
       <c r="B119" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C119" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D119" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A120">
-        <v>23690401</v>
+        <v>62664031</v>
       </c>
       <c r="B120" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C120" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A121">
-        <v>23033100</v>
+        <v>62664030</v>
       </c>
       <c r="B121" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C121" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D121" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A122">
-        <v>22447048</v>
+        <v>62664054</v>
       </c>
       <c r="B122" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C122" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D122" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A123">
-        <v>23447277</v>
+        <v>62546456</v>
       </c>
       <c r="B123" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C123" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D123" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A124">
-        <v>22811380</v>
+        <v>62539077</v>
       </c>
       <c r="B124" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C124" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D124" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A125">
-        <v>22423965</v>
+        <v>62951437</v>
       </c>
       <c r="B125" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C125" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D125" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A126">
-        <v>22510164</v>
+        <v>62511485</v>
       </c>
       <c r="B126" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C126" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D126" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A127">
-        <v>22248981</v>
+        <v>62951550</v>
       </c>
       <c r="B127" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C127" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D127" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A128">
-        <v>22244134</v>
+        <v>62640136</v>
       </c>
       <c r="B128" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C128" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D128" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A129">
-        <v>22434380</v>
+        <v>62558560</v>
       </c>
       <c r="B129" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C129" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D129" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A130">
-        <v>22907448</v>
+        <v>62652921</v>
       </c>
       <c r="B130" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C130" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D130" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A131">
-        <v>22447246</v>
+        <v>62511798</v>
       </c>
       <c r="B131" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C131" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D131" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A132">
-        <v>24515070</v>
+        <v>62514785</v>
       </c>
       <c r="B132" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C132" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D132" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A133">
-        <v>23342937</v>
+        <v>62511247</v>
       </c>
       <c r="B133" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="C133" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D133" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A134">
-        <v>23520068</v>
+        <v>62517777</v>
       </c>
       <c r="B134" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C134" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D134" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A135">
-        <v>23819105</v>
+        <v>62609930</v>
       </c>
       <c r="B135" t="s">
-        <v>30</v>
+        <v>248</v>
       </c>
       <c r="C135" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D135" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A136">
-        <v>22565437</v>
+        <v>62954240</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D136" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A137">
-        <v>22238222</v>
+        <v>62580006</v>
       </c>
       <c r="B137" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C137" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D137" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A138">
-        <v>22268048</v>
+        <v>62632661</v>
       </c>
       <c r="B138" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C138" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="D138" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A139">
-        <v>22408970</v>
+        <v>62513778</v>
       </c>
       <c r="B139" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C139" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D139" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A140">
-        <v>23151651</v>
+        <v>62512827</v>
       </c>
       <c r="B140" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C140" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D140" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A141">
-        <v>22600273</v>
+        <v>62577365</v>
       </c>
       <c r="B141" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="D141" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A142">
-        <v>22244862</v>
+        <v>62953704</v>
       </c>
       <c r="B142" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="D142" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A143">
-        <v>22248259</v>
+        <v>62609309</v>
       </c>
       <c r="B143" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C143" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A144">
-        <v>24759365</v>
+        <v>62511390</v>
       </c>
       <c r="B144" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C144" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D144" t="s">
-        <v>277</v>
+        <v>99</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A145">
-        <v>22354214</v>
+        <v>63016397</v>
       </c>
       <c r="B145" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="C145" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D145" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A146">
-        <v>23430475</v>
+        <v>62679086</v>
       </c>
       <c r="B146" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C146" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D146" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A147">
-        <v>23430669</v>
+        <v>62915962</v>
       </c>
       <c r="B147" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C147" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="D147" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A148">
-        <v>23490259</v>
+        <v>62490623</v>
       </c>
       <c r="B148" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C148" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D148" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A149">
-        <v>23490774</v>
+        <v>62916140</v>
       </c>
       <c r="B149" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C149" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D149" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A150">
-        <v>22384869</v>
+        <v>62679148</v>
       </c>
       <c r="B150" t="s">
+        <v>279</v>
+      </c>
+      <c r="C150" t="s">
+        <v>280</v>
+      </c>
+      <c r="D150" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A151">
+        <v>62546820</v>
+      </c>
+      <c r="B151" t="s">
+        <v>281</v>
+      </c>
+      <c r="C151" t="s">
+        <v>282</v>
+      </c>
+      <c r="D151" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A152">
+        <v>62546131</v>
+      </c>
+      <c r="B152" t="s">
+        <v>284</v>
+      </c>
+      <c r="C152" t="s">
+        <v>285</v>
+      </c>
+      <c r="D152" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A153">
+        <v>62558171</v>
+      </c>
+      <c r="B153" t="s">
+        <v>193</v>
+      </c>
+      <c r="C153" t="s">
+        <v>286</v>
+      </c>
+      <c r="D153" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A154">
+        <v>62546431</v>
+      </c>
+      <c r="B154" t="s">
+        <v>287</v>
+      </c>
+      <c r="C154" t="s">
         <v>288</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D154" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A155">
+        <v>62558167</v>
+      </c>
+      <c r="B155" t="s">
         <v>289</v>
       </c>
-      <c r="D150" t="s">
+      <c r="C155" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A151" t="s">
-        <v>4</v>
-      </c>
-      <c r="B151" t="s">
-        <v>4</v>
-      </c>
-      <c r="C151" t="s">
-        <v>4</v>
-      </c>
-      <c r="D151" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
-        <v>4</v>
-      </c>
-      <c r="B152" t="s">
-        <v>4</v>
-      </c>
-      <c r="C152" t="s">
-        <v>4</v>
-      </c>
-      <c r="D152" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A153" t="s">
-        <v>4</v>
-      </c>
-      <c r="B153" t="s">
-        <v>4</v>
-      </c>
-      <c r="C153" t="s">
-        <v>4</v>
-      </c>
-      <c r="D153" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A154" t="s">
-        <v>4</v>
-      </c>
-      <c r="B154" t="s">
-        <v>4</v>
-      </c>
-      <c r="C154" t="s">
-        <v>4</v>
-      </c>
-      <c r="D154" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>4</v>
-      </c>
-      <c r="B155" t="s">
-        <v>4</v>
-      </c>
-      <c r="C155" t="s">
-        <v>4</v>
-      </c>
       <c r="D155" t="s">
-        <v>4</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
-        <v>4</v>
+      <c r="A156">
+        <v>62558135</v>
       </c>
       <c r="B156" t="s">
-        <v>4</v>
+        <v>291</v>
       </c>
       <c r="C156" t="s">
-        <v>4</v>
+        <v>292</v>
       </c>
       <c r="D156" t="s">
-        <v>4</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A157" t="s">
-        <v>4</v>
+      <c r="A157">
+        <v>62558243</v>
       </c>
       <c r="B157" t="s">
-        <v>4</v>
+        <v>293</v>
       </c>
       <c r="C157" t="s">
-        <v>4</v>
+        <v>294</v>
       </c>
       <c r="D157" t="s">
-        <v>4</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A158" t="s">
-        <v>4</v>
+      <c r="A158">
+        <v>62906457</v>
       </c>
       <c r="B158" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="C158" t="s">
-        <v>4</v>
+        <v>296</v>
       </c>
       <c r="D158" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
-        <v>4</v>
+      <c r="A159">
+        <v>62617368</v>
       </c>
       <c r="B159" t="s">
-        <v>4</v>
+        <v>298</v>
       </c>
       <c r="C159" t="s">
-        <v>4</v>
+        <v>299</v>
       </c>
       <c r="D159" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
-        <v>4</v>
+      <c r="A160">
+        <v>62617139</v>
       </c>
       <c r="B160" t="s">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="C160" t="s">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="D160" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A161" t="s">
-        <v>4</v>
+      <c r="A161">
+        <v>62907835</v>
       </c>
       <c r="B161" t="s">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="C161" t="s">
-        <v>4</v>
+        <v>303</v>
       </c>
       <c r="D161" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A162">
-        <v>22058382</v>
+        <v>62900079</v>
       </c>
       <c r="B162" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C162" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="D162" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A163">
-        <v>22885076</v>
+        <v>62908650</v>
       </c>
       <c r="B163" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C163" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D163" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A164">
-        <v>22885528</v>
+        <v>62909217</v>
       </c>
       <c r="B164" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C164" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D164" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A165">
-        <v>22899293</v>
+        <v>62908605</v>
       </c>
       <c r="B165" t="s">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="C165" t="s">
+        <v>311</v>
+      </c>
+      <c r="D165" t="s">
         <v>297</v>
-      </c>
-      <c r="D165" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A166">
-        <v>22316218</v>
+        <v>62909036</v>
       </c>
       <c r="B166" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C166" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D166" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A167" t="s">
-        <v>0</v>
+      <c r="A167">
+        <v>62617279</v>
       </c>
       <c r="B167" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="C167" t="s">
-        <v>2</v>
+        <v>315</v>
       </c>
       <c r="D167" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A168" t="s">
-        <v>0</v>
+      <c r="A168">
+        <v>62910187</v>
       </c>
       <c r="B168" t="s">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="C168" t="s">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="D168" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A169" t="s">
-        <v>0</v>
+      <c r="A169">
+        <v>62908362</v>
       </c>
       <c r="B169" t="s">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="C169" t="s">
-        <v>2</v>
+        <v>319</v>
       </c>
       <c r="D169" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A170" t="s">
-        <v>0</v>
+      <c r="A170">
+        <v>62910178</v>
       </c>
       <c r="B170" t="s">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="C170" t="s">
-        <v>2</v>
+        <v>321</v>
       </c>
       <c r="D170" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A171" t="s">
-        <v>0</v>
+      <c r="A171">
+        <v>62900253</v>
       </c>
       <c r="B171" t="s">
-        <v>1</v>
+        <v>322</v>
       </c>
       <c r="C171" t="s">
-        <v>2</v>
+        <v>323</v>
       </c>
       <c r="D171" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A172" t="s">
-        <v>0</v>
+      <c r="A172">
+        <v>62909400</v>
       </c>
       <c r="B172" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="C172" t="s">
-        <v>2</v>
+        <v>325</v>
       </c>
       <c r="D172" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
-        <v>0</v>
+      <c r="A173">
+        <v>62530501</v>
       </c>
       <c r="B173" t="s">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="C173" t="s">
-        <v>2</v>
+        <v>327</v>
       </c>
       <c r="D173" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A174" t="s">
-        <v>0</v>
+      <c r="A174">
+        <v>62908025</v>
       </c>
       <c r="B174" t="s">
-        <v>1</v>
+        <v>328</v>
       </c>
       <c r="C174" t="s">
-        <v>2</v>
+        <v>329</v>
       </c>
       <c r="D174" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A175" t="s">
-        <v>0</v>
+      <c r="A175">
+        <v>62530644</v>
       </c>
       <c r="B175" t="s">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="C175" t="s">
-        <v>2</v>
+        <v>331</v>
       </c>
       <c r="D175" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A176" t="s">
-        <v>0</v>
+      <c r="A176">
+        <v>62907572</v>
       </c>
       <c r="B176" t="s">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C176" t="s">
-        <v>2</v>
+        <v>333</v>
       </c>
       <c r="D176" t="s">
-        <v>3</v>
+        <v>297</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A177">
-        <v>22199077</v>
+        <v>62906201</v>
       </c>
       <c r="B177" t="s">
-        <v>209</v>
+        <v>334</v>
       </c>
       <c r="C177" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="D177" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A178">
-        <v>22032568</v>
+        <v>62533426</v>
       </c>
       <c r="B178" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="C178" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="D178" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A179">
-        <v>22386470</v>
+        <v>62906198</v>
       </c>
       <c r="B179" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="C179" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="D179" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A180">
-        <v>23762126</v>
+        <v>62908872</v>
       </c>
       <c r="B180" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="C180" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="D180" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A181">
-        <v>22710322</v>
+        <v>62908408</v>
       </c>
       <c r="B181" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="C181" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="D181" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A182">
-        <v>22714388</v>
+        <v>62908443</v>
       </c>
       <c r="B182" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="C182" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="D182" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A183">
-        <v>23708181</v>
+        <v>62909483</v>
       </c>
       <c r="B183" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="C183" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="D183" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A184">
-        <v>22120047</v>
+        <v>62909206</v>
       </c>
       <c r="B184" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="C184" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="D184" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A185">
-        <v>23804286</v>
+        <v>62907620</v>
       </c>
       <c r="B185" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="C185" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="D185" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A186">
-        <v>23804424</v>
+        <v>62907551</v>
       </c>
       <c r="B186" t="s">
-        <v>132</v>
+        <v>352</v>
       </c>
       <c r="C186" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="D186" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A187">
-        <v>23560115</v>
+        <v>62906170</v>
       </c>
       <c r="B187" t="s">
-        <v>40</v>
+        <v>354</v>
       </c>
       <c r="C187" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="D187" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A188">
-        <v>23560172</v>
+        <v>62907984</v>
       </c>
       <c r="B188" t="s">
-        <v>40</v>
+        <v>356</v>
       </c>
       <c r="C188" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="D188" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A189">
-        <v>23550104</v>
+        <v>62906626</v>
       </c>
       <c r="B189" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="C189" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D189" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A190">
-        <v>22894115</v>
+        <v>62908678</v>
       </c>
       <c r="B190" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="C190" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D190" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A191">
-        <v>23806662</v>
+        <v>62909541</v>
       </c>
       <c r="B191" t="s">
-        <v>330</v>
+        <v>210</v>
       </c>
       <c r="C191" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="D191" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A192">
-        <v>23806145</v>
+        <v>62906391</v>
       </c>
       <c r="B192" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="C192" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="D192" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A193">
-        <v>22895323</v>
+        <v>62900087</v>
       </c>
       <c r="B193" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="C193" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="D193" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A194">
-        <v>22895333</v>
+        <v>62907857</v>
       </c>
       <c r="B194" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="C194" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="D194" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A195">
-        <v>24519535</v>
+        <v>62907946</v>
       </c>
       <c r="B195" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="C195" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="D195" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A196">
-        <v>22343172</v>
+        <v>62533208</v>
       </c>
       <c r="B196" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="C196" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="D196" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A197">
-        <v>22190866</v>
+        <v>62908735</v>
       </c>
       <c r="B197" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="C197" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="D197" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A198">
-        <v>24502907</v>
+        <v>62906506</v>
       </c>
       <c r="B198" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="C198" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="D198" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A199">
-        <v>22346661</v>
+        <v>62906460</v>
       </c>
       <c r="B199" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="C199" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="D199" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A200">
-        <v>23182250</v>
+        <v>62907032</v>
       </c>
       <c r="B200" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="C200" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="D200" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A201">
-        <v>23503014</v>
+        <v>62900323</v>
       </c>
       <c r="B201" t="s">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="C201" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="D201" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A202">
-        <v>22133034</v>
+        <v>62909188</v>
       </c>
       <c r="B202" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C202" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="D202" t="s">
-        <v>354</v>
+        <v>297</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A203">
-        <v>23533083</v>
+        <v>62617061</v>
       </c>
       <c r="B203" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="C203" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="D203" t="s">
-        <v>354</v>
+        <v>297</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A204">
-        <v>22827600</v>
+        <v>62637338</v>
       </c>
       <c r="B204" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C204" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="D204" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A205">
-        <v>22065581</v>
+      <c r="A205" t="s">
+        <v>5</v>
       </c>
       <c r="B205" t="s">
-        <v>360</v>
+        <v>5</v>
       </c>
       <c r="C205" t="s">
-        <v>361</v>
+        <v>5</v>
       </c>
       <c r="D205" t="s">
-        <v>359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A206">
-        <v>23478033</v>
+      <c r="A206" t="s">
+        <v>5</v>
       </c>
       <c r="B206" t="s">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>363</v>
+        <v>5</v>
       </c>
       <c r="D206" t="s">
-        <v>359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A207">
-        <v>22825904</v>
+      <c r="A207" t="s">
+        <v>5</v>
       </c>
       <c r="B207" t="s">
-        <v>364</v>
+        <v>5</v>
       </c>
       <c r="C207" t="s">
-        <v>365</v>
+        <v>5</v>
       </c>
       <c r="D207" t="s">
-        <v>359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A208">
-        <v>24532232</v>
+      <c r="A208" t="s">
+        <v>5</v>
       </c>
       <c r="B208" t="s">
-        <v>366</v>
+        <v>5</v>
       </c>
       <c r="C208" t="s">
-        <v>367</v>
+        <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A209">
-        <v>22304327</v>
+      <c r="A209" t="s">
+        <v>5</v>
       </c>
       <c r="B209" t="s">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="C209" t="s">
-        <v>368</v>
+        <v>5</v>
       </c>
       <c r="D209" t="s">
-        <v>369</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A210">
-        <v>22877504</v>
+      <c r="A210" t="s">
+        <v>5</v>
       </c>
       <c r="B210" t="s">
-        <v>370</v>
+        <v>5</v>
       </c>
       <c r="C210" t="s">
-        <v>371</v>
+        <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>372</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A211">
-        <v>23821416</v>
+      <c r="A211" t="s">
+        <v>5</v>
       </c>
       <c r="B211" t="s">
-        <v>373</v>
+        <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>374</v>
+        <v>5</v>
       </c>
       <c r="D211" t="s">
-        <v>372</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -4501,101 +4573,80 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A215" t="s">
-        <v>5</v>
+      <c r="A215">
+        <v>62616138</v>
       </c>
       <c r="B215" t="s">
-        <v>5</v>
+        <v>387</v>
       </c>
       <c r="C215" t="s">
-        <v>5</v>
-      </c>
-      <c r="D215" t="s">
-        <v>5</v>
+        <v>388</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A216" t="s">
-        <v>5</v>
+      <c r="A216">
+        <v>62586156</v>
       </c>
       <c r="B216" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C216" t="s">
-        <v>5</v>
-      </c>
-      <c r="D216" t="s">
-        <v>5</v>
+        <v>389</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A217" t="s">
-        <v>5</v>
+      <c r="A217">
+        <v>62530221</v>
       </c>
       <c r="B217" t="s">
-        <v>5</v>
+        <v>324</v>
       </c>
       <c r="C217" t="s">
-        <v>5</v>
-      </c>
-      <c r="D217" t="s">
-        <v>5</v>
+        <v>390</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A218" t="s">
-        <v>5</v>
+      <c r="A218">
+        <v>62585821</v>
       </c>
       <c r="B218" t="s">
-        <v>5</v>
+        <v>391</v>
       </c>
       <c r="C218" t="s">
-        <v>5</v>
-      </c>
-      <c r="D218" t="s">
-        <v>5</v>
+        <v>392</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A219" t="s">
-        <v>5</v>
+      <c r="A219">
+        <v>62533462</v>
       </c>
       <c r="B219" t="s">
-        <v>5</v>
+        <v>393</v>
       </c>
       <c r="C219" t="s">
-        <v>5</v>
-      </c>
-      <c r="D219" t="s">
-        <v>5</v>
+        <v>394</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A220" t="s">
-        <v>5</v>
+      <c r="A220">
+        <v>62699002</v>
       </c>
       <c r="B220" t="s">
-        <v>5</v>
+        <v>395</v>
       </c>
       <c r="C220" t="s">
-        <v>5</v>
-      </c>
-      <c r="D220" t="s">
-        <v>5</v>
+        <v>396</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A221" t="s">
-        <v>5</v>
+      <c r="A221">
+        <v>62580560</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="C221" t="s">
-        <v>5</v>
-      </c>
-      <c r="D221" t="s">
-        <v>5</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
